--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127386314</v>
+        <v>127369923</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>476867</v>
       </c>
       <c r="R2" t="n">
-        <v>6854648</v>
+        <v>6854642</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,65 +743,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127386081</v>
+        <v>127386314</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
@@ -819,10 +828,10 @@
         <v>476867</v>
       </c>
       <c r="R3" t="n">
-        <v>6854478</v>
+        <v>6854648</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,50 +869,51 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127386839</v>
+        <v>127386081</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,13 +923,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476824</v>
+        <v>476867</v>
       </c>
       <c r="R4" t="n">
-        <v>6854630</v>
+        <v>6854478</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,60 +973,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127371169</v>
+        <v>127386839</v>
       </c>
       <c r="B5" t="n">
-        <v>91346</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476901</v>
+        <v>476824</v>
       </c>
       <c r="R5" t="n">
-        <v>6854667</v>
+        <v>6854630</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1043,19 +1053,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1070,22 +1070,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127369215</v>
+        <v>127371169</v>
       </c>
       <c r="B6" t="n">
-        <v>78681</v>
+        <v>91346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,21 +1093,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476907</v>
+        <v>476901</v>
       </c>
       <c r="R6" t="n">
-        <v>6854785</v>
+        <v>6854667</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,52 +1189,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127386098</v>
+        <v>127369215</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>78681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476851</v>
+        <v>476907</v>
       </c>
       <c r="R7" t="n">
-        <v>6854670</v>
+        <v>6854785</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,75 +1257,88 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127369923</v>
+        <v>127386098</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476867</v>
+        <v>476851</v>
       </c>
       <c r="R8" t="n">
-        <v>6854642</v>
+        <v>6854670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,95 +1368,90 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127388142</v>
+        <v>127387597</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476840</v>
+        <v>476831</v>
       </c>
       <c r="R9" t="n">
-        <v>6854642</v>
+        <v>6854622</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1485,25 +1489,26 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127388973</v>
+        <v>127387592</v>
       </c>
       <c r="B10" t="n">
         <v>98443</v>
@@ -1533,22 +1538,30 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476828</v>
+        <v>476796</v>
       </c>
       <c r="R10" t="n">
-        <v>6854626</v>
+        <v>6854627</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1578,6 +1591,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,64 +1611,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127388966</v>
+        <v>127386850</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476792</v>
+        <v>476896</v>
       </c>
       <c r="R11" t="n">
-        <v>6854646</v>
+        <v>6854789</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,26 +1702,25 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127387597</v>
+        <v>127371659</v>
       </c>
       <c r="B12" t="n">
         <v>98443</v>
@@ -1735,32 +1748,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476831</v>
+        <v>476822</v>
       </c>
       <c r="R12" t="n">
-        <v>6854622</v>
+        <v>6854617</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1787,90 +1788,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127387592</v>
+        <v>127386809</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476796</v>
+        <v>476898</v>
       </c>
       <c r="R13" t="n">
-        <v>6854627</v>
+        <v>6854784</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,40 +1900,34 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127386850</v>
+        <v>127388142</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,37 +1935,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476896</v>
+        <v>476840</v>
       </c>
       <c r="R14" t="n">
-        <v>6854789</v>
+        <v>6854642</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,19 +2017,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127371659</v>
+        <v>127388973</v>
       </c>
       <c r="B15" t="n">
         <v>98443</v>
@@ -2057,17 +2057,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476822</v>
+        <v>476828</v>
       </c>
       <c r="R15" t="n">
-        <v>6854617</v>
+        <v>6854626</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2097,87 +2101,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127386809</v>
+        <v>127388966</v>
       </c>
       <c r="B16" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476898</v>
+        <v>476792</v>
       </c>
       <c r="R16" t="n">
-        <v>6854784</v>
+        <v>6854646</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,71 +2214,64 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127386305</v>
+        <v>127388145</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476855</v>
+        <v>476840</v>
       </c>
       <c r="R17" t="n">
-        <v>6854627</v>
+        <v>6854642</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2320,26 +2312,25 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127386099</v>
+        <v>127388963</v>
       </c>
       <c r="B18" t="n">
         <v>98443</v>
@@ -2369,7 +2360,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2378,13 +2369,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476865</v>
+        <v>476856</v>
       </c>
       <c r="R18" t="n">
-        <v>6854478</v>
+        <v>6854653</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,57 +2420,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127388145</v>
+        <v>127386305</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476840</v>
+        <v>476855</v>
       </c>
       <c r="R19" t="n">
-        <v>6854642</v>
+        <v>6854627</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2520,25 +2519,26 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127388963</v>
+        <v>127386099</v>
       </c>
       <c r="B20" t="n">
         <v>98443</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2577,13 +2577,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476856</v>
+        <v>476865</v>
       </c>
       <c r="R20" t="n">
-        <v>6854653</v>
+        <v>6854478</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -7707,7 +7707,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127388970</v>
+        <v>127387596</v>
       </c>
       <c r="B70" t="n">
         <v>98443</v>
@@ -7737,22 +7737,30 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>476836</v>
+        <v>476827</v>
       </c>
       <c r="R70" t="n">
-        <v>6854641</v>
+        <v>6854628</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7797,19 +7805,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127387596</v>
+        <v>127371242</v>
       </c>
       <c r="B71" t="n">
         <v>98443</v>
@@ -7839,30 +7847,22 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>476827</v>
+        <v>476826</v>
       </c>
       <c r="R71" t="n">
-        <v>6854628</v>
+        <v>6854459</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7889,37 +7889,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127371242</v>
+        <v>127386109</v>
       </c>
       <c r="B72" t="n">
         <v>98443</v>
@@ -7947,24 +7956,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>476826</v>
+        <v>476831</v>
       </c>
       <c r="R72" t="n">
-        <v>6854459</v>
+        <v>6854531</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7991,19 +7996,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8018,19 +8013,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127386109</v>
+        <v>127388970</v>
       </c>
       <c r="B73" t="n">
         <v>98443</v>
@@ -8058,20 +8053,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>476831</v>
+        <v>476836</v>
       </c>
       <c r="R73" t="n">
-        <v>6854531</v>
+        <v>6854641</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8109,66 +8108,67 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127369233</v>
+        <v>127386841</v>
       </c>
       <c r="B74" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>476907</v>
+        <v>476865</v>
       </c>
       <c r="R74" t="n">
-        <v>6854785</v>
+        <v>6854629</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8195,19 +8195,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8222,19 +8212,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127386097</v>
+        <v>127387595</v>
       </c>
       <c r="B75" t="n">
         <v>98443</v>
@@ -8264,22 +8254,30 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476794</v>
+        <v>476804</v>
       </c>
       <c r="R75" t="n">
-        <v>6854562</v>
+        <v>6854628</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8324,60 +8322,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127386841</v>
+        <v>127369233</v>
       </c>
       <c r="B76" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476865</v>
+        <v>476907</v>
       </c>
       <c r="R76" t="n">
-        <v>6854629</v>
+        <v>6854785</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8404,9 +8402,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8421,19 +8429,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127387595</v>
+        <v>127386097</v>
       </c>
       <c r="B77" t="n">
         <v>98443</v>
@@ -8463,30 +8471,22 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476804</v>
+        <v>476794</v>
       </c>
       <c r="R77" t="n">
-        <v>6854628</v>
+        <v>6854562</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8531,12 +8531,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8645,48 +8645,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127386843</v>
+        <v>127369891</v>
       </c>
       <c r="B79" t="n">
-        <v>98443</v>
+        <v>80152</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476842</v>
+        <v>476866</v>
       </c>
       <c r="R79" t="n">
-        <v>6854652</v>
+        <v>6854642</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8713,9 +8713,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8730,60 +8740,60 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127369660</v>
+        <v>127386843</v>
       </c>
       <c r="B80" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476880</v>
+        <v>476842</v>
       </c>
       <c r="R80" t="n">
-        <v>6854794</v>
+        <v>6854652</v>
       </c>
       <c r="S80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8810,19 +8820,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8837,65 +8837,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127386315</v>
+        <v>127369660</v>
       </c>
       <c r="B81" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476883</v>
+        <v>476880</v>
       </c>
       <c r="R81" t="n">
-        <v>6854657</v>
+        <v>6854794</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -8925,37 +8917,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386103</v>
+        <v>127386315</v>
       </c>
       <c r="B82" t="n">
         <v>98443</v>
@@ -8985,22 +8986,26 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476832</v>
+        <v>476883</v>
       </c>
       <c r="R82" t="n">
-        <v>6854485</v>
+        <v>6854657</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9045,19 +9050,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386300</v>
+        <v>127386103</v>
       </c>
       <c r="B83" t="n">
         <v>98443</v>
@@ -9087,26 +9092,22 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476830</v>
+        <v>476832</v>
       </c>
       <c r="R83" t="n">
-        <v>6854480</v>
+        <v>6854485</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9151,60 +9152,68 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386082</v>
+        <v>127386300</v>
       </c>
       <c r="B84" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476804</v>
+        <v>476830</v>
       </c>
       <c r="R84" t="n">
-        <v>6854643</v>
+        <v>6854480</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9242,28 +9251,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127386820</v>
+        <v>127386082</v>
       </c>
       <c r="B85" t="n">
-        <v>92608</v>
+        <v>78773</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9271,21 +9281,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9295,13 +9305,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476882</v>
+        <v>476804</v>
       </c>
       <c r="R85" t="n">
-        <v>6854669</v>
+        <v>6854643</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9345,60 +9355,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386834</v>
+        <v>127386820</v>
       </c>
       <c r="B86" t="n">
-        <v>80077</v>
+        <v>92608</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476869</v>
+        <v>476882</v>
       </c>
       <c r="R86" t="n">
-        <v>6854645</v>
+        <v>6854669</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9439,7 +9446,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9451,17 +9457,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127369891</v>
+        <v>127386834</v>
       </c>
       <c r="B87" t="n">
-        <v>80152</v>
+        <v>80077</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9469,37 +9475,40 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476866</v>
+        <v>476869</v>
       </c>
       <c r="R87" t="n">
-        <v>6854642</v>
+        <v>6854645</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9526,87 +9535,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127386828</v>
+        <v>127388974</v>
       </c>
       <c r="B88" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476869</v>
+        <v>476859</v>
       </c>
       <c r="R88" t="n">
-        <v>6854645</v>
+        <v>6854547</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9644,66 +9648,79 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386080</v>
+        <v>127386840</v>
       </c>
       <c r="B89" t="n">
-        <v>92628</v>
+        <v>98443</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476799</v>
+        <v>476852</v>
       </c>
       <c r="R89" t="n">
-        <v>6854562</v>
+        <v>6854630</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9741,50 +9758,51 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127386129</v>
+        <v>127386828</v>
       </c>
       <c r="B90" t="n">
-        <v>92616</v>
+        <v>80117</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9794,13 +9812,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476790</v>
+        <v>476869</v>
       </c>
       <c r="R90" t="n">
-        <v>6854633</v>
+        <v>6854645</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9844,64 +9862,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127388974</v>
+        <v>127386080</v>
       </c>
       <c r="B91" t="n">
-        <v>98443</v>
+        <v>92628</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476859</v>
+        <v>476799</v>
       </c>
       <c r="R91" t="n">
-        <v>6854547</v>
+        <v>6854562</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9939,79 +9953,66 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127386840</v>
+        <v>127386129</v>
       </c>
       <c r="B92" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476852</v>
+        <v>476790</v>
       </c>
       <c r="R92" t="n">
-        <v>6854630</v>
+        <v>6854633</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10049,19 +10050,18 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127369923</v>
+        <v>127369215</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>78681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476867</v>
+        <v>476907</v>
       </c>
       <c r="R2" t="n">
-        <v>6854642</v>
+        <v>6854785</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,55 +770,47 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127386314</v>
+        <v>127386081</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
@@ -828,10 +820,10 @@
         <v>476867</v>
       </c>
       <c r="R3" t="n">
-        <v>6854648</v>
+        <v>6854478</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,54 +861,61 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127386081</v>
+        <v>127386314</v>
       </c>
       <c r="B4" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
@@ -926,10 +925,10 @@
         <v>476867</v>
       </c>
       <c r="R4" t="n">
-        <v>6854478</v>
+        <v>6854648</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,18 +966,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1082,48 +1082,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127371169</v>
+        <v>127386098</v>
       </c>
       <c r="B6" t="n">
-        <v>91346</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476901</v>
+        <v>476851</v>
       </c>
       <c r="R6" t="n">
-        <v>6854667</v>
+        <v>6854670</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1150,71 +1154,62 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127369215</v>
+        <v>127369923</v>
       </c>
       <c r="B7" t="n">
-        <v>78681</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1224,13 +1219,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476907</v>
+        <v>476867</v>
       </c>
       <c r="R7" t="n">
-        <v>6854785</v>
+        <v>6854642</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1259,7 +1254,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1269,7 +1264,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,64 +1279,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127386098</v>
+        <v>127371169</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>91346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476851</v>
+        <v>476901</v>
       </c>
       <c r="R8" t="n">
-        <v>6854670</v>
+        <v>6854667</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,37 +1359,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127387597</v>
+        <v>127388973</v>
       </c>
       <c r="B9" t="n">
         <v>98443</v>
@@ -1428,30 +1428,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476831</v>
+        <v>476828</v>
       </c>
       <c r="R9" t="n">
-        <v>6854622</v>
+        <v>6854626</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,19 +1488,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127387592</v>
+        <v>127371659</v>
       </c>
       <c r="B10" t="n">
         <v>98443</v>
@@ -1536,32 +1528,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476796</v>
+        <v>476822</v>
       </c>
       <c r="R10" t="n">
-        <v>6854627</v>
+        <v>6854617</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,14 +1568,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,67 +1589,78 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127386850</v>
+        <v>127387597</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476896</v>
+        <v>476831</v>
       </c>
       <c r="R11" t="n">
-        <v>6854789</v>
+        <v>6854622</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1702,25 +1698,26 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127371659</v>
+        <v>127387592</v>
       </c>
       <c r="B12" t="n">
         <v>98443</v>
@@ -1748,20 +1745,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476822</v>
+        <v>476796</v>
       </c>
       <c r="R12" t="n">
-        <v>6854617</v>
+        <v>6854627</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,19 +1797,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:39</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,66 +1813,71 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127386809</v>
+        <v>127388966</v>
       </c>
       <c r="B13" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476898</v>
+        <v>476792</v>
       </c>
       <c r="R13" t="n">
-        <v>6854784</v>
+        <v>6854646</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1906,18 +1915,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2022,59 +2032,55 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127388973</v>
+        <v>127386809</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476828</v>
+        <v>476898</v>
       </c>
       <c r="R15" t="n">
-        <v>6854626</v>
+        <v>6854784</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,71 +2118,66 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127388966</v>
+        <v>127386850</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476792</v>
+        <v>476896</v>
       </c>
       <c r="R16" t="n">
-        <v>6854646</v>
+        <v>6854789</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2214,64 +2215,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127388145</v>
+        <v>127388963</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476840</v>
+        <v>476856</v>
       </c>
       <c r="R17" t="n">
-        <v>6854642</v>
+        <v>6854653</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2312,25 +2316,26 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127388963</v>
+        <v>127386305</v>
       </c>
       <c r="B18" t="n">
         <v>98443</v>
@@ -2360,19 +2365,23 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476856</v>
+        <v>476855</v>
       </c>
       <c r="R18" t="n">
-        <v>6854653</v>
+        <v>6854627</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2420,19 +2429,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127386305</v>
+        <v>127386099</v>
       </c>
       <c r="B19" t="n">
         <v>98443</v>
@@ -2462,26 +2471,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476855</v>
+        <v>476865</v>
       </c>
       <c r="R19" t="n">
-        <v>6854627</v>
+        <v>6854478</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,64 +2531,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127386099</v>
+        <v>127388145</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476865</v>
+        <v>476840</v>
       </c>
       <c r="R20" t="n">
-        <v>6854478</v>
+        <v>6854642</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2621,51 +2622,50 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127386848</v>
+        <v>127386067</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476840</v>
+        <v>476821</v>
       </c>
       <c r="R21" t="n">
-        <v>6854622</v>
+        <v>6854543</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,51 +2719,50 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127386067</v>
+        <v>127386848</v>
       </c>
       <c r="B22" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,13 +2772,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476821</v>
+        <v>476840</v>
       </c>
       <c r="R22" t="n">
-        <v>6854543</v>
+        <v>6854622</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2817,50 +2816,51 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127387585</v>
+        <v>127387581</v>
       </c>
       <c r="B23" t="n">
-        <v>80117</v>
+        <v>97321</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476865</v>
+        <v>476827</v>
       </c>
       <c r="R23" t="n">
-        <v>6854638</v>
+        <v>6854629</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2920,60 +2920,68 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127387581</v>
+        <v>127386302</v>
       </c>
       <c r="B24" t="n">
-        <v>97321</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476827</v>
+        <v>476828</v>
       </c>
       <c r="R24" t="n">
-        <v>6854629</v>
+        <v>6854531</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3011,25 +3019,26 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127386302</v>
+        <v>127388976</v>
       </c>
       <c r="B25" t="n">
         <v>98443</v>
@@ -3057,13 +3066,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3072,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476828</v>
+        <v>476880</v>
       </c>
       <c r="R25" t="n">
-        <v>6854531</v>
+        <v>6854486</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3123,47 +3132,51 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127386319</v>
+        <v>127386102</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
@@ -3173,10 +3186,10 @@
         <v>476821</v>
       </c>
       <c r="R26" t="n">
-        <v>6854475</v>
+        <v>6854465</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3214,57 +3227,54 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127386102</v>
+        <v>127386319</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
@@ -3274,10 +3284,10 @@
         <v>476821</v>
       </c>
       <c r="R27" t="n">
-        <v>6854465</v>
+        <v>6854475</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3315,19 +3325,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3441,56 +3450,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127388976</v>
+        <v>127387585</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476880</v>
+        <v>476865</v>
       </c>
       <c r="R29" t="n">
-        <v>6854486</v>
+        <v>6854638</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3528,19 +3529,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3652,48 +3652,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127386111</v>
+        <v>127371357</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476831</v>
+        <v>476901</v>
       </c>
       <c r="R31" t="n">
-        <v>6854682</v>
+        <v>6854667</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3720,9 +3720,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3737,64 +3747,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127386100</v>
+        <v>127370759</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>80152</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476829</v>
+        <v>476877</v>
       </c>
       <c r="R32" t="n">
-        <v>6854465</v>
+        <v>6854663</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3821,37 +3827,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127386299</v>
+        <v>127386111</v>
       </c>
       <c r="B33" t="n">
         <v>98443</v>
@@ -3879,28 +3894,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476817</v>
+        <v>476831</v>
       </c>
       <c r="R33" t="n">
-        <v>6854465</v>
+        <v>6854682</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3938,26 +3945,25 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127386303</v>
+        <v>127386100</v>
       </c>
       <c r="B34" t="n">
         <v>98443</v>
@@ -3987,26 +3993,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476836</v>
+        <v>476829</v>
       </c>
       <c r="R34" t="n">
-        <v>6854627</v>
+        <v>6854465</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4051,19 +4053,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127386112</v>
+        <v>127386299</v>
       </c>
       <c r="B35" t="n">
         <v>98443</v>
@@ -4091,20 +4093,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476873</v>
+        <v>476817</v>
       </c>
       <c r="R35" t="n">
-        <v>6854658</v>
+        <v>6854465</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4142,63 +4152,72 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127371357</v>
+        <v>127386303</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476901</v>
+        <v>476836</v>
       </c>
       <c r="R36" t="n">
-        <v>6854667</v>
+        <v>6854627</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4228,87 +4247,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127370759</v>
+        <v>127386112</v>
       </c>
       <c r="B37" t="n">
-        <v>80152</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476877</v>
+        <v>476873</v>
       </c>
       <c r="R37" t="n">
-        <v>6854663</v>
+        <v>6854658</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4335,19 +4345,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4362,72 +4362,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127387587</v>
+        <v>127386117</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476850</v>
+        <v>476835</v>
       </c>
       <c r="R38" t="n">
-        <v>6854640</v>
+        <v>6854539</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4465,26 +4453,25 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127387586</v>
+        <v>127386108</v>
       </c>
       <c r="B39" t="n">
         <v>98443</v>
@@ -4519,13 +4506,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476859</v>
+        <v>476830</v>
       </c>
       <c r="R39" t="n">
-        <v>6854667</v>
+        <v>6854468</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4569,19 +4556,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127386108</v>
+        <v>127387587</v>
       </c>
       <c r="B40" t="n">
         <v>98443</v>
@@ -4609,20 +4596,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476830</v>
+        <v>476850</v>
       </c>
       <c r="R40" t="n">
-        <v>6854468</v>
+        <v>6854640</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4660,18 +4659,19 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4789,32 +4789,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127386117</v>
+        <v>127387586</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476835</v>
+        <v>476859</v>
       </c>
       <c r="R42" t="n">
-        <v>6854539</v>
+        <v>6854667</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4874,12 +4874,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127386078</v>
+        <v>127386808</v>
       </c>
       <c r="B45" t="n">
-        <v>98464</v>
+        <v>79046</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476854</v>
+        <v>476882</v>
       </c>
       <c r="R45" t="n">
-        <v>6854673</v>
+        <v>6854781</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5185,44 +5185,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127386808</v>
+        <v>127386078</v>
       </c>
       <c r="B46" t="n">
-        <v>79046</v>
+        <v>98464</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5232,13 +5232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476882</v>
+        <v>476854</v>
       </c>
       <c r="R46" t="n">
-        <v>6854781</v>
+        <v>6854673</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5282,19 +5282,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127387598</v>
+        <v>127386312</v>
       </c>
       <c r="B47" t="n">
         <v>98443</v>
@@ -5322,32 +5322,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476767</v>
+        <v>476860</v>
       </c>
       <c r="R47" t="n">
-        <v>6854589</v>
+        <v>6854625</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5385,67 +5373,78 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127386087</v>
+        <v>127387598</v>
       </c>
       <c r="B48" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476780</v>
+        <v>476767</v>
       </c>
       <c r="R48" t="n">
-        <v>6854482</v>
+        <v>6854589</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5483,50 +5482,51 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127386089</v>
+        <v>127386838</v>
       </c>
       <c r="B49" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5536,13 +5536,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476838</v>
+        <v>476819</v>
       </c>
       <c r="R49" t="n">
-        <v>6854681</v>
+        <v>6854632</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5586,22 +5586,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127371200</v>
+        <v>127370572</v>
       </c>
       <c r="B50" t="n">
-        <v>92608</v>
+        <v>96696</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,21 +5609,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476901</v>
+        <v>476857</v>
       </c>
       <c r="R50" t="n">
-        <v>6854667</v>
+        <v>6854654</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5705,10 +5705,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127370572</v>
+        <v>127386087</v>
       </c>
       <c r="B51" t="n">
-        <v>96696</v>
+        <v>78772</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5716,37 +5716,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476857</v>
+        <v>476780</v>
       </c>
       <c r="R51" t="n">
-        <v>6854654</v>
+        <v>6854482</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5773,19 +5773,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5800,44 +5790,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386312</v>
+        <v>127386089</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>78772</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,13 +5837,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476860</v>
+        <v>476838</v>
       </c>
       <c r="R52" t="n">
-        <v>6854625</v>
+        <v>6854681</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5897,12 +5887,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6009,55 +5999,55 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127386838</v>
+        <v>127371200</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>92608</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476819</v>
+        <v>476901</v>
       </c>
       <c r="R54" t="n">
-        <v>6854632</v>
+        <v>6854667</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6084,9 +6074,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6101,12 +6101,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6637,12 +6637,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6752,19 +6752,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127387590</v>
+        <v>127386313</v>
       </c>
       <c r="B61" t="n">
         <v>98443</v>
@@ -6794,14 +6794,10 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -6811,13 +6807,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476860</v>
+        <v>476881</v>
       </c>
       <c r="R61" t="n">
-        <v>6854552</v>
+        <v>6854650</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6847,11 +6843,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>4 blommande stänglar</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6867,19 +6858,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127386313</v>
+        <v>127371630</v>
       </c>
       <c r="B62" t="n">
         <v>98443</v>
@@ -6909,26 +6900,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476881</v>
+        <v>476874</v>
       </c>
       <c r="R62" t="n">
-        <v>6854650</v>
+        <v>6854475</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6955,37 +6947,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127371630</v>
+        <v>127387590</v>
       </c>
       <c r="B63" t="n">
         <v>98443</v>
@@ -7015,27 +7016,30 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>476874</v>
+        <v>476860</v>
       </c>
       <c r="R63" t="n">
-        <v>6854475</v>
+        <v>6854552</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7062,19 +7066,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>16:38</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>4 blommande stänglar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7083,50 +7082,51 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger , Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127386842</v>
+        <v>127386068</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7136,13 +7136,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>476869</v>
+        <v>476822</v>
       </c>
       <c r="R64" t="n">
-        <v>6854655</v>
+        <v>6854551</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7186,22 +7186,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127386068</v>
+        <v>127371302</v>
       </c>
       <c r="B65" t="n">
-        <v>79046</v>
+        <v>78773</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7209,37 +7209,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476822</v>
+        <v>476826</v>
       </c>
       <c r="R65" t="n">
-        <v>6854551</v>
+        <v>6854459</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7266,9 +7266,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7283,12 +7293,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7491,14 +7501,14 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386096</v>
+        <v>127386842</v>
       </c>
       <c r="B68" t="n">
         <v>98443</v>
@@ -7526,24 +7536,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476806</v>
+        <v>476869</v>
       </c>
       <c r="R68" t="n">
-        <v>6854483</v>
+        <v>6854655</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7581,67 +7587,70 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127371302</v>
+        <v>127386096</v>
       </c>
       <c r="B69" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476826</v>
+        <v>476806</v>
       </c>
       <c r="R69" t="n">
-        <v>6854459</v>
+        <v>6854483</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7668,46 +7677,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127387596</v>
+        <v>127388970</v>
       </c>
       <c r="B70" t="n">
         <v>98443</v>
@@ -7737,30 +7737,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>476827</v>
+        <v>476836</v>
       </c>
       <c r="R70" t="n">
-        <v>6854628</v>
+        <v>6854641</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7805,19 +7797,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127371242</v>
+        <v>127387596</v>
       </c>
       <c r="B71" t="n">
         <v>98443</v>
@@ -7847,22 +7839,30 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>476826</v>
+        <v>476827</v>
       </c>
       <c r="R71" t="n">
-        <v>6854459</v>
+        <v>6854628</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7889,46 +7889,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127386109</v>
+        <v>127371242</v>
       </c>
       <c r="B72" t="n">
         <v>98443</v>
@@ -7956,20 +7947,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>476831</v>
+        <v>476826</v>
       </c>
       <c r="R72" t="n">
-        <v>6854531</v>
+        <v>6854459</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7996,9 +7991,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8013,19 +8018,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127388970</v>
+        <v>127386109</v>
       </c>
       <c r="B73" t="n">
         <v>98443</v>
@@ -8053,24 +8058,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>476836</v>
+        <v>476831</v>
       </c>
       <c r="R73" t="n">
-        <v>6854641</v>
+        <v>6854531</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8108,67 +8109,66 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127386841</v>
+        <v>127369233</v>
       </c>
       <c r="B74" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>476865</v>
+        <v>476907</v>
       </c>
       <c r="R74" t="n">
-        <v>6854629</v>
+        <v>6854785</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8195,9 +8195,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8212,19 +8222,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127387595</v>
+        <v>127386841</v>
       </c>
       <c r="B75" t="n">
         <v>98443</v>
@@ -8252,32 +8262,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476804</v>
+        <v>476865</v>
       </c>
       <c r="R75" t="n">
-        <v>6854628</v>
+        <v>6854629</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8315,64 +8313,67 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127369233</v>
+        <v>127388972</v>
       </c>
       <c r="B76" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476907</v>
+        <v>476809</v>
       </c>
       <c r="R76" t="n">
-        <v>6854785</v>
+        <v>6854638</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -8402,46 +8403,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127386097</v>
+        <v>127387595</v>
       </c>
       <c r="B77" t="n">
         <v>98443</v>
@@ -8471,22 +8463,30 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476794</v>
+        <v>476804</v>
       </c>
       <c r="R77" t="n">
-        <v>6854562</v>
+        <v>6854628</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8531,19 +8531,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127388972</v>
+        <v>127386097</v>
       </c>
       <c r="B78" t="n">
         <v>98443</v>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8582,13 +8582,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476809</v>
+        <v>476794</v>
       </c>
       <c r="R78" t="n">
-        <v>6854638</v>
+        <v>6854562</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8633,44 +8633,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127369891</v>
+        <v>127369660</v>
       </c>
       <c r="B79" t="n">
-        <v>80152</v>
+        <v>96696</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8680,13 +8680,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476866</v>
+        <v>476880</v>
       </c>
       <c r="R79" t="n">
-        <v>6854642</v>
+        <v>6854794</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8740,60 +8740,60 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127386843</v>
+        <v>127369891</v>
       </c>
       <c r="B80" t="n">
-        <v>98443</v>
+        <v>80152</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476842</v>
+        <v>476866</v>
       </c>
       <c r="R80" t="n">
-        <v>6854652</v>
+        <v>6854642</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8820,9 +8820,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8837,22 +8847,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127369660</v>
+        <v>127386820</v>
       </c>
       <c r="B81" t="n">
-        <v>96696</v>
+        <v>92608</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8860,37 +8870,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476880</v>
+        <v>476882</v>
       </c>
       <c r="R81" t="n">
-        <v>6854794</v>
+        <v>6854669</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8917,19 +8927,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8944,68 +8944,60 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386315</v>
+        <v>127386082</v>
       </c>
       <c r="B82" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476883</v>
+        <v>476804</v>
       </c>
       <c r="R82" t="n">
-        <v>6854657</v>
+        <v>6854643</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9043,26 +9035,25 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386103</v>
+        <v>127386315</v>
       </c>
       <c r="B83" t="n">
         <v>98443</v>
@@ -9092,22 +9083,26 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476832</v>
+        <v>476883</v>
       </c>
       <c r="R83" t="n">
-        <v>6854485</v>
+        <v>6854657</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9152,19 +9147,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386300</v>
+        <v>127386103</v>
       </c>
       <c r="B84" t="n">
         <v>98443</v>
@@ -9194,26 +9189,22 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476830</v>
+        <v>476832</v>
       </c>
       <c r="R84" t="n">
-        <v>6854480</v>
+        <v>6854485</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9258,60 +9249,68 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127386082</v>
+        <v>127386300</v>
       </c>
       <c r="B85" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476804</v>
+        <v>476830</v>
       </c>
       <c r="R85" t="n">
-        <v>6854643</v>
+        <v>6854480</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9349,50 +9348,51 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386820</v>
+        <v>127386843</v>
       </c>
       <c r="B86" t="n">
-        <v>92608</v>
+        <v>98443</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476882</v>
+        <v>476842</v>
       </c>
       <c r="R86" t="n">
-        <v>6854669</v>
+        <v>6854652</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9565,52 +9565,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127388974</v>
+        <v>127386828</v>
       </c>
       <c r="B88" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476859</v>
+        <v>476869</v>
       </c>
       <c r="R88" t="n">
-        <v>6854547</v>
+        <v>6854645</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9648,79 +9644,66 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386840</v>
+        <v>127386080</v>
       </c>
       <c r="B89" t="n">
-        <v>98443</v>
+        <v>92628</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476852</v>
+        <v>476799</v>
       </c>
       <c r="R89" t="n">
-        <v>6854630</v>
+        <v>6854562</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9758,51 +9741,50 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127386828</v>
+        <v>127386129</v>
       </c>
       <c r="B90" t="n">
-        <v>80117</v>
+        <v>92616</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9812,13 +9794,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476869</v>
+        <v>476790</v>
       </c>
       <c r="R90" t="n">
-        <v>6854645</v>
+        <v>6854633</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9862,60 +9844,64 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127386080</v>
+        <v>127388974</v>
       </c>
       <c r="B91" t="n">
-        <v>92628</v>
+        <v>98443</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476799</v>
+        <v>476859</v>
       </c>
       <c r="R91" t="n">
-        <v>6854562</v>
+        <v>6854547</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9953,66 +9939,79 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127386129</v>
+        <v>127386840</v>
       </c>
       <c r="B92" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476790</v>
+        <v>476852</v>
       </c>
       <c r="R92" t="n">
-        <v>6854633</v>
+        <v>6854630</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10050,70 +10049,67 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127386101</v>
+        <v>127386320</v>
       </c>
       <c r="B93" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>476785</v>
+        <v>476832</v>
       </c>
       <c r="R93" t="n">
-        <v>6854487</v>
+        <v>6854631</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10151,67 +10147,70 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127386320</v>
+        <v>127386101</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>476832</v>
+        <v>476785</v>
       </c>
       <c r="R94" t="n">
-        <v>6854631</v>
+        <v>6854487</v>
       </c>
       <c r="S94" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10249,18 +10248,19 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10364,10 +10364,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127370318</v>
+        <v>127388141</v>
       </c>
       <c r="B96" t="n">
-        <v>80117</v>
+        <v>57654</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10375,37 +10375,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476810</v>
+        <v>476834</v>
       </c>
       <c r="R96" t="n">
-        <v>6854587</v>
+        <v>6854535</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10432,19 +10440,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10459,61 +10457,57 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127386104</v>
+        <v>127370318</v>
       </c>
       <c r="B97" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476865</v>
+        <v>476810</v>
       </c>
       <c r="R97" t="n">
-        <v>6854661</v>
+        <v>6854587</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10543,37 +10537,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127386107</v>
+        <v>127386104</v>
       </c>
       <c r="B98" t="n">
         <v>98443</v>
@@ -10603,7 +10606,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -10612,10 +10615,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>476800</v>
+        <v>476865</v>
       </c>
       <c r="R98" t="n">
-        <v>6854551</v>
+        <v>6854661</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10668,63 +10671,59 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127388141</v>
+        <v>127386107</v>
       </c>
       <c r="B99" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476834</v>
+        <v>476800</v>
       </c>
       <c r="R99" t="n">
-        <v>6854535</v>
+        <v>6854551</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10762,78 +10761,67 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127387594</v>
+        <v>127386854</v>
       </c>
       <c r="B100" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>476850</v>
+        <v>476899</v>
       </c>
       <c r="R100" t="n">
-        <v>6854546</v>
+        <v>6854779</v>
       </c>
       <c r="S100" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10871,51 +10859,50 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Karin Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger , Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127386854</v>
+        <v>127386088</v>
       </c>
       <c r="B101" t="n">
-        <v>92616</v>
+        <v>78772</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10925,13 +10912,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476899</v>
+        <v>476826</v>
       </c>
       <c r="R101" t="n">
-        <v>6854779</v>
+        <v>6854482</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10975,12 +10962,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elias Blad, Karin Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger , Nadja Karlsson</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11084,48 +11071,56 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127386088</v>
+        <v>127386310</v>
       </c>
       <c r="B103" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>476826</v>
+        <v>476822</v>
       </c>
       <c r="R103" t="n">
-        <v>6854482</v>
+        <v>6854557</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11163,25 +11158,26 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger , Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127386310</v>
+        <v>127388967</v>
       </c>
       <c r="B104" t="n">
         <v>98443</v>
@@ -11211,23 +11207,19 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>476822</v>
+        <v>476843</v>
       </c>
       <c r="R104" t="n">
-        <v>6854557</v>
+        <v>6854525</v>
       </c>
       <c r="S104" t="n">
         <v>4</v>
@@ -11275,19 +11267,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127388967</v>
+        <v>127387594</v>
       </c>
       <c r="B105" t="n">
         <v>98443</v>
@@ -11317,22 +11309,30 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>476843</v>
+        <v>476850</v>
       </c>
       <c r="R105" t="n">
-        <v>6854525</v>
+        <v>6854546</v>
       </c>
       <c r="S105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11377,12 +11377,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -1398,52 +1398,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127388973</v>
+        <v>127386809</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476828</v>
+        <v>476898</v>
       </c>
       <c r="R9" t="n">
-        <v>6854626</v>
+        <v>6854784</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1481,67 +1477,66 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127371659</v>
+        <v>127386850</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476822</v>
+        <v>476896</v>
       </c>
       <c r="R10" t="n">
-        <v>6854617</v>
+        <v>6854789</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1568,19 +1563,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,72 +1580,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127387597</v>
+        <v>127388142</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476831</v>
+        <v>476840</v>
       </c>
       <c r="R11" t="n">
-        <v>6854622</v>
+        <v>6854642</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1698,26 +1679,25 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127387592</v>
+        <v>127388973</v>
       </c>
       <c r="B12" t="n">
         <v>98443</v>
@@ -1747,30 +1727,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476796</v>
+        <v>476828</v>
       </c>
       <c r="R12" t="n">
-        <v>6854627</v>
+        <v>6854626</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1800,11 +1772,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,19 +1787,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127388966</v>
+        <v>127371659</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1860,21 +1827,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476792</v>
+        <v>476822</v>
       </c>
       <c r="R13" t="n">
-        <v>6854646</v>
+        <v>6854617</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1904,86 +1867,99 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127388142</v>
+        <v>127387597</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476840</v>
+        <v>476831</v>
       </c>
       <c r="R14" t="n">
-        <v>6854642</v>
+        <v>6854622</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,66 +1997,79 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127386809</v>
+        <v>127387592</v>
       </c>
       <c r="B15" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476898</v>
+        <v>476796</v>
       </c>
       <c r="R15" t="n">
-        <v>6854784</v>
+        <v>6854627</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,72 +2101,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127386850</v>
+        <v>127388966</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476896</v>
+        <v>476792</v>
       </c>
       <c r="R16" t="n">
-        <v>6854789</v>
+        <v>6854646</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,18 +2214,19 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -5294,45 +5294,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127386312</v>
+        <v>127370572</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476860</v>
+        <v>476857</v>
       </c>
       <c r="R47" t="n">
-        <v>6854625</v>
+        <v>6854654</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5362,9 +5362,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5379,72 +5389,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127387598</v>
+        <v>127386087</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>78772</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476767</v>
+        <v>476780</v>
       </c>
       <c r="R48" t="n">
-        <v>6854589</v>
+        <v>6854482</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5482,51 +5480,50 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127386838</v>
+        <v>127386089</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>78772</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5536,13 +5533,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476819</v>
+        <v>476838</v>
       </c>
       <c r="R49" t="n">
-        <v>6854632</v>
+        <v>6854681</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5586,22 +5583,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127370572</v>
+        <v>127371346</v>
       </c>
       <c r="B50" t="n">
-        <v>96696</v>
+        <v>78772</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,21 +5606,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5633,13 +5630,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476857</v>
+        <v>476826</v>
       </c>
       <c r="R50" t="n">
-        <v>6854654</v>
+        <v>6854459</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5668,7 +5665,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5678,7 +5675,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5693,22 +5690,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127386087</v>
+        <v>127371200</v>
       </c>
       <c r="B51" t="n">
-        <v>78772</v>
+        <v>92608</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5716,37 +5713,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476780</v>
+        <v>476901</v>
       </c>
       <c r="R51" t="n">
-        <v>6854482</v>
+        <v>6854667</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5773,9 +5770,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5790,44 +5797,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386089</v>
+        <v>127386312</v>
       </c>
       <c r="B52" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5837,13 +5844,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476838</v>
+        <v>476860</v>
       </c>
       <c r="R52" t="n">
-        <v>6854681</v>
+        <v>6854625</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5887,60 +5894,72 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127371346</v>
+        <v>127387598</v>
       </c>
       <c r="B53" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476826</v>
+        <v>476767</v>
       </c>
       <c r="R53" t="n">
-        <v>6854459</v>
+        <v>6854589</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5967,87 +5986,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127371200</v>
+        <v>127386838</v>
       </c>
       <c r="B54" t="n">
-        <v>92608</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476901</v>
+        <v>476819</v>
       </c>
       <c r="R54" t="n">
-        <v>6854667</v>
+        <v>6854632</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6074,19 +6084,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6101,62 +6101,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127372315</v>
+        <v>127370418</v>
       </c>
       <c r="B55" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476894</v>
+        <v>476867</v>
       </c>
       <c r="R55" t="n">
-        <v>6854772</v>
+        <v>6854691</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6188,7 +6183,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6198,7 +6193,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6225,45 +6220,52 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127370418</v>
+        <v>127388147</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476867</v>
+        <v>476787</v>
       </c>
       <c r="R56" t="n">
-        <v>6854691</v>
+        <v>6854642</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6293,49 +6295,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127388147</v>
+        <v>127372315</v>
       </c>
       <c r="B57" t="n">
-        <v>92616</v>
+        <v>56849</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6343,41 +6336,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476787</v>
+        <v>476894</v>
       </c>
       <c r="R57" t="n">
-        <v>6854642</v>
+        <v>6854772</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6407,78 +6398,99 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127386849</v>
+        <v>127387593</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>476891</v>
+        <v>476780</v>
       </c>
       <c r="R58" t="n">
-        <v>6854776</v>
+        <v>6854617</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6510,31 +6522,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127387593</v>
+        <v>127387589</v>
       </c>
       <c r="B59" t="n">
         <v>98443</v>
@@ -6564,7 +6582,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6581,10 +6599,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476780</v>
+        <v>476812</v>
       </c>
       <c r="R59" t="n">
-        <v>6854617</v>
+        <v>6854623</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6649,7 +6667,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127387589</v>
+        <v>127386313</v>
       </c>
       <c r="B60" t="n">
         <v>98443</v>
@@ -6679,14 +6697,10 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -6696,13 +6710,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476812</v>
+        <v>476881</v>
       </c>
       <c r="R60" t="n">
-        <v>6854623</v>
+        <v>6854650</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6732,11 +6746,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6752,19 +6761,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127386313</v>
+        <v>127371630</v>
       </c>
       <c r="B61" t="n">
         <v>98443</v>
@@ -6794,26 +6803,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476881</v>
+        <v>476874</v>
       </c>
       <c r="R61" t="n">
-        <v>6854650</v>
+        <v>6854475</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6840,37 +6850,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127371630</v>
+        <v>127387590</v>
       </c>
       <c r="B62" t="n">
         <v>98443</v>
@@ -6900,27 +6919,30 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476874</v>
+        <v>476860</v>
       </c>
       <c r="R62" t="n">
-        <v>6854475</v>
+        <v>6854552</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6947,19 +6969,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>16:38</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>4 blommande stänglar</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6968,78 +6985,67 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127387590</v>
+        <v>127386849</v>
       </c>
       <c r="B63" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>476860</v>
+        <v>476891</v>
       </c>
       <c r="R63" t="n">
-        <v>6854552</v>
+        <v>6854776</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7071,30 +7077,24 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>4 blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8645,10 +8645,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127369660</v>
+        <v>127386820</v>
       </c>
       <c r="B79" t="n">
-        <v>96696</v>
+        <v>92608</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8656,37 +8656,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>4361</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476880</v>
+        <v>476882</v>
       </c>
       <c r="R79" t="n">
-        <v>6854794</v>
+        <v>6854669</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8713,19 +8713,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8740,57 +8730,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127369891</v>
+        <v>127386082</v>
       </c>
       <c r="B80" t="n">
-        <v>80152</v>
+        <v>78773</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476866</v>
+        <v>476804</v>
       </c>
       <c r="R80" t="n">
-        <v>6854642</v>
+        <v>6854643</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8820,19 +8810,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8847,22 +8827,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127386820</v>
+        <v>127369660</v>
       </c>
       <c r="B81" t="n">
-        <v>92608</v>
+        <v>96696</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8870,37 +8850,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476882</v>
+        <v>476880</v>
       </c>
       <c r="R81" t="n">
-        <v>6854669</v>
+        <v>6854794</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8927,9 +8907,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8944,57 +8934,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386082</v>
+        <v>127369891</v>
       </c>
       <c r="B82" t="n">
-        <v>78773</v>
+        <v>80152</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476804</v>
+        <v>476866</v>
       </c>
       <c r="R82" t="n">
-        <v>6854643</v>
+        <v>6854642</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9024,9 +9014,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9041,12 +9041,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -10877,10 +10877,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127386088</v>
+        <v>127386811</v>
       </c>
       <c r="B101" t="n">
-        <v>78772</v>
+        <v>79603</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10888,21 +10888,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10912,13 +10912,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476826</v>
+        <v>476887</v>
       </c>
       <c r="R101" t="n">
-        <v>6854482</v>
+        <v>6854810</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10962,22 +10962,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127386811</v>
+        <v>127386088</v>
       </c>
       <c r="B102" t="n">
-        <v>79603</v>
+        <v>78772</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10985,21 +10985,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11009,13 +11009,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>476887</v>
+        <v>476826</v>
       </c>
       <c r="R102" t="n">
-        <v>6854810</v>
+        <v>6854482</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11059,12 +11059,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127369215</v>
+        <v>127369923</v>
       </c>
       <c r="B2" t="n">
-        <v>78681</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476907</v>
+        <v>476867</v>
       </c>
       <c r="R2" t="n">
-        <v>6854785</v>
+        <v>6854642</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127386081</v>
+        <v>127371169</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>91346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476867</v>
+        <v>476901</v>
       </c>
       <c r="R3" t="n">
-        <v>6854478</v>
+        <v>6854667</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +850,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1184,32 +1194,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127369923</v>
+        <v>127369215</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>78681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,13 +1229,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476867</v>
+        <v>476907</v>
       </c>
       <c r="R7" t="n">
-        <v>6854642</v>
+        <v>6854785</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,7 +1264,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1264,7 +1274,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,22 +1289,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127371169</v>
+        <v>127386081</v>
       </c>
       <c r="B8" t="n">
-        <v>91346</v>
+        <v>78773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,37 +1312,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476901</v>
+        <v>476867</v>
       </c>
       <c r="R8" t="n">
-        <v>6854667</v>
+        <v>6854478</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,19 +1369,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,60 +1386,64 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127386809</v>
+        <v>127388973</v>
       </c>
       <c r="B9" t="n">
-        <v>79046</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476898</v>
+        <v>476828</v>
       </c>
       <c r="R9" t="n">
-        <v>6854784</v>
+        <v>6854626</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1477,66 +1481,67 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127386850</v>
+        <v>127371659</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476896</v>
+        <v>476822</v>
       </c>
       <c r="R10" t="n">
-        <v>6854789</v>
+        <v>6854617</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1563,9 +1568,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,68 +1595,72 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127388142</v>
+        <v>127387597</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476840</v>
+        <v>476831</v>
       </c>
       <c r="R11" t="n">
-        <v>6854642</v>
+        <v>6854622</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,25 +1698,26 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127388973</v>
+        <v>127387592</v>
       </c>
       <c r="B12" t="n">
         <v>98443</v>
@@ -1727,22 +1747,30 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476828</v>
+        <v>476796</v>
       </c>
       <c r="R12" t="n">
-        <v>6854626</v>
+        <v>6854627</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1772,6 +1800,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,19 +1820,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127371659</v>
+        <v>127388966</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1827,17 +1860,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476822</v>
+        <v>476792</v>
       </c>
       <c r="R13" t="n">
-        <v>6854617</v>
+        <v>6854646</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1867,99 +1904,86 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127387597</v>
+        <v>127388142</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476831</v>
+        <v>476840</v>
       </c>
       <c r="R14" t="n">
-        <v>6854622</v>
+        <v>6854642</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1997,79 +2021,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127387592</v>
+        <v>127386809</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476796</v>
+        <v>476898</v>
       </c>
       <c r="R15" t="n">
-        <v>6854627</v>
+        <v>6854784</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,82 +2112,72 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127388966</v>
+        <v>127386850</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476792</v>
+        <v>476896</v>
       </c>
       <c r="R16" t="n">
-        <v>6854646</v>
+        <v>6854789</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2214,19 +2215,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3547,55 +3547,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127386295</v>
+        <v>127386111</v>
       </c>
       <c r="B30" t="n">
-        <v>91346</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476888</v>
+        <v>476831</v>
       </c>
       <c r="R30" t="n">
-        <v>6854664</v>
+        <v>6854682</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3633,64 +3626,71 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127371357</v>
+        <v>127386303</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476901</v>
+        <v>476836</v>
       </c>
       <c r="R31" t="n">
-        <v>6854667</v>
+        <v>6854627</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -3720,87 +3720,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127370759</v>
+        <v>127386112</v>
       </c>
       <c r="B32" t="n">
-        <v>80152</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476877</v>
+        <v>476873</v>
       </c>
       <c r="R32" t="n">
-        <v>6854663</v>
+        <v>6854658</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3827,19 +3818,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3854,19 +3835,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127386111</v>
+        <v>127386100</v>
       </c>
       <c r="B33" t="n">
         <v>98443</v>
@@ -3894,17 +3875,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476831</v>
+        <v>476829</v>
       </c>
       <c r="R33" t="n">
-        <v>6854682</v>
+        <v>6854465</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3945,6 +3930,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3963,7 +3949,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127386100</v>
+        <v>127386299</v>
       </c>
       <c r="B34" t="n">
         <v>98443</v>
@@ -3993,22 +3979,26 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476829</v>
+        <v>476817</v>
       </c>
       <c r="R34" t="n">
         <v>6854465</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4053,54 +4043,53 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127386299</v>
+        <v>127386295</v>
       </c>
       <c r="B35" t="n">
-        <v>98443</v>
+        <v>91346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4108,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476817</v>
+        <v>476888</v>
       </c>
       <c r="R35" t="n">
-        <v>6854465</v>
+        <v>6854664</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4171,53 +4160,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127386303</v>
+        <v>127371357</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476836</v>
+        <v>476901</v>
       </c>
       <c r="R36" t="n">
-        <v>6854627</v>
+        <v>6854667</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4247,78 +4228,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127386112</v>
+        <v>127370759</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>80152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476873</v>
+        <v>476877</v>
       </c>
       <c r="R37" t="n">
-        <v>6854658</v>
+        <v>6854663</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4345,9 +4335,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4362,12 +4362,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -6113,45 +6113,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127370418</v>
+        <v>127372315</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476867</v>
+        <v>476894</v>
       </c>
       <c r="R55" t="n">
-        <v>6854691</v>
+        <v>6854772</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6183,7 +6188,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6193,7 +6198,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6220,52 +6225,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127388147</v>
+        <v>127370418</v>
       </c>
       <c r="B56" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476787</v>
+        <v>476867</v>
       </c>
       <c r="R56" t="n">
-        <v>6854642</v>
+        <v>6854691</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6295,40 +6293,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127372315</v>
+        <v>127388147</v>
       </c>
       <c r="B57" t="n">
-        <v>56849</v>
+        <v>92616</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6336,39 +6343,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476894</v>
+        <v>476787</v>
       </c>
       <c r="R57" t="n">
-        <v>6854772</v>
+        <v>6854642</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6398,39 +6407,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>17:12</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>17:12</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7101,10 +7101,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127386068</v>
+        <v>127371302</v>
       </c>
       <c r="B64" t="n">
-        <v>79046</v>
+        <v>78773</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7112,37 +7112,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>476822</v>
+        <v>476826</v>
       </c>
       <c r="R64" t="n">
-        <v>6854551</v>
+        <v>6854459</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7169,9 +7169,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7186,60 +7196,68 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127371302</v>
+        <v>127386308</v>
       </c>
       <c r="B65" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476826</v>
+        <v>476825</v>
       </c>
       <c r="R65" t="n">
-        <v>6854459</v>
+        <v>6854551</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7266,46 +7284,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386308</v>
+        <v>127386110</v>
       </c>
       <c r="B66" t="n">
         <v>98443</v>
@@ -7333,28 +7342,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476825</v>
+        <v>476818</v>
       </c>
       <c r="R66" t="n">
-        <v>6854551</v>
+        <v>6854660</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7392,26 +7393,25 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386110</v>
+        <v>127386842</v>
       </c>
       <c r="B67" t="n">
         <v>98443</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476818</v>
+        <v>476869</v>
       </c>
       <c r="R67" t="n">
-        <v>6854660</v>
+        <v>6854655</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7496,19 +7496,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386842</v>
+        <v>127386096</v>
       </c>
       <c r="B68" t="n">
         <v>98443</v>
@@ -7536,20 +7536,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476869</v>
+        <v>476806</v>
       </c>
       <c r="R68" t="n">
-        <v>6854655</v>
+        <v>6854483</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7587,67 +7591,64 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127386096</v>
+        <v>127386068</v>
       </c>
       <c r="B69" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476806</v>
+        <v>476822</v>
       </c>
       <c r="R69" t="n">
-        <v>6854483</v>
+        <v>6854551</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7688,7 +7689,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8645,10 +8645,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127386820</v>
+        <v>127369660</v>
       </c>
       <c r="B79" t="n">
-        <v>92608</v>
+        <v>96696</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8656,37 +8656,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4361</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476882</v>
+        <v>476880</v>
       </c>
       <c r="R79" t="n">
-        <v>6854669</v>
+        <v>6854794</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8713,9 +8713,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8730,57 +8740,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127386082</v>
+        <v>127369891</v>
       </c>
       <c r="B80" t="n">
-        <v>78773</v>
+        <v>80152</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476804</v>
+        <v>476866</v>
       </c>
       <c r="R80" t="n">
-        <v>6854643</v>
+        <v>6854642</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8810,9 +8820,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8827,22 +8847,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127369660</v>
+        <v>127386820</v>
       </c>
       <c r="B81" t="n">
-        <v>96696</v>
+        <v>92608</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8850,37 +8870,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476880</v>
+        <v>476882</v>
       </c>
       <c r="R81" t="n">
-        <v>6854794</v>
+        <v>6854669</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8907,19 +8927,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8934,57 +8944,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127369891</v>
+        <v>127386082</v>
       </c>
       <c r="B82" t="n">
-        <v>80152</v>
+        <v>78773</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476866</v>
+        <v>476804</v>
       </c>
       <c r="R82" t="n">
-        <v>6854642</v>
+        <v>6854643</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9014,19 +9024,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9041,12 +9041,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127369923</v>
+        <v>127386081</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>78777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>476867</v>
       </c>
       <c r="R2" t="n">
-        <v>6854642</v>
+        <v>6854478</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +775,7 @@
         <v>127371169</v>
       </c>
       <c r="B3" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,56 +879,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127386314</v>
+        <v>127369923</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>476867</v>
       </c>
       <c r="R4" t="n">
-        <v>6854648</v>
+        <v>6854642</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,78 +947,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127386839</v>
+        <v>127369215</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>78685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476824</v>
+        <v>476907</v>
       </c>
       <c r="R5" t="n">
-        <v>6854630</v>
+        <v>6854785</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,9 +1054,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127386098</v>
+        <v>127386314</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,22 +1123,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476851</v>
+        <v>476867</v>
       </c>
       <c r="R6" t="n">
-        <v>6854670</v>
+        <v>6854648</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,60 +1187,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127369215</v>
+        <v>127386839</v>
       </c>
       <c r="B7" t="n">
-        <v>78681</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476907</v>
+        <v>476824</v>
       </c>
       <c r="R7" t="n">
-        <v>6854785</v>
+        <v>6854630</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1262,19 +1267,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,57 +1284,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127386081</v>
+        <v>127386098</v>
       </c>
       <c r="B8" t="n">
-        <v>78773</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476867</v>
+        <v>476851</v>
       </c>
       <c r="R8" t="n">
-        <v>6854478</v>
+        <v>6854670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,6 +1379,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>127388973</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>127371659</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>127387597</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>127387592</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>127388966</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127388142</v>
+        <v>127386809</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>79050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,45 +1945,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476840</v>
+        <v>476898</v>
       </c>
       <c r="R14" t="n">
-        <v>6854642</v>
+        <v>6854784</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2027,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127386809</v>
+        <v>127386850</v>
       </c>
       <c r="B15" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476898</v>
+        <v>476896</v>
       </c>
       <c r="R15" t="n">
-        <v>6854784</v>
+        <v>6854789</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2136,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127386850</v>
+        <v>127388142</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2147,37 +2139,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476896</v>
+        <v>476840</v>
       </c>
       <c r="R16" t="n">
-        <v>6854789</v>
+        <v>6854642</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2221,61 +2221,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127388963</v>
+        <v>127388145</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476856</v>
+        <v>476840</v>
       </c>
       <c r="R17" t="n">
-        <v>6854653</v>
+        <v>6854642</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2316,29 +2312,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127386305</v>
+        <v>127388963</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,23 +2360,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476855</v>
+        <v>476856</v>
       </c>
       <c r="R18" t="n">
-        <v>6854627</v>
+        <v>6854653</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2429,22 +2420,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127386099</v>
+        <v>127386305</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,22 +2462,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476865</v>
+        <v>476855</v>
       </c>
       <c r="R19" t="n">
-        <v>6854478</v>
+        <v>6854627</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2531,60 +2526,64 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127388145</v>
+        <v>127386099</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476840</v>
+        <v>476865</v>
       </c>
       <c r="R20" t="n">
-        <v>6854642</v>
+        <v>6854478</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2622,18 +2621,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2643,7 +2643,7 @@
         <v>127386067</v>
       </c>
       <c r="B21" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>127386848</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,32 +2835,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127387581</v>
+        <v>127387585</v>
       </c>
       <c r="B23" t="n">
-        <v>97321</v>
+        <v>80121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476827</v>
+        <v>476865</v>
       </c>
       <c r="R23" t="n">
-        <v>6854629</v>
+        <v>6854638</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2932,53 +2932,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127386302</v>
+        <v>127386319</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476828</v>
+        <v>476821</v>
       </c>
       <c r="R24" t="n">
-        <v>6854531</v>
+        <v>6854475</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3019,7 +3011,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3038,56 +3029,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127388976</v>
+        <v>127369424</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476880</v>
+        <v>476879</v>
       </c>
       <c r="R25" t="n">
-        <v>6854486</v>
+        <v>6854650</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3114,40 +3097,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127386102</v>
+        <v>127386302</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,22 +3166,26 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476821</v>
+        <v>476828</v>
       </c>
       <c r="R26" t="n">
-        <v>6854465</v>
+        <v>6854531</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3234,57 +3230,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127386319</v>
+        <v>127388976</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476821</v>
+        <v>476880</v>
       </c>
       <c r="R27" t="n">
-        <v>6854475</v>
+        <v>6854486</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3325,63 +3329,68 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127369424</v>
+        <v>127386102</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476879</v>
+        <v>476821</v>
       </c>
       <c r="R28" t="n">
-        <v>6854650</v>
+        <v>6854465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3411,71 +3420,62 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127387585</v>
+        <v>127387581</v>
       </c>
       <c r="B29" t="n">
-        <v>80117</v>
+        <v>97325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476865</v>
+        <v>476827</v>
       </c>
       <c r="R29" t="n">
-        <v>6854638</v>
+        <v>6854629</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3547,48 +3547,55 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127386111</v>
+        <v>127386295</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476831</v>
+        <v>476888</v>
       </c>
       <c r="R30" t="n">
-        <v>6854682</v>
+        <v>6854664</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3626,71 +3633,64 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127386303</v>
+        <v>127371357</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476836</v>
+        <v>476901</v>
       </c>
       <c r="R31" t="n">
-        <v>6854627</v>
+        <v>6854667</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -3720,78 +3720,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127386112</v>
+        <v>127370759</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>80156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476873</v>
+        <v>476877</v>
       </c>
       <c r="R32" t="n">
-        <v>6854658</v>
+        <v>6854663</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3818,9 +3827,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3835,22 +3854,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127386100</v>
+        <v>127386111</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3875,21 +3894,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476829</v>
+        <v>476831</v>
       </c>
       <c r="R33" t="n">
-        <v>6854465</v>
+        <v>6854682</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3930,7 +3945,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3949,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127386299</v>
+        <v>127386100</v>
       </c>
       <c r="B34" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3979,26 +3993,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476817</v>
+        <v>476829</v>
       </c>
       <c r="R34" t="n">
         <v>6854465</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4043,53 +4053,54 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127386295</v>
+        <v>127386299</v>
       </c>
       <c r="B35" t="n">
-        <v>91346</v>
+        <v>98447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4097,10 +4108,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476888</v>
+        <v>476817</v>
       </c>
       <c r="R35" t="n">
-        <v>6854664</v>
+        <v>6854465</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4160,45 +4171,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127371357</v>
+        <v>127386303</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476901</v>
+        <v>476836</v>
       </c>
       <c r="R36" t="n">
-        <v>6854667</v>
+        <v>6854627</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4228,87 +4247,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127370759</v>
+        <v>127386112</v>
       </c>
       <c r="B37" t="n">
-        <v>80152</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476877</v>
+        <v>476873</v>
       </c>
       <c r="R37" t="n">
-        <v>6854663</v>
+        <v>6854658</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4335,19 +4345,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4362,12 +4362,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4377,7 +4377,7 @@
         <v>127386117</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>127386108</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>127387587</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>127386311</v>
       </c>
       <c r="B41" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>127387586</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>127369992</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>127388975</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>127386808</v>
       </c>
       <c r="B45" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>127386078</v>
       </c>
       <c r="B46" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5294,45 +5294,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127370572</v>
+        <v>127386312</v>
       </c>
       <c r="B47" t="n">
-        <v>96696</v>
+        <v>98447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476857</v>
+        <v>476860</v>
       </c>
       <c r="R47" t="n">
-        <v>6854654</v>
+        <v>6854625</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5362,19 +5362,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5389,60 +5379,72 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127386087</v>
+        <v>127387598</v>
       </c>
       <c r="B48" t="n">
-        <v>78772</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476780</v>
+        <v>476767</v>
       </c>
       <c r="R48" t="n">
-        <v>6854482</v>
+        <v>6854589</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5480,50 +5482,51 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127386089</v>
+        <v>127386838</v>
       </c>
       <c r="B49" t="n">
-        <v>78772</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,13 +5536,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476838</v>
+        <v>476819</v>
       </c>
       <c r="R49" t="n">
-        <v>6854681</v>
+        <v>6854632</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5583,22 +5586,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127371346</v>
+        <v>127386089</v>
       </c>
       <c r="B50" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5626,17 +5629,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476826</v>
+        <v>476838</v>
       </c>
       <c r="R50" t="n">
-        <v>6854459</v>
+        <v>6854681</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5663,19 +5666,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5690,22 +5683,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127371200</v>
+        <v>127386087</v>
       </c>
       <c r="B51" t="n">
-        <v>92608</v>
+        <v>78776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,37 +5706,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476901</v>
+        <v>476780</v>
       </c>
       <c r="R51" t="n">
-        <v>6854667</v>
+        <v>6854482</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5770,19 +5763,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5797,60 +5780,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386312</v>
+        <v>127371346</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>78776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476860</v>
+        <v>476826</v>
       </c>
       <c r="R52" t="n">
-        <v>6854625</v>
+        <v>6854459</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5877,9 +5860,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5894,72 +5887,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127387598</v>
+        <v>127370572</v>
       </c>
       <c r="B53" t="n">
-        <v>98443</v>
+        <v>96700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476767</v>
+        <v>476857</v>
       </c>
       <c r="R53" t="n">
-        <v>6854589</v>
+        <v>6854654</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5986,78 +5967,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127386838</v>
+        <v>127371200</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>92612</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476819</v>
+        <v>476901</v>
       </c>
       <c r="R54" t="n">
-        <v>6854632</v>
+        <v>6854667</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6084,9 +6074,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6101,62 +6101,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127372315</v>
+        <v>127370418</v>
       </c>
       <c r="B55" t="n">
-        <v>56849</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476894</v>
+        <v>476867</v>
       </c>
       <c r="R55" t="n">
-        <v>6854772</v>
+        <v>6854691</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6188,7 +6183,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6198,7 +6193,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6225,45 +6220,52 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127370418</v>
+        <v>127388147</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476867</v>
+        <v>476787</v>
       </c>
       <c r="R56" t="n">
-        <v>6854691</v>
+        <v>6854642</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6293,49 +6295,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127388147</v>
+        <v>127372315</v>
       </c>
       <c r="B57" t="n">
-        <v>92616</v>
+        <v>56853</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6343,41 +6336,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476787</v>
+        <v>476894</v>
       </c>
       <c r="R57" t="n">
-        <v>6854642</v>
+        <v>6854772</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6407,90 +6398,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127387593</v>
+        <v>127386849</v>
       </c>
       <c r="B58" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>476780</v>
+        <v>476891</v>
       </c>
       <c r="R58" t="n">
-        <v>6854617</v>
+        <v>6854776</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6522,40 +6510,34 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127387589</v>
+        <v>127387593</v>
       </c>
       <c r="B59" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6582,7 +6564,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6599,10 +6581,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476812</v>
+        <v>476780</v>
       </c>
       <c r="R59" t="n">
-        <v>6854623</v>
+        <v>6854617</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6667,10 +6649,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127386313</v>
+        <v>127387589</v>
       </c>
       <c r="B60" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6697,10 +6679,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -6710,13 +6696,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476881</v>
+        <v>476812</v>
       </c>
       <c r="R60" t="n">
-        <v>6854650</v>
+        <v>6854623</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6746,6 +6732,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6761,22 +6752,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127371630</v>
+        <v>127386313</v>
       </c>
       <c r="B61" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6803,27 +6794,26 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476874</v>
+        <v>476881</v>
       </c>
       <c r="R61" t="n">
-        <v>6854475</v>
+        <v>6854650</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6850,49 +6840,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127387590</v>
+        <v>127371630</v>
       </c>
       <c r="B62" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6919,30 +6900,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476860</v>
+        <v>476874</v>
       </c>
       <c r="R62" t="n">
-        <v>6854552</v>
+        <v>6854475</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6969,14 +6947,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>4 blommande stänglar</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6985,67 +6968,78 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127386849</v>
+        <v>127387590</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>476891</v>
+        <v>476860</v>
       </c>
       <c r="R63" t="n">
-        <v>6854776</v>
+        <v>6854552</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7077,24 +7071,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>4 blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7104,7 +7104,7 @@
         <v>127371302</v>
       </c>
       <c r="B64" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7208,56 +7208,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127386308</v>
+        <v>127386068</v>
       </c>
       <c r="B65" t="n">
-        <v>98443</v>
+        <v>79050</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476825</v>
+        <v>476822</v>
       </c>
       <c r="R65" t="n">
         <v>6854551</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7295,29 +7287,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386110</v>
+        <v>127386308</v>
       </c>
       <c r="B66" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7342,20 +7333,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476818</v>
+        <v>476825</v>
       </c>
       <c r="R66" t="n">
-        <v>6854660</v>
+        <v>6854551</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7393,28 +7392,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386842</v>
+        <v>127386110</v>
       </c>
       <c r="B67" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476869</v>
+        <v>476818</v>
       </c>
       <c r="R67" t="n">
-        <v>6854655</v>
+        <v>6854660</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7496,22 +7496,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386096</v>
+        <v>127386842</v>
       </c>
       <c r="B68" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7536,24 +7536,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476806</v>
+        <v>476869</v>
       </c>
       <c r="R68" t="n">
-        <v>6854483</v>
+        <v>6854655</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7591,64 +7587,67 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127386068</v>
+        <v>127386096</v>
       </c>
       <c r="B69" t="n">
-        <v>79046</v>
+        <v>98447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476822</v>
+        <v>476806</v>
       </c>
       <c r="R69" t="n">
-        <v>6854551</v>
+        <v>6854483</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7689,6 +7688,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>127388970</v>
       </c>
       <c r="B70" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>127387596</v>
       </c>
       <c r="B71" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>127371242</v>
       </c>
       <c r="B72" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>127386109</v>
       </c>
       <c r="B73" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8127,48 +8127,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127369233</v>
+        <v>127386841</v>
       </c>
       <c r="B74" t="n">
-        <v>79046</v>
+        <v>98447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>476907</v>
+        <v>476865</v>
       </c>
       <c r="R74" t="n">
-        <v>6854785</v>
+        <v>6854629</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8195,19 +8195,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8222,22 +8212,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127386841</v>
+        <v>127388972</v>
       </c>
       <c r="B75" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8262,20 +8252,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476865</v>
+        <v>476809</v>
       </c>
       <c r="R75" t="n">
-        <v>6854629</v>
+        <v>6854638</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8313,28 +8307,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127388972</v>
+        <v>127387595</v>
       </c>
       <c r="B76" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8361,22 +8356,30 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476809</v>
+        <v>476804</v>
       </c>
       <c r="R76" t="n">
-        <v>6854638</v>
+        <v>6854628</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8421,22 +8424,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127387595</v>
+        <v>127386097</v>
       </c>
       <c r="B77" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8463,30 +8466,22 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476804</v>
+        <v>476794</v>
       </c>
       <c r="R77" t="n">
-        <v>6854628</v>
+        <v>6854562</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8531,64 +8526,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127386097</v>
+        <v>127369233</v>
       </c>
       <c r="B78" t="n">
-        <v>98443</v>
+        <v>79050</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476794</v>
+        <v>476907</v>
       </c>
       <c r="R78" t="n">
-        <v>6854562</v>
+        <v>6854785</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8615,30 +8606,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8648,7 +8648,7 @@
         <v>127369660</v>
       </c>
       <c r="B79" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8752,48 +8752,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127369891</v>
+        <v>127386820</v>
       </c>
       <c r="B80" t="n">
-        <v>80152</v>
+        <v>92612</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>4361</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476866</v>
+        <v>476882</v>
       </c>
       <c r="R80" t="n">
-        <v>6854642</v>
+        <v>6854669</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8820,19 +8820,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8847,60 +8837,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127386820</v>
+        <v>127369891</v>
       </c>
       <c r="B81" t="n">
-        <v>92608</v>
+        <v>80156</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476882</v>
+        <v>476866</v>
       </c>
       <c r="R81" t="n">
-        <v>6854669</v>
+        <v>6854642</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8927,9 +8917,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8944,60 +8944,68 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386082</v>
+        <v>127386315</v>
       </c>
       <c r="B82" t="n">
-        <v>78773</v>
+        <v>98447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476804</v>
+        <v>476883</v>
       </c>
       <c r="R82" t="n">
-        <v>6854643</v>
+        <v>6854657</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9035,28 +9043,29 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386315</v>
+        <v>127386103</v>
       </c>
       <c r="B83" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9083,26 +9092,22 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476883</v>
+        <v>476832</v>
       </c>
       <c r="R83" t="n">
-        <v>6854657</v>
+        <v>6854485</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9147,22 +9152,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386103</v>
+        <v>127386300</v>
       </c>
       <c r="B84" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9189,22 +9194,26 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476832</v>
+        <v>476830</v>
       </c>
       <c r="R84" t="n">
-        <v>6854485</v>
+        <v>6854480</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9249,22 +9258,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127386300</v>
+        <v>127386843</v>
       </c>
       <c r="B85" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9289,28 +9298,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476830</v>
+        <v>476842</v>
       </c>
       <c r="R85" t="n">
-        <v>6854480</v>
+        <v>6854652</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9348,64 +9349,66 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386843</v>
+        <v>127386834</v>
       </c>
       <c r="B86" t="n">
-        <v>98443</v>
+        <v>80081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476842</v>
+        <v>476869</v>
       </c>
       <c r="R86" t="n">
-        <v>6854652</v>
+        <v>6854645</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9446,6 +9449,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9457,58 +9461,55 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127386834</v>
+        <v>127386082</v>
       </c>
       <c r="B87" t="n">
-        <v>80077</v>
+        <v>78777</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476869</v>
+        <v>476804</v>
       </c>
       <c r="R87" t="n">
-        <v>6854645</v>
+        <v>6854643</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9546,51 +9547,50 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127386828</v>
+        <v>127386129</v>
       </c>
       <c r="B88" t="n">
-        <v>80117</v>
+        <v>92620</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476869</v>
+        <v>476790</v>
       </c>
       <c r="R88" t="n">
-        <v>6854645</v>
+        <v>6854633</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9650,44 +9650,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386080</v>
+        <v>127386828</v>
       </c>
       <c r="B89" t="n">
-        <v>92628</v>
+        <v>80121</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9697,13 +9697,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476799</v>
+        <v>476869</v>
       </c>
       <c r="R89" t="n">
-        <v>6854562</v>
+        <v>6854645</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9747,22 +9747,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127386129</v>
+        <v>127386080</v>
       </c>
       <c r="B90" t="n">
-        <v>92616</v>
+        <v>92632</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9770,21 +9770,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9794,10 +9794,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476790</v>
+        <v>476799</v>
       </c>
       <c r="R90" t="n">
-        <v>6854633</v>
+        <v>6854562</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9856,10 +9856,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127388974</v>
+        <v>127386840</v>
       </c>
       <c r="B91" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9886,22 +9886,30 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476859</v>
+        <v>476852</v>
       </c>
       <c r="R91" t="n">
-        <v>6854547</v>
+        <v>6854630</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9946,22 +9954,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127386840</v>
+        <v>127388974</v>
       </c>
       <c r="B92" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9988,30 +9996,22 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476852</v>
+        <v>476859</v>
       </c>
       <c r="R92" t="n">
-        <v>6854630</v>
+        <v>6854547</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10056,60 +10056,64 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127386320</v>
+        <v>127386101</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>476832</v>
+        <v>476785</v>
       </c>
       <c r="R93" t="n">
-        <v>6854631</v>
+        <v>6854487</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10147,28 +10151,29 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127386101</v>
+        <v>127386837</v>
       </c>
       <c r="B94" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10193,24 +10198,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>476785</v>
+        <v>476808</v>
       </c>
       <c r="R94" t="n">
-        <v>6854487</v>
+        <v>6854629</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10248,51 +10249,50 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127386837</v>
+        <v>127386320</v>
       </c>
       <c r="B95" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10302,13 +10302,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>476808</v>
+        <v>476832</v>
       </c>
       <c r="R95" t="n">
-        <v>6854629</v>
+        <v>6854631</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10352,12 +10352,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10367,7 +10367,7 @@
         <v>127388141</v>
       </c>
       <c r="B96" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>127370318</v>
       </c>
       <c r="B97" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>127386104</v>
       </c>
       <c r="B98" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>127386107</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>127386854</v>
       </c>
       <c r="B100" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10877,10 +10877,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127386811</v>
+        <v>127386088</v>
       </c>
       <c r="B101" t="n">
-        <v>79603</v>
+        <v>78776</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10888,21 +10888,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10912,13 +10912,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476887</v>
+        <v>476826</v>
       </c>
       <c r="R101" t="n">
-        <v>6854810</v>
+        <v>6854482</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10962,60 +10962,68 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127386088</v>
+        <v>127386310</v>
       </c>
       <c r="B102" t="n">
-        <v>78772</v>
+        <v>98447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>476826</v>
+        <v>476822</v>
       </c>
       <c r="R102" t="n">
-        <v>6854482</v>
+        <v>6854557</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11053,28 +11061,29 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127386310</v>
+        <v>127388967</v>
       </c>
       <c r="B103" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11101,23 +11110,19 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>476822</v>
+        <v>476843</v>
       </c>
       <c r="R103" t="n">
-        <v>6854557</v>
+        <v>6854525</v>
       </c>
       <c r="S103" t="n">
         <v>4</v>
@@ -11165,22 +11170,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127388967</v>
+        <v>127387594</v>
       </c>
       <c r="B104" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11207,22 +11212,30 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>476843</v>
+        <v>476850</v>
       </c>
       <c r="R104" t="n">
-        <v>6854525</v>
+        <v>6854546</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11267,72 +11280,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127387594</v>
+        <v>127386811</v>
       </c>
       <c r="B105" t="n">
-        <v>98443</v>
+        <v>79607</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>476850</v>
+        <v>476887</v>
       </c>
       <c r="R105" t="n">
-        <v>6854546</v>
+        <v>6854810</v>
       </c>
       <c r="S105" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11370,19 +11371,18 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127386081</v>
+        <v>127369215</v>
       </c>
       <c r="B2" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476867</v>
+        <v>476907</v>
       </c>
       <c r="R2" t="n">
-        <v>6854478</v>
+        <v>6854785</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +743,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -879,48 +889,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127369923</v>
+        <v>127386314</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>476867</v>
       </c>
       <c r="R4" t="n">
-        <v>6854642</v>
+        <v>6854648</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,87 +965,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127369215</v>
+        <v>127386839</v>
       </c>
       <c r="B5" t="n">
-        <v>78685</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476907</v>
+        <v>476824</v>
       </c>
       <c r="R5" t="n">
-        <v>6854785</v>
+        <v>6854630</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,19 +1063,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,19 +1080,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127386314</v>
+        <v>127386098</v>
       </c>
       <c r="B6" t="n">
         <v>98447</v>
@@ -1123,26 +1122,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476867</v>
+        <v>476851</v>
       </c>
       <c r="R6" t="n">
-        <v>6854648</v>
+        <v>6854670</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,60 +1182,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127386839</v>
+        <v>127369923</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476824</v>
+        <v>476867</v>
       </c>
       <c r="R7" t="n">
-        <v>6854630</v>
+        <v>6854642</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1267,9 +1262,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,61 +1289,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127386098</v>
+        <v>127386081</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476851</v>
+        <v>476867</v>
       </c>
       <c r="R8" t="n">
-        <v>6854670</v>
+        <v>6854478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,7 +1380,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1398,52 +1398,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127388973</v>
+        <v>127386809</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476828</v>
+        <v>476898</v>
       </c>
       <c r="R9" t="n">
-        <v>6854626</v>
+        <v>6854784</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1481,67 +1477,66 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127371659</v>
+        <v>127386850</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476822</v>
+        <v>476896</v>
       </c>
       <c r="R10" t="n">
-        <v>6854617</v>
+        <v>6854789</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1568,19 +1563,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,72 +1580,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127387597</v>
+        <v>127388142</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476831</v>
+        <v>476840</v>
       </c>
       <c r="R11" t="n">
-        <v>6854622</v>
+        <v>6854642</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1698,26 +1679,25 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127387592</v>
+        <v>127388973</v>
       </c>
       <c r="B12" t="n">
         <v>98447</v>
@@ -1747,30 +1727,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476796</v>
+        <v>476828</v>
       </c>
       <c r="R12" t="n">
-        <v>6854627</v>
+        <v>6854626</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1800,11 +1772,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,19 +1787,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127388966</v>
+        <v>127371659</v>
       </c>
       <c r="B13" t="n">
         <v>98447</v>
@@ -1860,21 +1827,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476792</v>
+        <v>476822</v>
       </c>
       <c r="R13" t="n">
-        <v>6854646</v>
+        <v>6854617</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1904,78 +1867,99 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127386809</v>
+        <v>127387597</v>
       </c>
       <c r="B14" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476898</v>
+        <v>476831</v>
       </c>
       <c r="R14" t="n">
-        <v>6854784</v>
+        <v>6854622</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2013,66 +1997,79 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127386850</v>
+        <v>127387592</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476896</v>
+        <v>476796</v>
       </c>
       <c r="R15" t="n">
-        <v>6854789</v>
+        <v>6854627</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2104,77 +2101,79 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127388142</v>
+        <v>127388966</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476840</v>
+        <v>476792</v>
       </c>
       <c r="R16" t="n">
-        <v>6854642</v>
+        <v>6854646</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2215,18 +2214,19 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127387585</v>
+        <v>127386319</v>
       </c>
       <c r="B23" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476865</v>
+        <v>476821</v>
       </c>
       <c r="R23" t="n">
-        <v>6854638</v>
+        <v>6854475</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2920,60 +2920,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127386319</v>
+        <v>127369424</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476821</v>
+        <v>476879</v>
       </c>
       <c r="R24" t="n">
-        <v>6854475</v>
+        <v>6854650</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3000,9 +3000,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3017,60 +3027,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127369424</v>
+        <v>127387585</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476879</v>
+        <v>476865</v>
       </c>
       <c r="R25" t="n">
-        <v>6854650</v>
+        <v>6854638</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3097,19 +3107,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3124,12 +3124,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127386808</v>
+        <v>127386078</v>
       </c>
       <c r="B45" t="n">
-        <v>79050</v>
+        <v>98468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476882</v>
+        <v>476854</v>
       </c>
       <c r="R45" t="n">
-        <v>6854781</v>
+        <v>6854673</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5185,44 +5185,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127386078</v>
+        <v>127386808</v>
       </c>
       <c r="B46" t="n">
-        <v>98468</v>
+        <v>79050</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5232,13 +5232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476854</v>
+        <v>476882</v>
       </c>
       <c r="R46" t="n">
-        <v>6854673</v>
+        <v>6854781</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5282,57 +5282,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127386312</v>
+        <v>127371200</v>
       </c>
       <c r="B47" t="n">
-        <v>98447</v>
+        <v>92612</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476860</v>
+        <v>476901</v>
       </c>
       <c r="R47" t="n">
-        <v>6854625</v>
+        <v>6854667</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5362,9 +5362,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5379,19 +5389,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127387598</v>
+        <v>127386312</v>
       </c>
       <c r="B48" t="n">
         <v>98447</v>
@@ -5419,32 +5429,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476767</v>
+        <v>476860</v>
       </c>
       <c r="R48" t="n">
-        <v>6854589</v>
+        <v>6854625</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5482,26 +5480,25 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127386838</v>
+        <v>127387598</v>
       </c>
       <c r="B49" t="n">
         <v>98447</v>
@@ -5529,20 +5526,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476819</v>
+        <v>476767</v>
       </c>
       <c r="R49" t="n">
-        <v>6854632</v>
+        <v>6854589</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5580,50 +5589,51 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127386089</v>
+        <v>127386838</v>
       </c>
       <c r="B50" t="n">
-        <v>78776</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5633,13 +5643,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476838</v>
+        <v>476819</v>
       </c>
       <c r="R50" t="n">
-        <v>6854681</v>
+        <v>6854632</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5683,22 +5693,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127386087</v>
+        <v>127370572</v>
       </c>
       <c r="B51" t="n">
-        <v>78776</v>
+        <v>96700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5706,37 +5716,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476780</v>
+        <v>476857</v>
       </c>
       <c r="R51" t="n">
-        <v>6854482</v>
+        <v>6854654</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5763,9 +5773,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5780,19 +5800,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127371346</v>
+        <v>127386087</v>
       </c>
       <c r="B52" t="n">
         <v>78776</v>
@@ -5823,17 +5843,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476826</v>
+        <v>476780</v>
       </c>
       <c r="R52" t="n">
-        <v>6854459</v>
+        <v>6854482</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5860,19 +5880,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5887,22 +5897,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127370572</v>
+        <v>127386089</v>
       </c>
       <c r="B53" t="n">
-        <v>96700</v>
+        <v>78776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5910,37 +5920,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476857</v>
+        <v>476838</v>
       </c>
       <c r="R53" t="n">
-        <v>6854654</v>
+        <v>6854681</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5967,19 +5977,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5994,22 +5994,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127371200</v>
+        <v>127371346</v>
       </c>
       <c r="B54" t="n">
-        <v>92612</v>
+        <v>78776</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6017,21 +6017,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6041,13 +6041,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476901</v>
+        <v>476826</v>
       </c>
       <c r="R54" t="n">
-        <v>6854667</v>
+        <v>6854459</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6101,57 +6101,64 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127370418</v>
+        <v>127388147</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476867</v>
+        <v>476787</v>
       </c>
       <c r="R55" t="n">
-        <v>6854691</v>
+        <v>6854642</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6181,91 +6188,75 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127388147</v>
+        <v>127370418</v>
       </c>
       <c r="B56" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476787</v>
+        <v>476867</v>
       </c>
       <c r="R56" t="n">
-        <v>6854642</v>
+        <v>6854691</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6295,30 +6286,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7101,48 +7101,56 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127371302</v>
+        <v>127386308</v>
       </c>
       <c r="B64" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>476826</v>
+        <v>476825</v>
       </c>
       <c r="R64" t="n">
-        <v>6854459</v>
+        <v>6854551</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7169,71 +7177,62 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127386068</v>
+        <v>127386110</v>
       </c>
       <c r="B65" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7243,10 +7242,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476822</v>
+        <v>476818</v>
       </c>
       <c r="R65" t="n">
-        <v>6854551</v>
+        <v>6854660</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7305,7 +7304,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386308</v>
+        <v>127386842</v>
       </c>
       <c r="B66" t="n">
         <v>98447</v>
@@ -7333,28 +7332,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476825</v>
+        <v>476869</v>
       </c>
       <c r="R66" t="n">
-        <v>6854551</v>
+        <v>6854655</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7392,26 +7383,25 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386110</v>
+        <v>127386096</v>
       </c>
       <c r="B67" t="n">
         <v>98447</v>
@@ -7439,17 +7429,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476818</v>
+        <v>476806</v>
       </c>
       <c r="R67" t="n">
-        <v>6854660</v>
+        <v>6854483</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7490,6 +7484,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7508,48 +7503,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386842</v>
+        <v>127371302</v>
       </c>
       <c r="B68" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476869</v>
+        <v>476826</v>
       </c>
       <c r="R68" t="n">
-        <v>6854655</v>
+        <v>6854459</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7576,9 +7571,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7593,61 +7598,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127386096</v>
+        <v>127386068</v>
       </c>
       <c r="B69" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476806</v>
+        <v>476822</v>
       </c>
       <c r="R69" t="n">
-        <v>6854483</v>
+        <v>6854551</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7688,7 +7689,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8127,48 +8127,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127386841</v>
+        <v>127369233</v>
       </c>
       <c r="B74" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>476865</v>
+        <v>476907</v>
       </c>
       <c r="R74" t="n">
-        <v>6854629</v>
+        <v>6854785</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8195,9 +8195,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8212,19 +8222,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127388972</v>
+        <v>127386841</v>
       </c>
       <c r="B75" t="n">
         <v>98447</v>
@@ -8252,24 +8262,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476809</v>
+        <v>476865</v>
       </c>
       <c r="R75" t="n">
-        <v>6854638</v>
+        <v>6854629</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8307,26 +8313,25 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127387595</v>
+        <v>127388972</v>
       </c>
       <c r="B76" t="n">
         <v>98447</v>
@@ -8356,30 +8361,22 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476804</v>
+        <v>476809</v>
       </c>
       <c r="R76" t="n">
-        <v>6854628</v>
+        <v>6854638</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8424,19 +8421,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127386097</v>
+        <v>127387595</v>
       </c>
       <c r="B77" t="n">
         <v>98447</v>
@@ -8466,22 +8463,30 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476794</v>
+        <v>476804</v>
       </c>
       <c r="R77" t="n">
-        <v>6854562</v>
+        <v>6854628</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8526,60 +8531,64 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127369233</v>
+        <v>127386097</v>
       </c>
       <c r="B78" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476907</v>
+        <v>476794</v>
       </c>
       <c r="R78" t="n">
-        <v>6854785</v>
+        <v>6854562</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8606,39 +8615,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8752,48 +8752,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127386820</v>
+        <v>127369891</v>
       </c>
       <c r="B80" t="n">
-        <v>92612</v>
+        <v>80156</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476882</v>
+        <v>476866</v>
       </c>
       <c r="R80" t="n">
-        <v>6854669</v>
+        <v>6854642</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8820,9 +8820,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8837,60 +8847,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127369891</v>
+        <v>127386820</v>
       </c>
       <c r="B81" t="n">
-        <v>80156</v>
+        <v>92612</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476866</v>
+        <v>476882</v>
       </c>
       <c r="R81" t="n">
-        <v>6854642</v>
+        <v>6854669</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8917,19 +8927,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8944,12 +8944,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9367,51 +9367,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386834</v>
+        <v>127386082</v>
       </c>
       <c r="B86" t="n">
-        <v>80081</v>
+        <v>78777</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476869</v>
+        <v>476804</v>
       </c>
       <c r="R86" t="n">
-        <v>6854645</v>
+        <v>6854643</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9449,67 +9446,69 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127386082</v>
+        <v>127386834</v>
       </c>
       <c r="B87" t="n">
-        <v>78777</v>
+        <v>80081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476804</v>
+        <v>476869</v>
       </c>
       <c r="R87" t="n">
-        <v>6854643</v>
+        <v>6854645</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9547,66 +9546,71 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127386129</v>
+        <v>127388974</v>
       </c>
       <c r="B88" t="n">
-        <v>92620</v>
+        <v>98447</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476790</v>
+        <v>476859</v>
       </c>
       <c r="R88" t="n">
-        <v>6854633</v>
+        <v>6854547</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9644,63 +9648,76 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386828</v>
+        <v>127386840</v>
       </c>
       <c r="B89" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476869</v>
+        <v>476852</v>
       </c>
       <c r="R89" t="n">
-        <v>6854645</v>
+        <v>6854630</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9741,6 +9758,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9856,60 +9874,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127386840</v>
+        <v>127386129</v>
       </c>
       <c r="B91" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476852</v>
+        <v>476790</v>
       </c>
       <c r="R91" t="n">
-        <v>6854630</v>
+        <v>6854633</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9947,71 +9953,66 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127388974</v>
+        <v>127386828</v>
       </c>
       <c r="B92" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476859</v>
+        <v>476869</v>
       </c>
       <c r="R92" t="n">
-        <v>6854547</v>
+        <v>6854645</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10049,71 +10050,66 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127386101</v>
+        <v>127386320</v>
       </c>
       <c r="B93" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>476785</v>
+        <v>476832</v>
       </c>
       <c r="R93" t="n">
-        <v>6854487</v>
+        <v>6854631</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10151,26 +10147,25 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127386837</v>
+        <v>127386101</v>
       </c>
       <c r="B94" t="n">
         <v>98447</v>
@@ -10198,20 +10193,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>476808</v>
+        <v>476785</v>
       </c>
       <c r="R94" t="n">
-        <v>6854629</v>
+        <v>6854487</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10249,50 +10248,51 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127386320</v>
+        <v>127386837</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10302,13 +10302,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>476832</v>
+        <v>476808</v>
       </c>
       <c r="R95" t="n">
-        <v>6854631</v>
+        <v>6854629</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10352,22 +10352,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127388141</v>
+        <v>127370318</v>
       </c>
       <c r="B96" t="n">
-        <v>57658</v>
+        <v>80121</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10375,45 +10375,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476834</v>
+        <v>476810</v>
       </c>
       <c r="R96" t="n">
-        <v>6854535</v>
+        <v>6854587</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10440,9 +10432,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10457,57 +10459,61 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Filippa Paperin, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127370318</v>
+        <v>127386104</v>
       </c>
       <c r="B97" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476810</v>
+        <v>476865</v>
       </c>
       <c r="R97" t="n">
-        <v>6854587</v>
+        <v>6854661</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10537,46 +10543,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127386104</v>
+        <v>127386107</v>
       </c>
       <c r="B98" t="n">
         <v>98447</v>
@@ -10606,7 +10603,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -10615,10 +10612,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>476865</v>
+        <v>476800</v>
       </c>
       <c r="R98" t="n">
-        <v>6854661</v>
+        <v>6854551</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10678,52 +10675,56 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127386107</v>
+        <v>127388141</v>
       </c>
       <c r="B99" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476800</v>
+        <v>476834</v>
       </c>
       <c r="R99" t="n">
-        <v>6854551</v>
+        <v>6854535</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10761,19 +10762,18 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -3652,48 +3652,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127371357</v>
+        <v>127386111</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476901</v>
+        <v>476831</v>
       </c>
       <c r="R31" t="n">
-        <v>6854667</v>
+        <v>6854682</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3720,19 +3720,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3747,60 +3737,64 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127370759</v>
+        <v>127386100</v>
       </c>
       <c r="B32" t="n">
-        <v>80156</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476877</v>
+        <v>476829</v>
       </c>
       <c r="R32" t="n">
-        <v>6854663</v>
+        <v>6854465</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3827,46 +3821,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127386111</v>
+        <v>127386299</v>
       </c>
       <c r="B33" t="n">
         <v>98447</v>
@@ -3894,20 +3879,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476831</v>
+        <v>476817</v>
       </c>
       <c r="R33" t="n">
-        <v>6854682</v>
+        <v>6854465</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3945,25 +3938,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127386100</v>
+        <v>127386303</v>
       </c>
       <c r="B34" t="n">
         <v>98447</v>
@@ -3993,22 +3987,26 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476829</v>
+        <v>476836</v>
       </c>
       <c r="R34" t="n">
-        <v>6854465</v>
+        <v>6854627</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4053,19 +4051,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127386299</v>
+        <v>127386112</v>
       </c>
       <c r="B35" t="n">
         <v>98447</v>
@@ -4093,28 +4091,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476817</v>
+        <v>476873</v>
       </c>
       <c r="R35" t="n">
-        <v>6854465</v>
+        <v>6854658</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4152,72 +4142,63 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127386303</v>
+        <v>127371357</v>
       </c>
       <c r="B36" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476836</v>
+        <v>476901</v>
       </c>
       <c r="R36" t="n">
-        <v>6854627</v>
+        <v>6854667</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4247,78 +4228,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127386112</v>
+        <v>127370759</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>80156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476873</v>
+        <v>476877</v>
       </c>
       <c r="R37" t="n">
-        <v>6854658</v>
+        <v>6854663</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4345,9 +4335,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4362,44 +4362,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127386117</v>
+        <v>127386108</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476835</v>
+        <v>476830</v>
       </c>
       <c r="R38" t="n">
-        <v>6854539</v>
+        <v>6854468</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4471,7 +4471,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127386108</v>
+        <v>127387587</v>
       </c>
       <c r="B39" t="n">
         <v>98447</v>
@@ -4499,20 +4499,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476830</v>
+        <v>476850</v>
       </c>
       <c r="R39" t="n">
-        <v>6854468</v>
+        <v>6854640</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4550,25 +4562,26 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127387587</v>
+        <v>127386311</v>
       </c>
       <c r="B40" t="n">
         <v>98447</v>
@@ -4601,11 +4614,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4615,13 +4624,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476850</v>
+        <v>476828</v>
       </c>
       <c r="R40" t="n">
-        <v>6854640</v>
+        <v>6854592</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4651,6 +4660,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4666,19 +4680,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127386311</v>
+        <v>127387586</v>
       </c>
       <c r="B41" t="n">
         <v>98447</v>
@@ -4706,28 +4720,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476828</v>
+        <v>476859</v>
       </c>
       <c r="R41" t="n">
-        <v>6854592</v>
+        <v>6854667</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4759,37 +4765,31 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>1 blommande</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127387586</v>
+        <v>127369992</v>
       </c>
       <c r="B42" t="n">
         <v>98447</v>
@@ -4818,19 +4818,24 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
         <v>476859</v>
       </c>
       <c r="R42" t="n">
-        <v>6854667</v>
+        <v>6854645</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4857,9 +4862,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4874,19 +4889,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127369992</v>
+        <v>127388975</v>
       </c>
       <c r="B43" t="n">
         <v>98447</v>
@@ -4914,25 +4929,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476859</v>
+        <v>476864</v>
       </c>
       <c r="R43" t="n">
-        <v>6854645</v>
+        <v>6854487</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4959,91 +4973,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127388975</v>
+        <v>127386117</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476864</v>
+        <v>476835</v>
       </c>
       <c r="R44" t="n">
-        <v>6854487</v>
+        <v>6854539</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5081,51 +5082,50 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127386078</v>
+        <v>127386808</v>
       </c>
       <c r="B45" t="n">
-        <v>98468</v>
+        <v>79050</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476854</v>
+        <v>476882</v>
       </c>
       <c r="R45" t="n">
-        <v>6854673</v>
+        <v>6854781</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5185,44 +5185,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127386808</v>
+        <v>127386078</v>
       </c>
       <c r="B46" t="n">
-        <v>79050</v>
+        <v>98468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5232,13 +5232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476882</v>
+        <v>476854</v>
       </c>
       <c r="R46" t="n">
-        <v>6854781</v>
+        <v>6854673</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5282,22 +5282,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127371200</v>
+        <v>127386087</v>
       </c>
       <c r="B47" t="n">
-        <v>92612</v>
+        <v>78776</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,37 +5305,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476901</v>
+        <v>476780</v>
       </c>
       <c r="R47" t="n">
-        <v>6854667</v>
+        <v>6854482</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5362,19 +5362,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5389,44 +5379,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127386312</v>
+        <v>127386089</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5436,13 +5426,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476860</v>
+        <v>476838</v>
       </c>
       <c r="R48" t="n">
-        <v>6854625</v>
+        <v>6854681</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5486,72 +5476,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127387598</v>
+        <v>127371346</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476767</v>
+        <v>476826</v>
       </c>
       <c r="R49" t="n">
-        <v>6854589</v>
+        <v>6854459</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5578,78 +5556,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127386838</v>
+        <v>127370572</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476819</v>
+        <v>476857</v>
       </c>
       <c r="R50" t="n">
-        <v>6854632</v>
+        <v>6854654</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5676,9 +5663,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5693,22 +5690,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127370572</v>
+        <v>127371200</v>
       </c>
       <c r="B51" t="n">
-        <v>96700</v>
+        <v>92612</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5716,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5740,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476857</v>
+        <v>476901</v>
       </c>
       <c r="R51" t="n">
-        <v>6854654</v>
+        <v>6854667</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -5775,7 +5772,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5785,7 +5782,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5812,32 +5809,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386087</v>
+        <v>127386312</v>
       </c>
       <c r="B52" t="n">
-        <v>78776</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,13 +5844,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476780</v>
+        <v>476860</v>
       </c>
       <c r="R52" t="n">
-        <v>6854482</v>
+        <v>6854625</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5897,60 +5894,72 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127386089</v>
+        <v>127387598</v>
       </c>
       <c r="B53" t="n">
-        <v>78776</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476838</v>
+        <v>476767</v>
       </c>
       <c r="R53" t="n">
-        <v>6854681</v>
+        <v>6854589</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5988,66 +5997,67 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127371346</v>
+        <v>127386838</v>
       </c>
       <c r="B54" t="n">
-        <v>78776</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476826</v>
+        <v>476819</v>
       </c>
       <c r="R54" t="n">
-        <v>6854459</v>
+        <v>6854632</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6074,19 +6084,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6101,12 +6101,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7101,56 +7101,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127386308</v>
+        <v>127386068</v>
       </c>
       <c r="B64" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>476825</v>
+        <v>476822</v>
       </c>
       <c r="R64" t="n">
         <v>6854551</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7188,26 +7180,25 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127386110</v>
+        <v>127386308</v>
       </c>
       <c r="B65" t="n">
         <v>98447</v>
@@ -7235,20 +7226,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476818</v>
+        <v>476825</v>
       </c>
       <c r="R65" t="n">
-        <v>6854660</v>
+        <v>6854551</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7286,25 +7285,26 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386842</v>
+        <v>127386110</v>
       </c>
       <c r="B66" t="n">
         <v>98447</v>
@@ -7339,13 +7339,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476869</v>
+        <v>476818</v>
       </c>
       <c r="R66" t="n">
-        <v>6854655</v>
+        <v>6854660</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7389,19 +7389,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386096</v>
+        <v>127386842</v>
       </c>
       <c r="B67" t="n">
         <v>98447</v>
@@ -7429,24 +7429,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476806</v>
+        <v>476869</v>
       </c>
       <c r="R67" t="n">
-        <v>6854483</v>
+        <v>6854655</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7484,67 +7480,70 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127371302</v>
+        <v>127386096</v>
       </c>
       <c r="B68" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476826</v>
+        <v>476806</v>
       </c>
       <c r="R68" t="n">
-        <v>6854459</v>
+        <v>6854483</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7571,49 +7570,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127386068</v>
+        <v>127371302</v>
       </c>
       <c r="B69" t="n">
-        <v>79050</v>
+        <v>78777</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7621,37 +7611,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476822</v>
+        <v>476826</v>
       </c>
       <c r="R69" t="n">
-        <v>6854551</v>
+        <v>6854459</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7678,9 +7668,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7695,12 +7695,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8645,45 +8645,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127369660</v>
+        <v>127386315</v>
       </c>
       <c r="B79" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476880</v>
+        <v>476883</v>
       </c>
       <c r="R79" t="n">
-        <v>6854794</v>
+        <v>6854657</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8713,84 +8721,79 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127369891</v>
+        <v>127386103</v>
       </c>
       <c r="B80" t="n">
-        <v>80156</v>
+        <v>98447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476866</v>
+        <v>476832</v>
       </c>
       <c r="R80" t="n">
-        <v>6854642</v>
+        <v>6854485</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8820,87 +8823,86 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127386820</v>
+        <v>127386300</v>
       </c>
       <c r="B81" t="n">
-        <v>92612</v>
+        <v>98447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476882</v>
+        <v>476830</v>
       </c>
       <c r="R81" t="n">
-        <v>6854669</v>
+        <v>6854480</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8938,25 +8940,26 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386315</v>
+        <v>127386843</v>
       </c>
       <c r="B82" t="n">
         <v>98447</v>
@@ -8984,28 +8987,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476883</v>
+        <v>476842</v>
       </c>
       <c r="R82" t="n">
-        <v>6854657</v>
+        <v>6854652</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9043,68 +9038,63 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386103</v>
+        <v>127386082</v>
       </c>
       <c r="B83" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476832</v>
+        <v>476804</v>
       </c>
       <c r="R83" t="n">
-        <v>6854485</v>
+        <v>6854643</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9145,7 +9135,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9164,42 +9153,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386300</v>
+        <v>127386834</v>
       </c>
       <c r="B84" t="n">
-        <v>98447</v>
+        <v>80081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9207,13 +9191,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476830</v>
+        <v>476869</v>
       </c>
       <c r="R84" t="n">
-        <v>6854480</v>
+        <v>6854645</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9258,60 +9242,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127386843</v>
+        <v>127369660</v>
       </c>
       <c r="B85" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476842</v>
+        <v>476880</v>
       </c>
       <c r="R85" t="n">
-        <v>6854652</v>
+        <v>6854794</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9338,9 +9322,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9355,22 +9349,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386082</v>
+        <v>127386820</v>
       </c>
       <c r="B86" t="n">
-        <v>78777</v>
+        <v>92612</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9378,21 +9372,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9402,13 +9396,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476804</v>
+        <v>476882</v>
       </c>
       <c r="R86" t="n">
-        <v>6854643</v>
+        <v>6854669</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9452,22 +9446,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127386834</v>
+        <v>127369891</v>
       </c>
       <c r="B87" t="n">
-        <v>80081</v>
+        <v>80156</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9475,40 +9469,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476869</v>
+        <v>476866</v>
       </c>
       <c r="R87" t="n">
-        <v>6854645</v>
+        <v>6854642</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9535,82 +9526,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127388974</v>
+        <v>127386080</v>
       </c>
       <c r="B88" t="n">
-        <v>98447</v>
+        <v>92632</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476859</v>
+        <v>476799</v>
       </c>
       <c r="R88" t="n">
-        <v>6854547</v>
+        <v>6854562</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9648,79 +9644,66 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386840</v>
+        <v>127386129</v>
       </c>
       <c r="B89" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476852</v>
+        <v>476790</v>
       </c>
       <c r="R89" t="n">
-        <v>6854630</v>
+        <v>6854633</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9758,51 +9741,50 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127386080</v>
+        <v>127386828</v>
       </c>
       <c r="B90" t="n">
-        <v>92632</v>
+        <v>80121</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9812,13 +9794,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476799</v>
+        <v>476869</v>
       </c>
       <c r="R90" t="n">
-        <v>6854562</v>
+        <v>6854645</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9862,60 +9844,64 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127386129</v>
+        <v>127388974</v>
       </c>
       <c r="B91" t="n">
-        <v>92620</v>
+        <v>98447</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476790</v>
+        <v>476859</v>
       </c>
       <c r="R91" t="n">
-        <v>6854633</v>
+        <v>6854547</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9953,63 +9939,76 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127386828</v>
+        <v>127386840</v>
       </c>
       <c r="B92" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476869</v>
+        <v>476852</v>
       </c>
       <c r="R92" t="n">
-        <v>6854645</v>
+        <v>6854630</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10050,6 +10049,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10364,45 +10364,49 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127370318</v>
+        <v>127386104</v>
       </c>
       <c r="B96" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476810</v>
+        <v>476865</v>
       </c>
       <c r="R96" t="n">
-        <v>6854587</v>
+        <v>6854661</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10432,46 +10436,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127386104</v>
+        <v>127386107</v>
       </c>
       <c r="B97" t="n">
         <v>98447</v>
@@ -10501,7 +10496,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10510,10 +10505,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476865</v>
+        <v>476800</v>
       </c>
       <c r="R97" t="n">
-        <v>6854661</v>
+        <v>6854551</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10573,52 +10568,56 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127386107</v>
+        <v>127388141</v>
       </c>
       <c r="B98" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>476800</v>
+        <v>476834</v>
       </c>
       <c r="R98" t="n">
-        <v>6854551</v>
+        <v>6854535</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10656,29 +10655,28 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127388141</v>
+        <v>127370318</v>
       </c>
       <c r="B99" t="n">
-        <v>57658</v>
+        <v>80121</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10686,45 +10684,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476834</v>
+        <v>476810</v>
       </c>
       <c r="R99" t="n">
-        <v>6854535</v>
+        <v>6854587</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10751,9 +10741,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10768,12 +10768,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Filippa Paperin, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127369215</v>
+        <v>127386081</v>
       </c>
       <c r="B2" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476907</v>
+        <v>476867</v>
       </c>
       <c r="R2" t="n">
-        <v>6854785</v>
+        <v>6854478</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -889,56 +879,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127386314</v>
+        <v>127369923</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>476867</v>
       </c>
       <c r="R4" t="n">
-        <v>6854648</v>
+        <v>6854642</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,37 +947,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127386839</v>
+        <v>127386314</v>
       </c>
       <c r="B5" t="n">
         <v>98447</v>
@@ -1023,20 +1014,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476824</v>
+        <v>476867</v>
       </c>
       <c r="R5" t="n">
-        <v>6854630</v>
+        <v>6854648</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,25 +1073,26 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127386098</v>
+        <v>127386839</v>
       </c>
       <c r="B6" t="n">
         <v>98447</v>
@@ -1120,24 +1120,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476851</v>
+        <v>476824</v>
       </c>
       <c r="R6" t="n">
-        <v>6854670</v>
+        <v>6854630</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,64 +1171,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127369923</v>
+        <v>127386098</v>
       </c>
       <c r="B7" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476867</v>
+        <v>476851</v>
       </c>
       <c r="R7" t="n">
-        <v>6854642</v>
+        <v>6854670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,49 +1261,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127386081</v>
+        <v>127369215</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,37 +1302,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476867</v>
+        <v>476907</v>
       </c>
       <c r="R8" t="n">
-        <v>6854478</v>
+        <v>6854785</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,9 +1359,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,12 +1386,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2640,32 +2640,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127386067</v>
+        <v>127386848</v>
       </c>
       <c r="B21" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476821</v>
+        <v>476840</v>
       </c>
       <c r="R21" t="n">
-        <v>6854543</v>
+        <v>6854622</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,50 +2719,51 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127386848</v>
+        <v>127386067</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2772,13 +2773,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476840</v>
+        <v>476821</v>
       </c>
       <c r="R22" t="n">
-        <v>6854622</v>
+        <v>6854543</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2816,19 +2817,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -4374,32 +4374,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127386108</v>
+        <v>127386117</v>
       </c>
       <c r="B38" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476830</v>
+        <v>476835</v>
       </c>
       <c r="R38" t="n">
-        <v>6854468</v>
+        <v>6854539</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4471,7 +4471,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127387587</v>
+        <v>127386108</v>
       </c>
       <c r="B39" t="n">
         <v>98447</v>
@@ -4499,32 +4499,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476850</v>
+        <v>476830</v>
       </c>
       <c r="R39" t="n">
-        <v>6854640</v>
+        <v>6854468</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4562,26 +4550,25 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127386311</v>
+        <v>127387587</v>
       </c>
       <c r="B40" t="n">
         <v>98447</v>
@@ -4614,7 +4601,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4624,13 +4615,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476828</v>
+        <v>476850</v>
       </c>
       <c r="R40" t="n">
-        <v>6854592</v>
+        <v>6854640</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4660,11 +4651,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4680,19 +4666,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127387586</v>
+        <v>127386311</v>
       </c>
       <c r="B41" t="n">
         <v>98447</v>
@@ -4720,20 +4706,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476859</v>
+        <v>476828</v>
       </c>
       <c r="R41" t="n">
-        <v>6854667</v>
+        <v>6854592</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4765,31 +4759,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127369992</v>
+        <v>127387586</v>
       </c>
       <c r="B42" t="n">
         <v>98447</v>
@@ -4818,24 +4818,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
         <v>476859</v>
       </c>
       <c r="R42" t="n">
-        <v>6854645</v>
+        <v>6854667</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4862,19 +4857,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4889,19 +4874,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127388975</v>
+        <v>127369992</v>
       </c>
       <c r="B43" t="n">
         <v>98447</v>
@@ -4929,24 +4914,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476864</v>
+        <v>476859</v>
       </c>
       <c r="R43" t="n">
-        <v>6854487</v>
+        <v>6854645</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4973,78 +4959,91 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127386117</v>
+        <v>127388975</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476835</v>
+        <v>476864</v>
       </c>
       <c r="R44" t="n">
-        <v>6854539</v>
+        <v>6854487</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5082,50 +5081,51 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127386808</v>
+        <v>127386078</v>
       </c>
       <c r="B45" t="n">
-        <v>79050</v>
+        <v>98468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476882</v>
+        <v>476854</v>
       </c>
       <c r="R45" t="n">
-        <v>6854781</v>
+        <v>6854673</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5185,44 +5185,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127386078</v>
+        <v>127386808</v>
       </c>
       <c r="B46" t="n">
-        <v>98468</v>
+        <v>79050</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5232,13 +5232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476854</v>
+        <v>476882</v>
       </c>
       <c r="R46" t="n">
-        <v>6854673</v>
+        <v>6854781</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5282,22 +5282,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127386087</v>
+        <v>127371200</v>
       </c>
       <c r="B47" t="n">
-        <v>78776</v>
+        <v>92612</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,37 +5305,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476780</v>
+        <v>476901</v>
       </c>
       <c r="R47" t="n">
-        <v>6854482</v>
+        <v>6854667</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5362,9 +5362,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5379,44 +5389,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127386089</v>
+        <v>127386312</v>
       </c>
       <c r="B48" t="n">
-        <v>78776</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5426,13 +5436,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476838</v>
+        <v>476860</v>
       </c>
       <c r="R48" t="n">
-        <v>6854681</v>
+        <v>6854625</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5476,60 +5486,72 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127371346</v>
+        <v>127387598</v>
       </c>
       <c r="B49" t="n">
-        <v>78776</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476826</v>
+        <v>476767</v>
       </c>
       <c r="R49" t="n">
-        <v>6854459</v>
+        <v>6854589</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5556,87 +5578,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127370572</v>
+        <v>127386838</v>
       </c>
       <c r="B50" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476857</v>
+        <v>476819</v>
       </c>
       <c r="R50" t="n">
-        <v>6854654</v>
+        <v>6854632</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5663,19 +5676,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5690,22 +5693,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127371200</v>
+        <v>127370572</v>
       </c>
       <c r="B51" t="n">
-        <v>92612</v>
+        <v>96700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,21 +5716,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5740,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476901</v>
+        <v>476857</v>
       </c>
       <c r="R51" t="n">
-        <v>6854667</v>
+        <v>6854654</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -5772,7 +5775,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5782,7 +5785,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5809,32 +5812,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386312</v>
+        <v>127386087</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5844,13 +5847,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476860</v>
+        <v>476780</v>
       </c>
       <c r="R52" t="n">
-        <v>6854625</v>
+        <v>6854482</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5894,72 +5897,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127387598</v>
+        <v>127386089</v>
       </c>
       <c r="B53" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476767</v>
+        <v>476838</v>
       </c>
       <c r="R53" t="n">
-        <v>6854589</v>
+        <v>6854681</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5997,67 +5988,66 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127386838</v>
+        <v>127371346</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476819</v>
+        <v>476826</v>
       </c>
       <c r="R54" t="n">
-        <v>6854632</v>
+        <v>6854459</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6084,9 +6074,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6101,12 +6101,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6437,48 +6437,60 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127386849</v>
+        <v>127387593</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>476891</v>
+        <v>476780</v>
       </c>
       <c r="R58" t="n">
-        <v>6854776</v>
+        <v>6854617</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6510,31 +6522,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127387593</v>
+        <v>127387589</v>
       </c>
       <c r="B59" t="n">
         <v>98447</v>
@@ -6564,7 +6582,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6581,10 +6599,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476780</v>
+        <v>476812</v>
       </c>
       <c r="R59" t="n">
-        <v>6854617</v>
+        <v>6854623</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6649,7 +6667,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127387589</v>
+        <v>127386313</v>
       </c>
       <c r="B60" t="n">
         <v>98447</v>
@@ -6679,14 +6697,10 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -6696,13 +6710,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476812</v>
+        <v>476881</v>
       </c>
       <c r="R60" t="n">
-        <v>6854623</v>
+        <v>6854650</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6732,11 +6746,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6752,19 +6761,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127386313</v>
+        <v>127371630</v>
       </c>
       <c r="B61" t="n">
         <v>98447</v>
@@ -6794,26 +6803,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476881</v>
+        <v>476874</v>
       </c>
       <c r="R61" t="n">
-        <v>6854650</v>
+        <v>6854475</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6840,37 +6850,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127371630</v>
+        <v>127387590</v>
       </c>
       <c r="B62" t="n">
         <v>98447</v>
@@ -6900,27 +6919,30 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476874</v>
+        <v>476860</v>
       </c>
       <c r="R62" t="n">
-        <v>6854475</v>
+        <v>6854552</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6947,19 +6969,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>16:38</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>4 blommande stänglar</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6968,78 +6985,67 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127387590</v>
+        <v>127386849</v>
       </c>
       <c r="B63" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>476860</v>
+        <v>476891</v>
       </c>
       <c r="R63" t="n">
-        <v>6854552</v>
+        <v>6854776</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7071,78 +7077,80 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>4 blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127386068</v>
+        <v>127386308</v>
       </c>
       <c r="B64" t="n">
-        <v>79050</v>
+        <v>98447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>476822</v>
+        <v>476825</v>
       </c>
       <c r="R64" t="n">
         <v>6854551</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7180,25 +7188,26 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127386308</v>
+        <v>127386110</v>
       </c>
       <c r="B65" t="n">
         <v>98447</v>
@@ -7226,28 +7235,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476825</v>
+        <v>476818</v>
       </c>
       <c r="R65" t="n">
-        <v>6854551</v>
+        <v>6854660</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7285,26 +7286,25 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386110</v>
+        <v>127386842</v>
       </c>
       <c r="B66" t="n">
         <v>98447</v>
@@ -7339,13 +7339,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476818</v>
+        <v>476869</v>
       </c>
       <c r="R66" t="n">
-        <v>6854660</v>
+        <v>6854655</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7389,19 +7389,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386842</v>
+        <v>127386096</v>
       </c>
       <c r="B67" t="n">
         <v>98447</v>
@@ -7429,20 +7429,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476869</v>
+        <v>476806</v>
       </c>
       <c r="R67" t="n">
-        <v>6854655</v>
+        <v>6854483</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7480,70 +7484,67 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386096</v>
+        <v>127371302</v>
       </c>
       <c r="B68" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476806</v>
+        <v>476826</v>
       </c>
       <c r="R68" t="n">
-        <v>6854483</v>
+        <v>6854459</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7570,40 +7571,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127371302</v>
+        <v>127386068</v>
       </c>
       <c r="B69" t="n">
-        <v>78777</v>
+        <v>79050</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7611,37 +7621,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476826</v>
+        <v>476822</v>
       </c>
       <c r="R69" t="n">
-        <v>6854459</v>
+        <v>6854551</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7668,19 +7678,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7695,12 +7695,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8645,53 +8645,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127386315</v>
+        <v>127369660</v>
       </c>
       <c r="B79" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476883</v>
+        <v>476880</v>
       </c>
       <c r="R79" t="n">
-        <v>6854657</v>
+        <v>6854794</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8721,79 +8713,84 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127386103</v>
+        <v>127369891</v>
       </c>
       <c r="B80" t="n">
-        <v>98447</v>
+        <v>80156</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476832</v>
+        <v>476866</v>
       </c>
       <c r="R80" t="n">
-        <v>6854485</v>
+        <v>6854642</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8823,86 +8820,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127386300</v>
+        <v>127386820</v>
       </c>
       <c r="B81" t="n">
-        <v>98447</v>
+        <v>92612</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476830</v>
+        <v>476882</v>
       </c>
       <c r="R81" t="n">
-        <v>6854480</v>
+        <v>6854669</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8940,26 +8938,25 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386843</v>
+        <v>127386315</v>
       </c>
       <c r="B82" t="n">
         <v>98447</v>
@@ -8987,20 +8984,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476842</v>
+        <v>476883</v>
       </c>
       <c r="R82" t="n">
-        <v>6854652</v>
+        <v>6854657</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9038,63 +9043,68 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386082</v>
+        <v>127386103</v>
       </c>
       <c r="B83" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476804</v>
+        <v>476832</v>
       </c>
       <c r="R83" t="n">
-        <v>6854643</v>
+        <v>6854485</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9135,6 +9145,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9153,37 +9164,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386834</v>
+        <v>127386300</v>
       </c>
       <c r="B84" t="n">
-        <v>80081</v>
+        <v>98447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9191,13 +9207,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476869</v>
+        <v>476830</v>
       </c>
       <c r="R84" t="n">
-        <v>6854645</v>
+        <v>6854480</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9242,60 +9258,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127369660</v>
+        <v>127386843</v>
       </c>
       <c r="B85" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476880</v>
+        <v>476842</v>
       </c>
       <c r="R85" t="n">
-        <v>6854794</v>
+        <v>6854652</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9322,19 +9338,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9349,22 +9355,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386820</v>
+        <v>127386082</v>
       </c>
       <c r="B86" t="n">
-        <v>92612</v>
+        <v>78777</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9372,21 +9378,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9396,13 +9402,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476882</v>
+        <v>476804</v>
       </c>
       <c r="R86" t="n">
-        <v>6854669</v>
+        <v>6854643</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9446,22 +9452,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127369891</v>
+        <v>127386834</v>
       </c>
       <c r="B87" t="n">
-        <v>80156</v>
+        <v>80081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9469,37 +9475,40 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476866</v>
+        <v>476869</v>
       </c>
       <c r="R87" t="n">
-        <v>6854642</v>
+        <v>6854645</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9526,87 +9535,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127386080</v>
+        <v>127388974</v>
       </c>
       <c r="B88" t="n">
-        <v>92632</v>
+        <v>98447</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476799</v>
+        <v>476859</v>
       </c>
       <c r="R88" t="n">
-        <v>6854562</v>
+        <v>6854547</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9644,66 +9648,79 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386129</v>
+        <v>127386840</v>
       </c>
       <c r="B89" t="n">
-        <v>92620</v>
+        <v>98447</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476790</v>
+        <v>476852</v>
       </c>
       <c r="R89" t="n">
-        <v>6854633</v>
+        <v>6854630</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9741,50 +9758,51 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127386828</v>
+        <v>127386080</v>
       </c>
       <c r="B90" t="n">
-        <v>80121</v>
+        <v>92632</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9794,13 +9812,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476869</v>
+        <v>476799</v>
       </c>
       <c r="R90" t="n">
-        <v>6854645</v>
+        <v>6854562</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9844,64 +9862,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127388974</v>
+        <v>127386129</v>
       </c>
       <c r="B91" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476859</v>
+        <v>476790</v>
       </c>
       <c r="R91" t="n">
-        <v>6854547</v>
+        <v>6854633</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9939,76 +9953,63 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127386840</v>
+        <v>127386828</v>
       </c>
       <c r="B92" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476852</v>
+        <v>476869</v>
       </c>
       <c r="R92" t="n">
-        <v>6854630</v>
+        <v>6854645</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10049,7 +10050,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10364,49 +10364,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127386104</v>
+        <v>127370318</v>
       </c>
       <c r="B96" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476865</v>
+        <v>476810</v>
       </c>
       <c r="R96" t="n">
-        <v>6854661</v>
+        <v>6854587</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10436,37 +10432,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127386107</v>
+        <v>127386104</v>
       </c>
       <c r="B97" t="n">
         <v>98447</v>
@@ -10496,7 +10501,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10505,10 +10510,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476800</v>
+        <v>476865</v>
       </c>
       <c r="R97" t="n">
-        <v>6854551</v>
+        <v>6854661</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10568,56 +10573,52 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127388141</v>
+        <v>127386107</v>
       </c>
       <c r="B98" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>476834</v>
+        <v>476800</v>
       </c>
       <c r="R98" t="n">
-        <v>6854535</v>
+        <v>6854551</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10655,28 +10656,29 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127370318</v>
+        <v>127388141</v>
       </c>
       <c r="B99" t="n">
-        <v>80121</v>
+        <v>57658</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10684,37 +10686,45 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476810</v>
+        <v>476834</v>
       </c>
       <c r="R99" t="n">
-        <v>6854587</v>
+        <v>6854535</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10741,19 +10751,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10768,12 +10768,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127386081</v>
+        <v>127369215</v>
       </c>
       <c r="B2" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476867</v>
+        <v>476907</v>
       </c>
       <c r="R2" t="n">
-        <v>6854478</v>
+        <v>6854785</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +743,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -986,43 +996,35 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127386314</v>
+        <v>127386081</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
@@ -1032,10 +1034,10 @@
         <v>476867</v>
       </c>
       <c r="R5" t="n">
-        <v>6854648</v>
+        <v>6854478</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,29 +1075,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127386839</v>
+        <v>127386314</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,20 +1121,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476824</v>
+        <v>476867</v>
       </c>
       <c r="R6" t="n">
-        <v>6854630</v>
+        <v>6854648</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,28 +1180,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127386098</v>
+        <v>127386839</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,24 +1227,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476851</v>
+        <v>476824</v>
       </c>
       <c r="R7" t="n">
-        <v>6854670</v>
+        <v>6854630</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1272,67 +1278,70 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127369215</v>
+        <v>127386098</v>
       </c>
       <c r="B8" t="n">
-        <v>78685</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476907</v>
+        <v>476851</v>
       </c>
       <c r="R8" t="n">
-        <v>6854785</v>
+        <v>6854670</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,39 +1368,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127386850</v>
+        <v>127388142</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,37 +1506,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476896</v>
+        <v>476840</v>
       </c>
       <c r="R10" t="n">
-        <v>6854789</v>
+        <v>6854642</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1580,65 +1588,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127388142</v>
+        <v>127388973</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476840</v>
+        <v>476828</v>
       </c>
       <c r="R11" t="n">
-        <v>6854642</v>
+        <v>6854626</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1679,28 +1683,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127388973</v>
+        <v>127371659</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1725,21 +1730,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476828</v>
+        <v>476822</v>
       </c>
       <c r="R12" t="n">
-        <v>6854626</v>
+        <v>6854617</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1769,40 +1770,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127371659</v>
+        <v>127387597</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,20 +1837,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476822</v>
+        <v>476831</v>
       </c>
       <c r="R13" t="n">
-        <v>6854617</v>
+        <v>6854622</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1867,49 +1889,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127387597</v>
+        <v>127387592</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,7 +1949,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1953,10 +1966,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476831</v>
+        <v>476796</v>
       </c>
       <c r="R14" t="n">
-        <v>6854622</v>
+        <v>6854627</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1989,6 +2002,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,10 +2034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127387592</v>
+        <v>127388966</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,30 +2064,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476796</v>
+        <v>476792</v>
       </c>
       <c r="R15" t="n">
-        <v>6854627</v>
+        <v>6854646</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2099,11 +2109,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,64 +2124,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127388966</v>
+        <v>127386850</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476792</v>
+        <v>476896</v>
       </c>
       <c r="R16" t="n">
-        <v>6854646</v>
+        <v>6854789</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2214,19 +2215,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
         <v>127388963</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127386305</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127386099</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,32 +2640,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127386848</v>
+        <v>127386067</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476840</v>
+        <v>476821</v>
       </c>
       <c r="R21" t="n">
-        <v>6854622</v>
+        <v>6854543</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,51 +2719,50 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127386067</v>
+        <v>127386848</v>
       </c>
       <c r="B22" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,13 +2772,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476821</v>
+        <v>476840</v>
       </c>
       <c r="R22" t="n">
-        <v>6854543</v>
+        <v>6854622</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2817,63 +2816,72 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127386319</v>
+        <v>127386302</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476821</v>
+        <v>476828</v>
       </c>
       <c r="R23" t="n">
-        <v>6854475</v>
+        <v>6854531</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -2914,6 +2922,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2932,48 +2941,56 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127369424</v>
+        <v>127388976</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476879</v>
+        <v>476880</v>
       </c>
       <c r="R24" t="n">
-        <v>6854650</v>
+        <v>6854486</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3000,87 +3017,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127387585</v>
+        <v>127386102</v>
       </c>
       <c r="B25" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476865</v>
+        <v>476821</v>
       </c>
       <c r="R25" t="n">
-        <v>6854638</v>
+        <v>6854465</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3118,71 +3130,64 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127386302</v>
+        <v>127386319</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476828</v>
+        <v>476821</v>
       </c>
       <c r="R26" t="n">
-        <v>6854531</v>
+        <v>6854475</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3223,7 +3228,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3242,56 +3246,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127388976</v>
+        <v>127369424</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476880</v>
+        <v>476879</v>
       </c>
       <c r="R27" t="n">
-        <v>6854486</v>
+        <v>6854650</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3318,82 +3314,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127386102</v>
+        <v>127387585</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476821</v>
+        <v>476865</v>
       </c>
       <c r="R28" t="n">
-        <v>6854465</v>
+        <v>6854638</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3431,19 +3432,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3652,48 +3652,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127386111</v>
+        <v>127371357</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476831</v>
+        <v>476901</v>
       </c>
       <c r="R31" t="n">
-        <v>6854682</v>
+        <v>6854667</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3720,9 +3720,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3737,64 +3747,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127386100</v>
+        <v>127370759</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>80156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476829</v>
+        <v>476877</v>
       </c>
       <c r="R32" t="n">
-        <v>6854465</v>
+        <v>6854663</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3821,40 +3827,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127386299</v>
+        <v>127386111</v>
       </c>
       <c r="B33" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,28 +3894,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476817</v>
+        <v>476831</v>
       </c>
       <c r="R33" t="n">
-        <v>6854465</v>
+        <v>6854682</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3938,29 +3945,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127386303</v>
+        <v>127386100</v>
       </c>
       <c r="B34" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3987,26 +3993,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476836</v>
+        <v>476829</v>
       </c>
       <c r="R34" t="n">
-        <v>6854627</v>
+        <v>6854465</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4051,22 +4053,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127386112</v>
+        <v>127386299</v>
       </c>
       <c r="B35" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4091,20 +4093,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476873</v>
+        <v>476817</v>
       </c>
       <c r="R35" t="n">
-        <v>6854658</v>
+        <v>6854465</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4142,63 +4152,72 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127371357</v>
+        <v>127386303</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476901</v>
+        <v>476836</v>
       </c>
       <c r="R36" t="n">
-        <v>6854667</v>
+        <v>6854627</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4228,87 +4247,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127370759</v>
+        <v>127386112</v>
       </c>
       <c r="B37" t="n">
-        <v>80156</v>
+        <v>98448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476877</v>
+        <v>476873</v>
       </c>
       <c r="R37" t="n">
-        <v>6854663</v>
+        <v>6854658</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4335,19 +4345,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4362,60 +4362,64 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127386117</v>
+        <v>127388975</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476835</v>
+        <v>476864</v>
       </c>
       <c r="R38" t="n">
-        <v>6854539</v>
+        <v>6854487</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4453,50 +4457,51 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127386108</v>
+        <v>127386117</v>
       </c>
       <c r="B39" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4506,10 +4511,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476830</v>
+        <v>476835</v>
       </c>
       <c r="R39" t="n">
-        <v>6854468</v>
+        <v>6854539</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4568,10 +4573,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127387587</v>
+        <v>127386108</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4596,32 +4601,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476850</v>
+        <v>476830</v>
       </c>
       <c r="R40" t="n">
-        <v>6854640</v>
+        <v>6854468</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4659,29 +4652,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127386311</v>
+        <v>127387587</v>
       </c>
       <c r="B41" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4711,7 +4703,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -4721,13 +4717,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476828</v>
+        <v>476850</v>
       </c>
       <c r="R41" t="n">
-        <v>6854592</v>
+        <v>6854640</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4757,11 +4753,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4777,22 +4768,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127387586</v>
+        <v>127386311</v>
       </c>
       <c r="B42" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4817,20 +4808,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476859</v>
+        <v>476828</v>
       </c>
       <c r="R42" t="n">
-        <v>6854667</v>
+        <v>6854592</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4862,34 +4861,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127369992</v>
+        <v>127387586</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4915,24 +4920,19 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
         <v>476859</v>
       </c>
       <c r="R43" t="n">
-        <v>6854645</v>
+        <v>6854667</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4959,19 +4959,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4986,22 +4976,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127388975</v>
+        <v>127369992</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5026,24 +5016,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476864</v>
+        <v>476859</v>
       </c>
       <c r="R44" t="n">
-        <v>6854487</v>
+        <v>6854645</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5070,62 +5061,71 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127386078</v>
+        <v>127386808</v>
       </c>
       <c r="B45" t="n">
-        <v>98468</v>
+        <v>79050</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476854</v>
+        <v>476882</v>
       </c>
       <c r="R45" t="n">
-        <v>6854673</v>
+        <v>6854781</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5185,44 +5185,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127386808</v>
+        <v>127386078</v>
       </c>
       <c r="B46" t="n">
-        <v>79050</v>
+        <v>98469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5232,13 +5232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476882</v>
+        <v>476854</v>
       </c>
       <c r="R46" t="n">
-        <v>6854781</v>
+        <v>6854673</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5282,22 +5282,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127371200</v>
+        <v>127370572</v>
       </c>
       <c r="B47" t="n">
-        <v>92612</v>
+        <v>96700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476901</v>
+        <v>476857</v>
       </c>
       <c r="R47" t="n">
-        <v>6854667</v>
+        <v>6854654</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5401,45 +5401,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127386312</v>
+        <v>127371200</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>92612</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476860</v>
+        <v>476901</v>
       </c>
       <c r="R48" t="n">
-        <v>6854625</v>
+        <v>6854667</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5469,9 +5469,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5486,72 +5496,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127387598</v>
+        <v>127386087</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476767</v>
+        <v>476780</v>
       </c>
       <c r="R49" t="n">
-        <v>6854589</v>
+        <v>6854482</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5589,51 +5587,50 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127386838</v>
+        <v>127386089</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5643,13 +5640,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476819</v>
+        <v>476838</v>
       </c>
       <c r="R50" t="n">
-        <v>6854632</v>
+        <v>6854681</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5693,22 +5690,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127370572</v>
+        <v>127371346</v>
       </c>
       <c r="B51" t="n">
-        <v>96700</v>
+        <v>78776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5716,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5740,13 +5737,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476857</v>
+        <v>476826</v>
       </c>
       <c r="R51" t="n">
-        <v>6854654</v>
+        <v>6854459</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5775,7 +5772,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5785,7 +5782,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5800,44 +5797,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386087</v>
+        <v>127386312</v>
       </c>
       <c r="B52" t="n">
-        <v>78776</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5847,13 +5844,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476780</v>
+        <v>476860</v>
       </c>
       <c r="R52" t="n">
-        <v>6854482</v>
+        <v>6854625</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5897,60 +5894,72 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127386089</v>
+        <v>127387598</v>
       </c>
       <c r="B53" t="n">
-        <v>78776</v>
+        <v>98448</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476838</v>
+        <v>476767</v>
       </c>
       <c r="R53" t="n">
-        <v>6854681</v>
+        <v>6854589</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5988,66 +5997,67 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127371346</v>
+        <v>127386838</v>
       </c>
       <c r="B54" t="n">
-        <v>78776</v>
+        <v>98448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476826</v>
+        <v>476819</v>
       </c>
       <c r="R54" t="n">
-        <v>6854459</v>
+        <v>6854632</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6074,19 +6084,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6101,64 +6101,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127388147</v>
+        <v>127370418</v>
       </c>
       <c r="B55" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476787</v>
+        <v>476867</v>
       </c>
       <c r="R55" t="n">
-        <v>6854642</v>
+        <v>6854691</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6188,75 +6181,91 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127370418</v>
+        <v>127388147</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476867</v>
+        <v>476787</v>
       </c>
       <c r="R56" t="n">
-        <v>6854691</v>
+        <v>6854642</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6286,39 +6295,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6437,60 +6437,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127387593</v>
+        <v>127386849</v>
       </c>
       <c r="B58" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>476780</v>
+        <v>476891</v>
       </c>
       <c r="R58" t="n">
-        <v>6854617</v>
+        <v>6854776</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6522,40 +6510,34 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127387589</v>
+        <v>127387593</v>
       </c>
       <c r="B59" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6582,7 +6564,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6599,10 +6581,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476812</v>
+        <v>476780</v>
       </c>
       <c r="R59" t="n">
-        <v>6854623</v>
+        <v>6854617</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6667,10 +6649,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127386313</v>
+        <v>127387589</v>
       </c>
       <c r="B60" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6697,10 +6679,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -6710,13 +6696,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476881</v>
+        <v>476812</v>
       </c>
       <c r="R60" t="n">
-        <v>6854650</v>
+        <v>6854623</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6746,6 +6732,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6761,22 +6752,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127371630</v>
+        <v>127386313</v>
       </c>
       <c r="B61" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6803,27 +6794,26 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476874</v>
+        <v>476881</v>
       </c>
       <c r="R61" t="n">
-        <v>6854475</v>
+        <v>6854650</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6850,49 +6840,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127387590</v>
+        <v>127371630</v>
       </c>
       <c r="B62" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6919,30 +6900,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476860</v>
+        <v>476874</v>
       </c>
       <c r="R62" t="n">
-        <v>6854552</v>
+        <v>6854475</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6969,14 +6947,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>4 blommande stänglar</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6985,67 +6968,78 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127386849</v>
+        <v>127387590</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>476891</v>
+        <v>476860</v>
       </c>
       <c r="R63" t="n">
-        <v>6854776</v>
+        <v>6854552</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7077,80 +7071,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>4 blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127386308</v>
+        <v>127386068</v>
       </c>
       <c r="B64" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>476825</v>
+        <v>476822</v>
       </c>
       <c r="R64" t="n">
         <v>6854551</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7188,67 +7180,66 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127386110</v>
+        <v>127371302</v>
       </c>
       <c r="B65" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476818</v>
+        <v>476826</v>
       </c>
       <c r="R65" t="n">
-        <v>6854660</v>
+        <v>6854459</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7275,9 +7266,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7292,22 +7293,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386842</v>
+        <v>127386308</v>
       </c>
       <c r="B66" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,20 +7333,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476869</v>
+        <v>476825</v>
       </c>
       <c r="R66" t="n">
-        <v>6854655</v>
+        <v>6854551</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7383,28 +7392,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386096</v>
+        <v>127386110</v>
       </c>
       <c r="B67" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7429,21 +7439,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476806</v>
+        <v>476818</v>
       </c>
       <c r="R67" t="n">
-        <v>6854483</v>
+        <v>6854660</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7484,7 +7490,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7503,48 +7508,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127371302</v>
+        <v>127386842</v>
       </c>
       <c r="B68" t="n">
-        <v>78777</v>
+        <v>98448</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476826</v>
+        <v>476869</v>
       </c>
       <c r="R68" t="n">
-        <v>6854459</v>
+        <v>6854655</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7571,19 +7576,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7598,57 +7593,61 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127386068</v>
+        <v>127386096</v>
       </c>
       <c r="B69" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476822</v>
+        <v>476806</v>
       </c>
       <c r="R69" t="n">
-        <v>6854551</v>
+        <v>6854483</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7689,6 +7688,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>127388970</v>
       </c>
       <c r="B70" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7809,10 +7809,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127387596</v>
+        <v>127371242</v>
       </c>
       <c r="B71" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7839,30 +7839,22 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>476827</v>
+        <v>476826</v>
       </c>
       <c r="R71" t="n">
-        <v>6854628</v>
+        <v>6854459</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7889,40 +7881,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127371242</v>
+        <v>127386109</v>
       </c>
       <c r="B72" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7947,24 +7948,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>476826</v>
+        <v>476831</v>
       </c>
       <c r="R72" t="n">
-        <v>6854459</v>
+        <v>6854531</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7991,19 +7988,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8018,22 +8005,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127386109</v>
+        <v>127387596</v>
       </c>
       <c r="B73" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8058,20 +8045,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>476831</v>
+        <v>476827</v>
       </c>
       <c r="R73" t="n">
-        <v>6854531</v>
+        <v>6854628</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8109,66 +8108,67 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127369233</v>
+        <v>127386841</v>
       </c>
       <c r="B74" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>476907</v>
+        <v>476865</v>
       </c>
       <c r="R74" t="n">
-        <v>6854785</v>
+        <v>6854629</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8195,19 +8195,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8222,22 +8212,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127386841</v>
+        <v>127388972</v>
       </c>
       <c r="B75" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8262,20 +8252,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476865</v>
+        <v>476809</v>
       </c>
       <c r="R75" t="n">
-        <v>6854629</v>
+        <v>6854638</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8313,28 +8307,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127388972</v>
+        <v>127387595</v>
       </c>
       <c r="B76" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8361,22 +8356,30 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476809</v>
+        <v>476804</v>
       </c>
       <c r="R76" t="n">
-        <v>6854638</v>
+        <v>6854628</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8421,22 +8424,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127387595</v>
+        <v>127386097</v>
       </c>
       <c r="B77" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8463,30 +8466,22 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476804</v>
+        <v>476794</v>
       </c>
       <c r="R77" t="n">
-        <v>6854628</v>
+        <v>6854562</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8531,64 +8526,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127386097</v>
+        <v>127369233</v>
       </c>
       <c r="B78" t="n">
-        <v>98447</v>
+        <v>79050</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476794</v>
+        <v>476907</v>
       </c>
       <c r="R78" t="n">
-        <v>6854562</v>
+        <v>6854785</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8615,30 +8606,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8752,48 +8752,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127369891</v>
+        <v>127386820</v>
       </c>
       <c r="B80" t="n">
-        <v>80156</v>
+        <v>92612</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>4361</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476866</v>
+        <v>476882</v>
       </c>
       <c r="R80" t="n">
-        <v>6854642</v>
+        <v>6854669</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8820,19 +8820,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8847,60 +8837,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127386820</v>
+        <v>127369891</v>
       </c>
       <c r="B81" t="n">
-        <v>92612</v>
+        <v>80156</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476882</v>
+        <v>476866</v>
       </c>
       <c r="R81" t="n">
-        <v>6854669</v>
+        <v>6854642</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8927,9 +8917,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8944,22 +8944,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386315</v>
+        <v>127386103</v>
       </c>
       <c r="B82" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8986,26 +8986,22 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476883</v>
+        <v>476832</v>
       </c>
       <c r="R82" t="n">
-        <v>6854657</v>
+        <v>6854485</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9050,22 +9046,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386103</v>
+        <v>127386300</v>
       </c>
       <c r="B83" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9092,22 +9088,26 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476832</v>
+        <v>476830</v>
       </c>
       <c r="R83" t="n">
-        <v>6854485</v>
+        <v>6854480</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9152,22 +9152,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386300</v>
+        <v>127386843</v>
       </c>
       <c r="B84" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9192,28 +9192,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476830</v>
+        <v>476842</v>
       </c>
       <c r="R84" t="n">
-        <v>6854480</v>
+        <v>6854652</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9251,29 +9243,28 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127386843</v>
+        <v>127386315</v>
       </c>
       <c r="B85" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9298,20 +9289,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476842</v>
+        <v>476883</v>
       </c>
       <c r="R85" t="n">
-        <v>6854652</v>
+        <v>6854657</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9349,18 +9348,19 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9565,52 +9565,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127388974</v>
+        <v>127386080</v>
       </c>
       <c r="B88" t="n">
-        <v>98447</v>
+        <v>92632</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476859</v>
+        <v>476799</v>
       </c>
       <c r="R88" t="n">
-        <v>6854547</v>
+        <v>6854562</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9648,79 +9644,66 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386840</v>
+        <v>127386129</v>
       </c>
       <c r="B89" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476852</v>
+        <v>476790</v>
       </c>
       <c r="R89" t="n">
-        <v>6854630</v>
+        <v>6854633</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9758,51 +9741,50 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127386080</v>
+        <v>127386828</v>
       </c>
       <c r="B90" t="n">
-        <v>92632</v>
+        <v>80121</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9812,13 +9794,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476799</v>
+        <v>476869</v>
       </c>
       <c r="R90" t="n">
-        <v>6854562</v>
+        <v>6854645</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9862,60 +9844,72 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127386129</v>
+        <v>127386840</v>
       </c>
       <c r="B91" t="n">
-        <v>92620</v>
+        <v>98448</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476790</v>
+        <v>476852</v>
       </c>
       <c r="R91" t="n">
-        <v>6854633</v>
+        <v>6854630</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9953,66 +9947,71 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127386828</v>
+        <v>127388974</v>
       </c>
       <c r="B92" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476869</v>
+        <v>476859</v>
       </c>
       <c r="R92" t="n">
-        <v>6854645</v>
+        <v>6854547</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10050,18 +10049,19 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10168,7 +10168,7 @@
         <v>127386101</v>
       </c>
       <c r="B94" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>127386837</v>
       </c>
       <c r="B95" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10364,10 +10364,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127370318</v>
+        <v>127388141</v>
       </c>
       <c r="B96" t="n">
-        <v>80121</v>
+        <v>57658</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10375,37 +10375,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476810</v>
+        <v>476834</v>
       </c>
       <c r="R96" t="n">
-        <v>6854587</v>
+        <v>6854535</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10432,19 +10440,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10459,61 +10457,57 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127386104</v>
+        <v>127370318</v>
       </c>
       <c r="B97" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476865</v>
+        <v>476810</v>
       </c>
       <c r="R97" t="n">
-        <v>6854661</v>
+        <v>6854587</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10543,30 +10537,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10576,7 +10579,7 @@
         <v>127386107</v>
       </c>
       <c r="B98" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10675,56 +10678,52 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127388141</v>
+        <v>127386104</v>
       </c>
       <c r="B99" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476834</v>
+        <v>476865</v>
       </c>
       <c r="R99" t="n">
-        <v>6854535</v>
+        <v>6854661</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10762,18 +10761,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10974,56 +10974,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127386310</v>
+        <v>127386811</v>
       </c>
       <c r="B102" t="n">
-        <v>98447</v>
+        <v>79607</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>476822</v>
+        <v>476887</v>
       </c>
       <c r="R102" t="n">
-        <v>6854557</v>
+        <v>6854810</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11061,29 +11053,28 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127388967</v>
+        <v>127386310</v>
       </c>
       <c r="B103" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11110,19 +11101,23 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>476843</v>
+        <v>476822</v>
       </c>
       <c r="R103" t="n">
-        <v>6854525</v>
+        <v>6854557</v>
       </c>
       <c r="S103" t="n">
         <v>4</v>
@@ -11170,12 +11165,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11185,7 +11180,7 @@
         <v>127387594</v>
       </c>
       <c r="B104" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11292,48 +11287,52 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127386811</v>
+        <v>127388967</v>
       </c>
       <c r="B105" t="n">
-        <v>79607</v>
+        <v>98448</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>476887</v>
+        <v>476843</v>
       </c>
       <c r="R105" t="n">
-        <v>6854810</v>
+        <v>6854525</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11371,18 +11370,19 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127371169</v>
+        <v>127369923</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476901</v>
+        <v>476867</v>
       </c>
       <c r="R3" t="n">
-        <v>6854667</v>
+        <v>6854642</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,57 +877,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127369923</v>
+        <v>127386081</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>78777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>476867</v>
       </c>
       <c r="R4" t="n">
-        <v>6854642</v>
+        <v>6854478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,19 +957,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127386081</v>
+        <v>127371169</v>
       </c>
       <c r="B5" t="n">
-        <v>78777</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476867</v>
+        <v>476901</v>
       </c>
       <c r="R5" t="n">
-        <v>6854478</v>
+        <v>6854667</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,9 +1054,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,12 +1081,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2640,32 +2640,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127386067</v>
+        <v>127386848</v>
       </c>
       <c r="B21" t="n">
-        <v>79050</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476821</v>
+        <v>476840</v>
       </c>
       <c r="R21" t="n">
-        <v>6854543</v>
+        <v>6854622</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,50 +2719,51 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127386848</v>
+        <v>127386067</v>
       </c>
       <c r="B22" t="n">
-        <v>98448</v>
+        <v>79050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2772,13 +2773,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476840</v>
+        <v>476821</v>
       </c>
       <c r="R22" t="n">
-        <v>6854622</v>
+        <v>6854543</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2816,19 +2817,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3149,32 +3149,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127386319</v>
+        <v>127387581</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>97325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3184,13 +3184,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476821</v>
+        <v>476827</v>
       </c>
       <c r="R26" t="n">
-        <v>6854475</v>
+        <v>6854629</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3234,60 +3234,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127369424</v>
+        <v>127386319</v>
       </c>
       <c r="B27" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476879</v>
+        <v>476821</v>
       </c>
       <c r="R27" t="n">
-        <v>6854650</v>
+        <v>6854475</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3314,19 +3314,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3341,60 +3331,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127387585</v>
+        <v>127369424</v>
       </c>
       <c r="B28" t="n">
-        <v>80121</v>
+        <v>80150</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476865</v>
+        <v>476879</v>
       </c>
       <c r="R28" t="n">
-        <v>6854638</v>
+        <v>6854650</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3421,9 +3411,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3438,44 +3438,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127387581</v>
+        <v>127387585</v>
       </c>
       <c r="B29" t="n">
-        <v>97325</v>
+        <v>80121</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476827</v>
+        <v>476865</v>
       </c>
       <c r="R29" t="n">
-        <v>6854629</v>
+        <v>6854638</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -7198,48 +7198,56 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127371302</v>
+        <v>127386308</v>
       </c>
       <c r="B65" t="n">
-        <v>78777</v>
+        <v>98448</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476826</v>
+        <v>476825</v>
       </c>
       <c r="R65" t="n">
-        <v>6854459</v>
+        <v>6854551</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7266,46 +7274,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386308</v>
+        <v>127386110</v>
       </c>
       <c r="B66" t="n">
         <v>98448</v>
@@ -7333,28 +7332,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476825</v>
+        <v>476818</v>
       </c>
       <c r="R66" t="n">
-        <v>6854551</v>
+        <v>6854660</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7392,26 +7383,25 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386110</v>
+        <v>127386842</v>
       </c>
       <c r="B67" t="n">
         <v>98448</v>
@@ -7446,13 +7436,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476818</v>
+        <v>476869</v>
       </c>
       <c r="R67" t="n">
-        <v>6854660</v>
+        <v>6854655</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7496,19 +7486,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386842</v>
+        <v>127386096</v>
       </c>
       <c r="B68" t="n">
         <v>98448</v>
@@ -7536,20 +7526,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476869</v>
+        <v>476806</v>
       </c>
       <c r="R68" t="n">
-        <v>6854655</v>
+        <v>6854483</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7587,70 +7581,67 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127386096</v>
+        <v>127371302</v>
       </c>
       <c r="B69" t="n">
-        <v>98448</v>
+        <v>78777</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476806</v>
+        <v>476826</v>
       </c>
       <c r="R69" t="n">
-        <v>6854483</v>
+        <v>6854459</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7677,30 +7668,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7809,7 +7809,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127371242</v>
+        <v>127387596</v>
       </c>
       <c r="B71" t="n">
         <v>98448</v>
@@ -7839,22 +7839,30 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>476826</v>
+        <v>476827</v>
       </c>
       <c r="R71" t="n">
-        <v>6854459</v>
+        <v>6854628</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7881,46 +7889,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127386109</v>
+        <v>127371242</v>
       </c>
       <c r="B72" t="n">
         <v>98448</v>
@@ -7948,20 +7947,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>476831</v>
+        <v>476826</v>
       </c>
       <c r="R72" t="n">
-        <v>6854531</v>
+        <v>6854459</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7988,9 +7991,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8005,19 +8018,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127387596</v>
+        <v>127386109</v>
       </c>
       <c r="B73" t="n">
         <v>98448</v>
@@ -8045,32 +8058,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>476827</v>
+        <v>476831</v>
       </c>
       <c r="R73" t="n">
-        <v>6854628</v>
+        <v>6854531</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8108,19 +8109,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8645,45 +8645,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127369660</v>
+        <v>127386315</v>
       </c>
       <c r="B79" t="n">
-        <v>96700</v>
+        <v>98448</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476880</v>
+        <v>476883</v>
       </c>
       <c r="R79" t="n">
-        <v>6854794</v>
+        <v>6854657</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8713,87 +8721,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127386820</v>
+        <v>127386103</v>
       </c>
       <c r="B80" t="n">
-        <v>92612</v>
+        <v>98448</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476882</v>
+        <v>476832</v>
       </c>
       <c r="R80" t="n">
-        <v>6854669</v>
+        <v>6854485</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8831,66 +8834,75 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127369891</v>
+        <v>127386300</v>
       </c>
       <c r="B81" t="n">
-        <v>80156</v>
+        <v>98448</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476866</v>
+        <v>476830</v>
       </c>
       <c r="R81" t="n">
-        <v>6854642</v>
+        <v>6854480</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8917,46 +8929,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386103</v>
+        <v>127386843</v>
       </c>
       <c r="B82" t="n">
         <v>98448</v>
@@ -8984,24 +8987,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476832</v>
+        <v>476842</v>
       </c>
       <c r="R82" t="n">
-        <v>6854485</v>
+        <v>6854652</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9039,75 +9038,66 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386300</v>
+        <v>127386082</v>
       </c>
       <c r="B83" t="n">
-        <v>98448</v>
+        <v>78777</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476830</v>
+        <v>476804</v>
       </c>
       <c r="R83" t="n">
-        <v>6854480</v>
+        <v>6854643</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9145,64 +9135,66 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386843</v>
+        <v>127386834</v>
       </c>
       <c r="B84" t="n">
-        <v>98448</v>
+        <v>80081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476842</v>
+        <v>476869</v>
       </c>
       <c r="R84" t="n">
-        <v>6854652</v>
+        <v>6854645</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9243,6 +9235,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9254,60 +9247,52 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127386315</v>
+        <v>127369660</v>
       </c>
       <c r="B85" t="n">
-        <v>98448</v>
+        <v>96700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476883</v>
+        <v>476880</v>
       </c>
       <c r="R85" t="n">
-        <v>6854657</v>
+        <v>6854794</v>
       </c>
       <c r="S85" t="n">
         <v>4</v>
@@ -9337,40 +9322,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386082</v>
+        <v>127386820</v>
       </c>
       <c r="B86" t="n">
-        <v>78777</v>
+        <v>92612</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9378,21 +9372,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9402,13 +9396,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476804</v>
+        <v>476882</v>
       </c>
       <c r="R86" t="n">
-        <v>6854643</v>
+        <v>6854669</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9452,22 +9446,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127386834</v>
+        <v>127369891</v>
       </c>
       <c r="B87" t="n">
-        <v>80081</v>
+        <v>80156</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9475,40 +9469,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476869</v>
+        <v>476866</v>
       </c>
       <c r="R87" t="n">
-        <v>6854645</v>
+        <v>6854642</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9535,62 +9526,71 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127386080</v>
+        <v>127386828</v>
       </c>
       <c r="B88" t="n">
-        <v>92632</v>
+        <v>80121</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476799</v>
+        <v>476869</v>
       </c>
       <c r="R88" t="n">
-        <v>6854562</v>
+        <v>6854645</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9650,60 +9650,72 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386129</v>
+        <v>127386840</v>
       </c>
       <c r="B89" t="n">
-        <v>92620</v>
+        <v>98448</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476790</v>
+        <v>476852</v>
       </c>
       <c r="R89" t="n">
-        <v>6854633</v>
+        <v>6854630</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9741,66 +9753,71 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127386828</v>
+        <v>127388974</v>
       </c>
       <c r="B90" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476869</v>
+        <v>476859</v>
       </c>
       <c r="R90" t="n">
-        <v>6854645</v>
+        <v>6854547</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9838,78 +9855,67 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127386840</v>
+        <v>127386080</v>
       </c>
       <c r="B91" t="n">
-        <v>98448</v>
+        <v>92632</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476852</v>
+        <v>476799</v>
       </c>
       <c r="R91" t="n">
-        <v>6854630</v>
+        <v>6854562</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9947,71 +9953,66 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127388974</v>
+        <v>127386129</v>
       </c>
       <c r="B92" t="n">
-        <v>98448</v>
+        <v>92620</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476859</v>
+        <v>476790</v>
       </c>
       <c r="R92" t="n">
-        <v>6854547</v>
+        <v>6854633</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10049,19 +10050,18 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10780,32 +10780,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127386854</v>
+        <v>127386088</v>
       </c>
       <c r="B100" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10815,13 +10815,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>476899</v>
+        <v>476826</v>
       </c>
       <c r="R100" t="n">
-        <v>6854779</v>
+        <v>6854482</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10865,60 +10865,68 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127386088</v>
+        <v>127386310</v>
       </c>
       <c r="B101" t="n">
-        <v>78776</v>
+        <v>98448</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476826</v>
+        <v>476822</v>
       </c>
       <c r="R101" t="n">
-        <v>6854482</v>
+        <v>6854557</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10956,66 +10964,71 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127386811</v>
+        <v>127388967</v>
       </c>
       <c r="B102" t="n">
-        <v>79607</v>
+        <v>98448</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>476887</v>
+        <v>476843</v>
       </c>
       <c r="R102" t="n">
-        <v>6854810</v>
+        <v>6854525</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11053,25 +11066,26 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127386310</v>
+        <v>127387594</v>
       </c>
       <c r="B103" t="n">
         <v>98448</v>
@@ -11101,10 +11115,14 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
@@ -11114,13 +11132,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>476822</v>
+        <v>476850</v>
       </c>
       <c r="R103" t="n">
-        <v>6854557</v>
+        <v>6854546</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11165,72 +11183,60 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127387594</v>
+        <v>127386854</v>
       </c>
       <c r="B104" t="n">
-        <v>98448</v>
+        <v>92620</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>476850</v>
+        <v>476899</v>
       </c>
       <c r="R104" t="n">
-        <v>6854546</v>
+        <v>6854779</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11268,71 +11274,66 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127388967</v>
+        <v>127386811</v>
       </c>
       <c r="B105" t="n">
-        <v>98448</v>
+        <v>79607</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>476843</v>
+        <v>476887</v>
       </c>
       <c r="R105" t="n">
-        <v>6854525</v>
+        <v>6854810</v>
       </c>
       <c r="S105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11370,19 +11371,18 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127369215</v>
       </c>
       <c r="B2" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127369923</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127386081</v>
       </c>
       <c r="B4" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,48 +986,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127371169</v>
+        <v>127386839</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476901</v>
+        <v>476824</v>
       </c>
       <c r="R5" t="n">
-        <v>6854667</v>
+        <v>6854630</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,19 +1054,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,65 +1071,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127386314</v>
+        <v>127371169</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>91352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476867</v>
+        <v>476901</v>
       </c>
       <c r="R6" t="n">
-        <v>6854648</v>
+        <v>6854667</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1169,40 +1151,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127386839</v>
+        <v>127386098</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,20 +1218,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476824</v>
+        <v>476851</v>
       </c>
       <c r="R7" t="n">
-        <v>6854630</v>
+        <v>6854670</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,28 +1273,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127386098</v>
+        <v>127386314</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,22 +1322,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476851</v>
+        <v>476867</v>
       </c>
       <c r="R8" t="n">
-        <v>6854670</v>
+        <v>6854648</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,12 +1386,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1401,7 +1401,7 @@
         <v>127386809</v>
       </c>
       <c r="B9" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127388142</v>
+        <v>127386850</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,45 +1506,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476840</v>
+        <v>476896</v>
       </c>
       <c r="R10" t="n">
-        <v>6854642</v>
+        <v>6854789</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,61 +1580,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127388973</v>
+        <v>127388142</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476828</v>
+        <v>476840</v>
       </c>
       <c r="R11" t="n">
-        <v>6854626</v>
+        <v>6854642</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1683,29 +1679,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127371659</v>
+        <v>127387592</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,20 +1725,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476822</v>
+        <v>476796</v>
       </c>
       <c r="R12" t="n">
-        <v>6854617</v>
+        <v>6854627</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,19 +1777,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:39</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,18 +1793,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1812,7 +1815,7 @@
         <v>127387597</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127387592</v>
+        <v>127388973</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,30 +1952,22 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476796</v>
+        <v>476828</v>
       </c>
       <c r="R14" t="n">
-        <v>6854627</v>
+        <v>6854626</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2002,11 +1997,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,22 +2012,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127388966</v>
+        <v>127371659</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2052,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476792</v>
+        <v>476822</v>
       </c>
       <c r="R15" t="n">
-        <v>6854646</v>
+        <v>6854617</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2106,78 +2092,91 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127386850</v>
+        <v>127388966</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476896</v>
+        <v>476792</v>
       </c>
       <c r="R16" t="n">
-        <v>6854789</v>
+        <v>6854646</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,63 +2214,68 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127388145</v>
+        <v>127388963</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476840</v>
+        <v>476856</v>
       </c>
       <c r="R17" t="n">
-        <v>6854642</v>
+        <v>6854653</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2312,67 +2316,64 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127388963</v>
+        <v>127388145</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476856</v>
+        <v>476840</v>
       </c>
       <c r="R18" t="n">
-        <v>6854653</v>
+        <v>6854642</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2413,29 +2414,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127386305</v>
+        <v>127386099</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,26 +2462,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476855</v>
+        <v>476865</v>
       </c>
       <c r="R19" t="n">
-        <v>6854627</v>
+        <v>6854478</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,22 +2522,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127386099</v>
+        <v>127386305</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,22 +2564,26 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476865</v>
+        <v>476855</v>
       </c>
       <c r="R20" t="n">
-        <v>6854478</v>
+        <v>6854627</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,44 +2628,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127386848</v>
+        <v>127386067</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>79052</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476840</v>
+        <v>476821</v>
       </c>
       <c r="R21" t="n">
-        <v>6854622</v>
+        <v>6854543</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,51 +2719,50 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127386067</v>
+        <v>127386848</v>
       </c>
       <c r="B22" t="n">
-        <v>79050</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,13 +2772,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476821</v>
+        <v>476840</v>
       </c>
       <c r="R22" t="n">
-        <v>6854543</v>
+        <v>6854622</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2817,71 +2816,64 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127386302</v>
+        <v>127386319</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476828</v>
+        <v>476821</v>
       </c>
       <c r="R23" t="n">
-        <v>6854531</v>
+        <v>6854475</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -2922,7 +2914,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2941,56 +2932,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127388976</v>
+        <v>127369424</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>80152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476880</v>
+        <v>476879</v>
       </c>
       <c r="R24" t="n">
-        <v>6854486</v>
+        <v>6854650</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3017,82 +3000,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127386102</v>
+        <v>127387585</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>80123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476821</v>
+        <v>476865</v>
       </c>
       <c r="R25" t="n">
-        <v>6854465</v>
+        <v>6854638</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3130,19 +3118,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Elis Lewin, Erik Christiansson, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3152,7 +3139,7 @@
         <v>127387581</v>
       </c>
       <c r="B26" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,52 +3226,60 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karin Berg Andersson, Filippa Paperin, Nadja Karlsson, Alice Helander, Elias Blad, Malte Lindberg, Emilia Blixt, Tilde Carlinger, Elis Lewin, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127386319</v>
+        <v>127386302</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476821</v>
+        <v>476828</v>
       </c>
       <c r="R27" t="n">
-        <v>6854475</v>
+        <v>6854531</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3325,6 +3320,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3343,48 +3339,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127369424</v>
+        <v>127388976</v>
       </c>
       <c r="B28" t="n">
-        <v>80150</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476879</v>
+        <v>476880</v>
       </c>
       <c r="R28" t="n">
-        <v>6854650</v>
+        <v>6854486</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3411,87 +3415,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127387585</v>
+        <v>127386102</v>
       </c>
       <c r="B29" t="n">
-        <v>80121</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476865</v>
+        <v>476821</v>
       </c>
       <c r="R29" t="n">
-        <v>6854638</v>
+        <v>6854465</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3529,70 +3528,64 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127386295</v>
+        <v>127370759</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>80158</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476888</v>
+        <v>476877</v>
       </c>
       <c r="R30" t="n">
-        <v>6854664</v>
+        <v>6854663</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3622,40 +3615,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127371357</v>
+        <v>127386295</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>91352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,34 +3665,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476901</v>
+        <v>476888</v>
       </c>
       <c r="R31" t="n">
-        <v>6854667</v>
+        <v>6854664</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -3720,66 +3729,57 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127370759</v>
+        <v>127371357</v>
       </c>
       <c r="B32" t="n">
-        <v>80156</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476877</v>
+        <v>476901</v>
       </c>
       <c r="R32" t="n">
-        <v>6854663</v>
+        <v>6854667</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3866,10 +3866,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127386111</v>
+        <v>127386299</v>
       </c>
       <c r="B33" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3894,20 +3894,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476831</v>
+        <v>476817</v>
       </c>
       <c r="R33" t="n">
-        <v>6854682</v>
+        <v>6854465</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3945,18 +3953,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3966,7 +3975,7 @@
         <v>127386100</v>
       </c>
       <c r="B34" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4065,10 +4074,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127386299</v>
+        <v>127386111</v>
       </c>
       <c r="B35" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,28 +4102,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476817</v>
+        <v>476831</v>
       </c>
       <c r="R35" t="n">
-        <v>6854465</v>
+        <v>6854682</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4152,19 +4153,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
         <v>127386303</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>127386112</v>
       </c>
       <c r="B37" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127388975</v>
+        <v>127386108</v>
       </c>
       <c r="B38" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4402,24 +4402,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476864</v>
+        <v>476830</v>
       </c>
       <c r="R38" t="n">
-        <v>6854487</v>
+        <v>6854468</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4457,67 +4453,78 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127386117</v>
+        <v>127387587</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476835</v>
+        <v>476850</v>
       </c>
       <c r="R39" t="n">
-        <v>6854539</v>
+        <v>6854640</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4555,28 +4562,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin, Erik Christiansson, Elis Lewin, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127386108</v>
+        <v>127388975</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4601,20 +4609,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476830</v>
+        <v>476864</v>
       </c>
       <c r="R40" t="n">
-        <v>6854468</v>
+        <v>6854487</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4652,78 +4664,67 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127387587</v>
+        <v>127386117</v>
       </c>
       <c r="B41" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476850</v>
+        <v>476835</v>
       </c>
       <c r="R41" t="n">
-        <v>6854640</v>
+        <v>6854539</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4761,29 +4762,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127386311</v>
+        <v>127387586</v>
       </c>
       <c r="B42" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4808,28 +4808,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476828</v>
+        <v>476859</v>
       </c>
       <c r="R42" t="n">
-        <v>6854592</v>
+        <v>6854667</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4861,40 +4853,34 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 blommande</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127387586</v>
+        <v>127369992</v>
       </c>
       <c r="B43" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,19 +4906,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
         <v>476859</v>
       </c>
       <c r="R43" t="n">
-        <v>6854667</v>
+        <v>6854645</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4959,9 +4950,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4976,22 +4977,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127369992</v>
+        <v>127386311</v>
       </c>
       <c r="B44" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5016,25 +5017,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476859</v>
+        <v>476828</v>
       </c>
       <c r="R44" t="n">
-        <v>6854645</v>
+        <v>6854592</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5061,19 +5065,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:41</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5082,18 +5081,19 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5103,7 +5103,7 @@
         <v>127386808</v>
       </c>
       <c r="B45" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>127386078</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5294,10 +5294,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127370572</v>
+        <v>127386087</v>
       </c>
       <c r="B47" t="n">
-        <v>96700</v>
+        <v>78778</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,37 +5305,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476857</v>
+        <v>476780</v>
       </c>
       <c r="R47" t="n">
-        <v>6854654</v>
+        <v>6854482</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5362,19 +5362,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5389,12 +5379,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5404,7 +5394,7 @@
         <v>127371200</v>
       </c>
       <c r="B48" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5508,10 +5498,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127386087</v>
+        <v>127371346</v>
       </c>
       <c r="B49" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5539,17 +5529,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476780</v>
+        <v>476826</v>
       </c>
       <c r="R49" t="n">
-        <v>6854482</v>
+        <v>6854459</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5576,9 +5566,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5593,12 +5593,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5608,7 +5608,7 @@
         <v>127386089</v>
       </c>
       <c r="B50" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5702,10 +5702,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127371346</v>
+        <v>127370572</v>
       </c>
       <c r="B51" t="n">
-        <v>78776</v>
+        <v>96702</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476826</v>
+        <v>476857</v>
       </c>
       <c r="R51" t="n">
-        <v>6854459</v>
+        <v>6854654</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5797,22 +5797,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386312</v>
+        <v>127387598</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,20 +5837,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476860</v>
+        <v>476767</v>
       </c>
       <c r="R52" t="n">
-        <v>6854625</v>
+        <v>6854589</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5888,28 +5900,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127387598</v>
+        <v>127386312</v>
       </c>
       <c r="B53" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5934,32 +5947,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476767</v>
+        <v>476860</v>
       </c>
       <c r="R53" t="n">
-        <v>6854589</v>
+        <v>6854625</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5997,19 +5998,18 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6019,7 +6019,7 @@
         <v>127386838</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>127370418</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>127388147</v>
       </c>
       <c r="B56" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>127372315</v>
       </c>
       <c r="B57" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>127386849</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6534,10 +6534,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127387593</v>
+        <v>127387589</v>
       </c>
       <c r="B59" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476780</v>
+        <v>476812</v>
       </c>
       <c r="R59" t="n">
-        <v>6854617</v>
+        <v>6854623</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6649,10 +6649,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127387589</v>
+        <v>127386313</v>
       </c>
       <c r="B60" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6679,14 +6679,10 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -6696,13 +6692,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476812</v>
+        <v>476881</v>
       </c>
       <c r="R60" t="n">
-        <v>6854623</v>
+        <v>6854650</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6732,11 +6728,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6752,22 +6743,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127386313</v>
+        <v>127371630</v>
       </c>
       <c r="B61" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6794,26 +6785,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476881</v>
+        <v>476874</v>
       </c>
       <c r="R61" t="n">
-        <v>6854650</v>
+        <v>6854475</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6840,40 +6832,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127371630</v>
+        <v>127387593</v>
       </c>
       <c r="B62" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6900,27 +6901,30 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476874</v>
+        <v>476780</v>
       </c>
       <c r="R62" t="n">
-        <v>6854475</v>
+        <v>6854617</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6947,19 +6951,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>16:38</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6968,18 +6967,19 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6989,7 +6989,7 @@
         <v>127387590</v>
       </c>
       <c r="B63" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>127386068</v>
       </c>
       <c r="B64" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7198,10 +7198,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127386308</v>
+        <v>127386096</v>
       </c>
       <c r="B65" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7228,26 +7228,22 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476825</v>
+        <v>476806</v>
       </c>
       <c r="R65" t="n">
-        <v>6854551</v>
+        <v>6854483</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7292,60 +7288,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386110</v>
+        <v>127371302</v>
       </c>
       <c r="B66" t="n">
-        <v>98448</v>
+        <v>78779</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476818</v>
+        <v>476826</v>
       </c>
       <c r="R66" t="n">
-        <v>6854660</v>
+        <v>6854459</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7372,9 +7368,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7389,22 +7395,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386842</v>
+        <v>127386308</v>
       </c>
       <c r="B67" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7429,20 +7435,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476869</v>
+        <v>476825</v>
       </c>
       <c r="R67" t="n">
-        <v>6854655</v>
+        <v>6854551</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7480,28 +7494,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386096</v>
+        <v>127386110</v>
       </c>
       <c r="B68" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7526,21 +7541,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476806</v>
+        <v>476818</v>
       </c>
       <c r="R68" t="n">
-        <v>6854483</v>
+        <v>6854660</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7581,7 +7592,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7600,48 +7610,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127371302</v>
+        <v>127386842</v>
       </c>
       <c r="B69" t="n">
-        <v>78777</v>
+        <v>98450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476826</v>
+        <v>476869</v>
       </c>
       <c r="R69" t="n">
-        <v>6854459</v>
+        <v>6854655</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7668,19 +7678,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7695,22 +7695,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127388970</v>
+        <v>127371242</v>
       </c>
       <c r="B70" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7737,22 +7737,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>476836</v>
+        <v>476826</v>
       </c>
       <c r="R70" t="n">
-        <v>6854641</v>
+        <v>6854459</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7779,30 +7779,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7812,7 +7821,7 @@
         <v>127387596</v>
       </c>
       <c r="B71" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7919,10 +7928,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127371242</v>
+        <v>127388970</v>
       </c>
       <c r="B72" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7949,22 +7958,22 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>476826</v>
+        <v>476836</v>
       </c>
       <c r="R72" t="n">
-        <v>6854459</v>
+        <v>6854641</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7991,39 +8000,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8033,7 +8033,7 @@
         <v>127386109</v>
       </c>
       <c r="B73" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8127,48 +8127,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127386841</v>
+        <v>127369233</v>
       </c>
       <c r="B74" t="n">
-        <v>98448</v>
+        <v>79052</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>476865</v>
+        <v>476907</v>
       </c>
       <c r="R74" t="n">
-        <v>6854629</v>
+        <v>6854785</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8195,9 +8195,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8212,12 +8222,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8227,7 +8237,7 @@
         <v>127388972</v>
       </c>
       <c r="B75" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8329,7 +8339,7 @@
         <v>127387595</v>
       </c>
       <c r="B76" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8439,7 +8449,7 @@
         <v>127386097</v>
       </c>
       <c r="B77" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8538,48 +8548,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127369233</v>
+        <v>127386841</v>
       </c>
       <c r="B78" t="n">
-        <v>79050</v>
+        <v>98450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476907</v>
+        <v>476865</v>
       </c>
       <c r="R78" t="n">
-        <v>6854785</v>
+        <v>6854629</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8606,19 +8616,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8633,65 +8633,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127386315</v>
+        <v>127369660</v>
       </c>
       <c r="B79" t="n">
-        <v>98448</v>
+        <v>96702</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476883</v>
+        <v>476880</v>
       </c>
       <c r="R79" t="n">
-        <v>6854657</v>
+        <v>6854794</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8721,82 +8713,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127386103</v>
+        <v>127386820</v>
       </c>
       <c r="B80" t="n">
-        <v>98448</v>
+        <v>92614</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476832</v>
+        <v>476882</v>
       </c>
       <c r="R80" t="n">
-        <v>6854485</v>
+        <v>6854669</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8834,75 +8831,66 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127386300</v>
+        <v>127369891</v>
       </c>
       <c r="B81" t="n">
-        <v>98448</v>
+        <v>80158</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476830</v>
+        <v>476866</v>
       </c>
       <c r="R81" t="n">
-        <v>6854480</v>
+        <v>6854642</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8929,40 +8917,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386843</v>
+        <v>127386300</v>
       </c>
       <c r="B82" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8987,20 +8984,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476842</v>
+        <v>476830</v>
       </c>
       <c r="R82" t="n">
-        <v>6854652</v>
+        <v>6854480</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9038,66 +9043,75 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386082</v>
+        <v>127386315</v>
       </c>
       <c r="B83" t="n">
-        <v>78777</v>
+        <v>98450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476804</v>
+        <v>476883</v>
       </c>
       <c r="R83" t="n">
-        <v>6854643</v>
+        <v>6854657</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9135,69 +9149,71 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386834</v>
+        <v>127386103</v>
       </c>
       <c r="B84" t="n">
-        <v>80081</v>
+        <v>98450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476869</v>
+        <v>476832</v>
       </c>
       <c r="R84" t="n">
-        <v>6854645</v>
+        <v>6854485</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9242,60 +9258,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127369660</v>
+        <v>127386843</v>
       </c>
       <c r="B85" t="n">
-        <v>96700</v>
+        <v>98450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476880</v>
+        <v>476842</v>
       </c>
       <c r="R85" t="n">
-        <v>6854794</v>
+        <v>6854652</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9322,19 +9338,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9349,22 +9355,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386820</v>
+        <v>127386082</v>
       </c>
       <c r="B86" t="n">
-        <v>92612</v>
+        <v>78779</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9372,21 +9378,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9396,13 +9402,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476882</v>
+        <v>476804</v>
       </c>
       <c r="R86" t="n">
-        <v>6854669</v>
+        <v>6854643</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9446,22 +9452,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127369891</v>
+        <v>127386834</v>
       </c>
       <c r="B87" t="n">
-        <v>80156</v>
+        <v>80083</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9469,37 +9475,40 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476866</v>
+        <v>476869</v>
       </c>
       <c r="R87" t="n">
-        <v>6854642</v>
+        <v>6854645</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9526,39 +9535,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9568,7 +9568,7 @@
         <v>127386828</v>
       </c>
       <c r="B88" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9662,60 +9662,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386840</v>
+        <v>127386080</v>
       </c>
       <c r="B89" t="n">
-        <v>98448</v>
+        <v>92634</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476852</v>
+        <v>476799</v>
       </c>
       <c r="R89" t="n">
-        <v>6854630</v>
+        <v>6854562</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9753,71 +9741,66 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127388974</v>
+        <v>127386129</v>
       </c>
       <c r="B90" t="n">
-        <v>98448</v>
+        <v>92622</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476859</v>
+        <v>476790</v>
       </c>
       <c r="R90" t="n">
-        <v>6854547</v>
+        <v>6854633</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9855,67 +9838,70 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127386080</v>
+        <v>127388974</v>
       </c>
       <c r="B91" t="n">
-        <v>92632</v>
+        <v>98450</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476799</v>
+        <v>476859</v>
       </c>
       <c r="R91" t="n">
-        <v>6854562</v>
+        <v>6854547</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9953,66 +9939,79 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127386129</v>
+        <v>127386840</v>
       </c>
       <c r="B92" t="n">
-        <v>92620</v>
+        <v>98450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476790</v>
+        <v>476852</v>
       </c>
       <c r="R92" t="n">
-        <v>6854633</v>
+        <v>6854630</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10050,66 +10049,71 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127386320</v>
+        <v>127386101</v>
       </c>
       <c r="B93" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>476832</v>
+        <v>476785</v>
       </c>
       <c r="R93" t="n">
-        <v>6854631</v>
+        <v>6854487</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10147,28 +10151,29 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127386101</v>
+        <v>127386837</v>
       </c>
       <c r="B94" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10193,24 +10198,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>476785</v>
+        <v>476808</v>
       </c>
       <c r="R94" t="n">
-        <v>6854487</v>
+        <v>6854629</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10248,51 +10249,50 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127386837</v>
+        <v>127386320</v>
       </c>
       <c r="B95" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10302,13 +10302,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>476808</v>
+        <v>476832</v>
       </c>
       <c r="R95" t="n">
-        <v>6854629</v>
+        <v>6854631</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10352,22 +10352,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127388141</v>
+        <v>127370318</v>
       </c>
       <c r="B96" t="n">
-        <v>57658</v>
+        <v>80123</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10375,45 +10375,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476834</v>
+        <v>476810</v>
       </c>
       <c r="R96" t="n">
-        <v>6854535</v>
+        <v>6854587</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10440,9 +10432,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10457,22 +10459,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Filippa Paperin, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127370318</v>
+        <v>127388141</v>
       </c>
       <c r="B97" t="n">
-        <v>80121</v>
+        <v>57660</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10480,37 +10482,45 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476810</v>
+        <v>476834</v>
       </c>
       <c r="R97" t="n">
-        <v>6854587</v>
+        <v>6854535</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10537,19 +10547,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10564,12 +10564,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10579,7 +10579,7 @@
         <v>127386107</v>
       </c>
       <c r="B98" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>127386104</v>
       </c>
       <c r="B99" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>127386088</v>
       </c>
       <c r="B100" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10877,56 +10877,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127386310</v>
+        <v>127386854</v>
       </c>
       <c r="B101" t="n">
-        <v>98448</v>
+        <v>92622</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476822</v>
+        <v>476899</v>
       </c>
       <c r="R101" t="n">
-        <v>6854557</v>
+        <v>6854779</v>
       </c>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10964,71 +10956,66 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127388967</v>
+        <v>127386811</v>
       </c>
       <c r="B102" t="n">
-        <v>98448</v>
+        <v>79609</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>476843</v>
+        <v>476887</v>
       </c>
       <c r="R102" t="n">
-        <v>6854525</v>
+        <v>6854810</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11066,29 +11053,28 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127387594</v>
+        <v>127386310</v>
       </c>
       <c r="B103" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11115,14 +11101,10 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
@@ -11132,13 +11114,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>476850</v>
+        <v>476822</v>
       </c>
       <c r="R103" t="n">
-        <v>6854546</v>
+        <v>6854557</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11183,60 +11165,64 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127386854</v>
+        <v>127388967</v>
       </c>
       <c r="B104" t="n">
-        <v>92620</v>
+        <v>98450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>476899</v>
+        <v>476843</v>
       </c>
       <c r="R104" t="n">
-        <v>6854779</v>
+        <v>6854525</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11274,66 +11260,79 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127386811</v>
+        <v>127387594</v>
       </c>
       <c r="B105" t="n">
-        <v>79607</v>
+        <v>98450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>476887</v>
+        <v>476850</v>
       </c>
       <c r="R105" t="n">
-        <v>6854810</v>
+        <v>6854546</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11371,18 +11370,19 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127386081</v>
+        <v>127371169</v>
       </c>
       <c r="B4" t="n">
-        <v>78779</v>
+        <v>91352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476867</v>
+        <v>476901</v>
       </c>
       <c r="R4" t="n">
-        <v>6854478</v>
+        <v>6854667</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,9 +957,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,44 +984,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127386839</v>
+        <v>127386081</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476824</v>
+        <v>476867</v>
       </c>
       <c r="R5" t="n">
-        <v>6854630</v>
+        <v>6854478</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,57 +1081,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127371169</v>
+        <v>127386314</v>
       </c>
       <c r="B6" t="n">
-        <v>91352</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476901</v>
+        <v>476867</v>
       </c>
       <c r="R6" t="n">
-        <v>6854667</v>
+        <v>6854648</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1151,46 +1169,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127386098</v>
+        <v>127386839</v>
       </c>
       <c r="B7" t="n">
         <v>98450</v>
@@ -1218,24 +1227,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476851</v>
+        <v>476824</v>
       </c>
       <c r="R7" t="n">
-        <v>6854670</v>
+        <v>6854630</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1273,26 +1278,25 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127386314</v>
+        <v>127386098</v>
       </c>
       <c r="B8" t="n">
         <v>98450</v>
@@ -1322,26 +1326,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476867</v>
+        <v>476851</v>
       </c>
       <c r="R8" t="n">
-        <v>6854648</v>
+        <v>6854670</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,22 +1386,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127386809</v>
+        <v>127388142</v>
       </c>
       <c r="B9" t="n">
-        <v>79052</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1409,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476898</v>
+        <v>476840</v>
       </c>
       <c r="R9" t="n">
-        <v>6854784</v>
+        <v>6854642</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1483,60 +1491,64 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127386850</v>
+        <v>127388973</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476896</v>
+        <v>476828</v>
       </c>
       <c r="R10" t="n">
-        <v>6854789</v>
+        <v>6854626</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,71 +1586,64 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127388142</v>
+        <v>127371659</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476840</v>
+        <v>476822</v>
       </c>
       <c r="R11" t="n">
-        <v>6854642</v>
+        <v>6854617</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1668,9 +1673,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,19 +1700,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127387592</v>
+        <v>127387597</v>
       </c>
       <c r="B12" t="n">
         <v>98450</v>
@@ -1727,7 +1742,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1744,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476796</v>
+        <v>476831</v>
       </c>
       <c r="R12" t="n">
-        <v>6854627</v>
+        <v>6854622</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1780,11 +1795,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127387597</v>
+        <v>127387592</v>
       </c>
       <c r="B13" t="n">
         <v>98450</v>
@@ -1842,7 +1852,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1859,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476831</v>
+        <v>476796</v>
       </c>
       <c r="R13" t="n">
-        <v>6854622</v>
+        <v>6854627</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1895,6 +1905,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1922,7 +1937,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127388973</v>
+        <v>127388966</v>
       </c>
       <c r="B14" t="n">
         <v>98450</v>
@@ -1952,7 +1967,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1961,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476828</v>
+        <v>476792</v>
       </c>
       <c r="R14" t="n">
-        <v>6854626</v>
+        <v>6854646</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2024,48 +2039,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127371659</v>
+        <v>127386809</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476822</v>
+        <v>476898</v>
       </c>
       <c r="R15" t="n">
-        <v>6854617</v>
+        <v>6854784</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2092,19 +2107,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,64 +2124,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127388966</v>
+        <v>127386850</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476792</v>
+        <v>476896</v>
       </c>
       <c r="R16" t="n">
-        <v>6854646</v>
+        <v>6854789</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2214,68 +2215,63 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127388963</v>
+        <v>127388145</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476856</v>
+        <v>476840</v>
       </c>
       <c r="R17" t="n">
-        <v>6854653</v>
+        <v>6854642</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2316,64 +2312,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127388145</v>
+        <v>127388963</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476840</v>
+        <v>476856</v>
       </c>
       <c r="R18" t="n">
-        <v>6854642</v>
+        <v>6854653</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2414,25 +2413,26 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127386099</v>
+        <v>127386305</v>
       </c>
       <c r="B19" t="n">
         <v>98450</v>
@@ -2462,22 +2462,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476865</v>
+        <v>476855</v>
       </c>
       <c r="R19" t="n">
-        <v>6854478</v>
+        <v>6854627</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2522,19 +2526,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127386305</v>
+        <v>127386099</v>
       </c>
       <c r="B20" t="n">
         <v>98450</v>
@@ -2564,26 +2568,22 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476855</v>
+        <v>476865</v>
       </c>
       <c r="R20" t="n">
-        <v>6854627</v>
+        <v>6854478</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2932,48 +2932,56 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127369424</v>
+        <v>127386302</v>
       </c>
       <c r="B24" t="n">
-        <v>80152</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476879</v>
+        <v>476828</v>
       </c>
       <c r="R24" t="n">
-        <v>6854650</v>
+        <v>6854531</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3000,87 +3008,86 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127387585</v>
+        <v>127388976</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476865</v>
+        <v>476880</v>
       </c>
       <c r="R25" t="n">
-        <v>6854638</v>
+        <v>6854486</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3118,66 +3125,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Elis Lewin, Erik Christiansson, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127387581</v>
+        <v>127386102</v>
       </c>
       <c r="B26" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476827</v>
+        <v>476821</v>
       </c>
       <c r="R26" t="n">
-        <v>6854629</v>
+        <v>6854465</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3215,74 +3227,67 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Filippa Paperin, Nadja Karlsson, Alice Helander, Elias Blad, Malte Lindberg, Emilia Blixt, Tilde Carlinger, Elis Lewin, Erik Christiansson</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127386302</v>
+        <v>127387585</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476828</v>
+        <v>476865</v>
       </c>
       <c r="R27" t="n">
-        <v>6854531</v>
+        <v>6854638</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3320,75 +3325,66 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127388976</v>
+        <v>127369424</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>80152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476880</v>
+        <v>476879</v>
       </c>
       <c r="R28" t="n">
-        <v>6854486</v>
+        <v>6854650</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3415,82 +3411,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127386102</v>
+        <v>127387581</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476821</v>
+        <v>476827</v>
       </c>
       <c r="R29" t="n">
-        <v>6854465</v>
+        <v>6854629</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3528,64 +3529,70 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127370759</v>
+        <v>127386295</v>
       </c>
       <c r="B30" t="n">
-        <v>80158</v>
+        <v>91352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476877</v>
+        <v>476888</v>
       </c>
       <c r="R30" t="n">
-        <v>6854663</v>
+        <v>6854664</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3615,91 +3622,75 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127386295</v>
+        <v>127370759</v>
       </c>
       <c r="B31" t="n">
-        <v>91352</v>
+        <v>80158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476888</v>
+        <v>476877</v>
       </c>
       <c r="R31" t="n">
-        <v>6854664</v>
+        <v>6854663</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -3729,30 +3720,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3866,7 +3866,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127386299</v>
+        <v>127386111</v>
       </c>
       <c r="B33" t="n">
         <v>98450</v>
@@ -3894,28 +3894,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476817</v>
+        <v>476831</v>
       </c>
       <c r="R33" t="n">
-        <v>6854465</v>
+        <v>6854682</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3953,19 +3945,18 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4074,7 +4065,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127386111</v>
+        <v>127386299</v>
       </c>
       <c r="B35" t="n">
         <v>98450</v>
@@ -4102,20 +4093,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476831</v>
+        <v>476817</v>
       </c>
       <c r="R35" t="n">
-        <v>6854682</v>
+        <v>6854465</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4153,18 +4152,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4374,32 +4374,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127386108</v>
+        <v>127386117</v>
       </c>
       <c r="B38" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476830</v>
+        <v>476835</v>
       </c>
       <c r="R38" t="n">
-        <v>6854468</v>
+        <v>6854539</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4471,7 +4471,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127387587</v>
+        <v>127386108</v>
       </c>
       <c r="B39" t="n">
         <v>98450</v>
@@ -4499,32 +4499,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476850</v>
+        <v>476830</v>
       </c>
       <c r="R39" t="n">
-        <v>6854640</v>
+        <v>6854468</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4562,26 +4550,25 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin, Erik Christiansson, Elis Lewin, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127388975</v>
+        <v>127387587</v>
       </c>
       <c r="B40" t="n">
         <v>98450</v>
@@ -4611,22 +4598,30 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476864</v>
+        <v>476850</v>
       </c>
       <c r="R40" t="n">
-        <v>6854487</v>
+        <v>6854640</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4671,60 +4666,68 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127386117</v>
+        <v>127386311</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476835</v>
+        <v>476828</v>
       </c>
       <c r="R41" t="n">
-        <v>6854539</v>
+        <v>6854592</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4756,24 +4759,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4989,7 +4998,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127386311</v>
+        <v>127388975</v>
       </c>
       <c r="B44" t="n">
         <v>98450</v>
@@ -5019,23 +5028,19 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476828</v>
+        <v>476864</v>
       </c>
       <c r="R44" t="n">
-        <v>6854592</v>
+        <v>6854487</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5070,11 +5075,6 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>1 blommande</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5088,12 +5088,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5294,10 +5294,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127386087</v>
+        <v>127370572</v>
       </c>
       <c r="B47" t="n">
-        <v>78778</v>
+        <v>96702</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,37 +5305,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476780</v>
+        <v>476857</v>
       </c>
       <c r="R47" t="n">
-        <v>6854482</v>
+        <v>6854654</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5362,9 +5362,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5379,12 +5389,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5498,7 +5508,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127371346</v>
+        <v>127386089</v>
       </c>
       <c r="B49" t="n">
         <v>78778</v>
@@ -5529,17 +5539,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476826</v>
+        <v>476838</v>
       </c>
       <c r="R49" t="n">
-        <v>6854459</v>
+        <v>6854681</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5566,19 +5576,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5593,19 +5593,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127386089</v>
+        <v>127386087</v>
       </c>
       <c r="B50" t="n">
         <v>78778</v>
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476838</v>
+        <v>476780</v>
       </c>
       <c r="R50" t="n">
-        <v>6854681</v>
+        <v>6854482</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5702,10 +5702,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127370572</v>
+        <v>127371346</v>
       </c>
       <c r="B51" t="n">
-        <v>96702</v>
+        <v>78778</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476857</v>
+        <v>476826</v>
       </c>
       <c r="R51" t="n">
-        <v>6854654</v>
+        <v>6854459</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5797,19 +5797,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127387598</v>
+        <v>127386312</v>
       </c>
       <c r="B52" t="n">
         <v>98450</v>
@@ -5837,32 +5837,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476767</v>
+        <v>476860</v>
       </c>
       <c r="R52" t="n">
-        <v>6854589</v>
+        <v>6854625</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5900,26 +5888,25 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127386312</v>
+        <v>127387598</v>
       </c>
       <c r="B53" t="n">
         <v>98450</v>
@@ -5947,20 +5934,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476860</v>
+        <v>476767</v>
       </c>
       <c r="R53" t="n">
-        <v>6854625</v>
+        <v>6854589</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5998,18 +5997,19 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6113,45 +6113,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127370418</v>
+        <v>127388147</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476867</v>
+        <v>476787</v>
       </c>
       <c r="R55" t="n">
-        <v>6854691</v>
+        <v>6854642</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6181,49 +6188,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127388147</v>
+        <v>127372315</v>
       </c>
       <c r="B56" t="n">
-        <v>92622</v>
+        <v>56855</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6231,41 +6229,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476787</v>
+        <v>476894</v>
       </c>
       <c r="R56" t="n">
-        <v>6854642</v>
+        <v>6854772</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6295,80 +6291,84 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127372315</v>
+        <v>127370418</v>
       </c>
       <c r="B57" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476894</v>
+        <v>476867</v>
       </c>
       <c r="R57" t="n">
-        <v>6854772</v>
+        <v>6854691</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6534,7 +6534,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127387589</v>
+        <v>127387593</v>
       </c>
       <c r="B59" t="n">
         <v>98450</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476812</v>
+        <v>476780</v>
       </c>
       <c r="R59" t="n">
-        <v>6854623</v>
+        <v>6854617</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127386313</v>
+        <v>127387589</v>
       </c>
       <c r="B60" t="n">
         <v>98450</v>
@@ -6679,10 +6679,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -6692,13 +6696,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476881</v>
+        <v>476812</v>
       </c>
       <c r="R60" t="n">
-        <v>6854650</v>
+        <v>6854623</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6728,6 +6732,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6743,19 +6752,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127371630</v>
+        <v>127386313</v>
       </c>
       <c r="B61" t="n">
         <v>98450</v>
@@ -6785,27 +6794,26 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476874</v>
+        <v>476881</v>
       </c>
       <c r="R61" t="n">
-        <v>6854475</v>
+        <v>6854650</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6832,46 +6840,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127387593</v>
+        <v>127371630</v>
       </c>
       <c r="B62" t="n">
         <v>98450</v>
@@ -6901,30 +6900,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476780</v>
+        <v>476874</v>
       </c>
       <c r="R62" t="n">
-        <v>6854617</v>
+        <v>6854475</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6951,14 +6947,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6967,19 +6968,18 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7191,59 +7191,55 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127386096</v>
+        <v>127371302</v>
       </c>
       <c r="B65" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476806</v>
+        <v>476826</v>
       </c>
       <c r="R65" t="n">
-        <v>6854483</v>
+        <v>6854459</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7270,78 +7266,95 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127371302</v>
+        <v>127386308</v>
       </c>
       <c r="B66" t="n">
-        <v>78779</v>
+        <v>98450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476826</v>
+        <v>476825</v>
       </c>
       <c r="R66" t="n">
-        <v>6854459</v>
+        <v>6854551</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7368,46 +7381,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386308</v>
+        <v>127386110</v>
       </c>
       <c r="B67" t="n">
         <v>98450</v>
@@ -7435,28 +7439,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476825</v>
+        <v>476818</v>
       </c>
       <c r="R67" t="n">
-        <v>6854551</v>
+        <v>6854660</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7494,26 +7490,25 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386110</v>
+        <v>127386842</v>
       </c>
       <c r="B68" t="n">
         <v>98450</v>
@@ -7548,13 +7543,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476818</v>
+        <v>476869</v>
       </c>
       <c r="R68" t="n">
-        <v>6854660</v>
+        <v>6854655</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7598,19 +7593,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127386842</v>
+        <v>127386096</v>
       </c>
       <c r="B69" t="n">
         <v>98450</v>
@@ -7638,20 +7633,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476869</v>
+        <v>476806</v>
       </c>
       <c r="R69" t="n">
-        <v>6854655</v>
+        <v>6854483</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7689,25 +7688,26 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127371242</v>
+        <v>127388970</v>
       </c>
       <c r="B70" t="n">
         <v>98450</v>
@@ -7737,22 +7737,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>476826</v>
+        <v>476836</v>
       </c>
       <c r="R70" t="n">
-        <v>6854459</v>
+        <v>6854641</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7779,39 +7779,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7928,7 +7919,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127388970</v>
+        <v>127371242</v>
       </c>
       <c r="B72" t="n">
         <v>98450</v>
@@ -7958,22 +7949,22 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>476836</v>
+        <v>476826</v>
       </c>
       <c r="R72" t="n">
-        <v>6854641</v>
+        <v>6854459</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8000,30 +7991,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127388972</v>
+        <v>127386841</v>
       </c>
       <c r="B75" t="n">
         <v>98450</v>
@@ -8262,24 +8262,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476809</v>
+        <v>476865</v>
       </c>
       <c r="R75" t="n">
-        <v>6854638</v>
+        <v>6854629</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8317,26 +8313,25 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127387595</v>
+        <v>127388972</v>
       </c>
       <c r="B76" t="n">
         <v>98450</v>
@@ -8366,30 +8361,22 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476804</v>
+        <v>476809</v>
       </c>
       <c r="R76" t="n">
-        <v>6854628</v>
+        <v>6854638</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8434,19 +8421,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127386097</v>
+        <v>127387595</v>
       </c>
       <c r="B77" t="n">
         <v>98450</v>
@@ -8476,22 +8463,30 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476794</v>
+        <v>476804</v>
       </c>
       <c r="R77" t="n">
-        <v>6854562</v>
+        <v>6854628</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8536,19 +8531,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127386841</v>
+        <v>127386097</v>
       </c>
       <c r="B78" t="n">
         <v>98450</v>
@@ -8576,20 +8571,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476865</v>
+        <v>476794</v>
       </c>
       <c r="R78" t="n">
-        <v>6854629</v>
+        <v>6854562</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8627,50 +8626,51 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127369660</v>
+        <v>127369891</v>
       </c>
       <c r="B79" t="n">
-        <v>96702</v>
+        <v>80158</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>6463</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8680,13 +8680,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476880</v>
+        <v>476866</v>
       </c>
       <c r="R79" t="n">
-        <v>6854794</v>
+        <v>6854642</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8740,12 +8740,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8849,32 +8849,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127369891</v>
+        <v>127369660</v>
       </c>
       <c r="B81" t="n">
-        <v>80158</v>
+        <v>96702</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8884,13 +8884,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476866</v>
+        <v>476880</v>
       </c>
       <c r="R81" t="n">
-        <v>6854642</v>
+        <v>6854794</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8944,19 +8944,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386300</v>
+        <v>127386315</v>
       </c>
       <c r="B82" t="n">
         <v>98450</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J82" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476830</v>
+        <v>476883</v>
       </c>
       <c r="R82" t="n">
-        <v>6854480</v>
+        <v>6854657</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -9062,7 +9062,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386315</v>
+        <v>127386103</v>
       </c>
       <c r="B83" t="n">
         <v>98450</v>
@@ -9092,26 +9092,22 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476883</v>
+        <v>476832</v>
       </c>
       <c r="R83" t="n">
-        <v>6854657</v>
+        <v>6854485</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9156,19 +9152,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386103</v>
+        <v>127386300</v>
       </c>
       <c r="B84" t="n">
         <v>98450</v>
@@ -9198,22 +9194,26 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476832</v>
+        <v>476830</v>
       </c>
       <c r="R84" t="n">
-        <v>6854485</v>
+        <v>6854480</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9258,12 +9258,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9367,48 +9367,51 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386082</v>
+        <v>127386834</v>
       </c>
       <c r="B86" t="n">
-        <v>78779</v>
+        <v>80083</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476804</v>
+        <v>476869</v>
       </c>
       <c r="R86" t="n">
-        <v>6854643</v>
+        <v>6854645</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9446,69 +9449,67 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127386834</v>
+        <v>127386082</v>
       </c>
       <c r="B87" t="n">
-        <v>80083</v>
+        <v>78779</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476869</v>
+        <v>476804</v>
       </c>
       <c r="R87" t="n">
-        <v>6854645</v>
+        <v>6854643</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9546,19 +9547,18 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10576,7 +10576,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127386107</v>
+        <v>127386104</v>
       </c>
       <c r="B98" t="n">
         <v>98450</v>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -10615,10 +10615,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>476800</v>
+        <v>476865</v>
       </c>
       <c r="R98" t="n">
-        <v>6854551</v>
+        <v>6854661</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10678,7 +10678,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127386104</v>
+        <v>127386107</v>
       </c>
       <c r="B99" t="n">
         <v>98450</v>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476865</v>
+        <v>476800</v>
       </c>
       <c r="R99" t="n">
-        <v>6854661</v>
+        <v>6854551</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10780,32 +10780,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127386088</v>
+        <v>127386854</v>
       </c>
       <c r="B100" t="n">
-        <v>78778</v>
+        <v>92622</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10815,13 +10815,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>476826</v>
+        <v>476899</v>
       </c>
       <c r="R100" t="n">
-        <v>6854482</v>
+        <v>6854779</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10865,44 +10865,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127386854</v>
+        <v>127386088</v>
       </c>
       <c r="B101" t="n">
-        <v>92622</v>
+        <v>78778</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10912,13 +10912,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476899</v>
+        <v>476826</v>
       </c>
       <c r="R101" t="n">
-        <v>6854779</v>
+        <v>6854482</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10962,60 +10962,68 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127386811</v>
+        <v>127386310</v>
       </c>
       <c r="B102" t="n">
-        <v>79609</v>
+        <v>98450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>476887</v>
+        <v>476822</v>
       </c>
       <c r="R102" t="n">
-        <v>6854810</v>
+        <v>6854557</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11053,25 +11061,26 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127386310</v>
+        <v>127388967</v>
       </c>
       <c r="B103" t="n">
         <v>98450</v>
@@ -11101,23 +11110,19 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>476822</v>
+        <v>476843</v>
       </c>
       <c r="R103" t="n">
-        <v>6854557</v>
+        <v>6854525</v>
       </c>
       <c r="S103" t="n">
         <v>4</v>
@@ -11165,19 +11170,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127388967</v>
+        <v>127387594</v>
       </c>
       <c r="B104" t="n">
         <v>98450</v>
@@ -11207,22 +11212,30 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>476843</v>
+        <v>476850</v>
       </c>
       <c r="R104" t="n">
-        <v>6854525</v>
+        <v>6854546</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11267,72 +11280,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127387594</v>
+        <v>127386811</v>
       </c>
       <c r="B105" t="n">
-        <v>98450</v>
+        <v>79609</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>476850</v>
+        <v>476887</v>
       </c>
       <c r="R105" t="n">
-        <v>6854546</v>
+        <v>6854810</v>
       </c>
       <c r="S105" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11370,19 +11371,18 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin, Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127369923</v>
+        <v>127386081</v>
       </c>
       <c r="B3" t="n">
-        <v>80152</v>
+        <v>78779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>476867</v>
       </c>
       <c r="R3" t="n">
-        <v>6854642</v>
+        <v>6854478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,19 +850,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -996,45 +986,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127386081</v>
+        <v>127369923</v>
       </c>
       <c r="B5" t="n">
-        <v>78779</v>
+        <v>80152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>476867</v>
       </c>
       <c r="R5" t="n">
-        <v>6854478</v>
+        <v>6854642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,9 +1054,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,12 +1081,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127388142</v>
+        <v>127386850</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,45 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476840</v>
+        <v>476896</v>
       </c>
       <c r="R9" t="n">
-        <v>6854642</v>
+        <v>6854789</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,64 +1483,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127388973</v>
+        <v>127386809</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>79052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476828</v>
+        <v>476898</v>
       </c>
       <c r="R10" t="n">
-        <v>6854626</v>
+        <v>6854784</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,64 +1574,71 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127371659</v>
+        <v>127388142</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476822</v>
+        <v>476840</v>
       </c>
       <c r="R11" t="n">
-        <v>6854617</v>
+        <v>6854642</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1673,19 +1668,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,19 +1685,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127387597</v>
+        <v>127388973</v>
       </c>
       <c r="B12" t="n">
         <v>98450</v>
@@ -1742,30 +1727,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476831</v>
+        <v>476828</v>
       </c>
       <c r="R12" t="n">
-        <v>6854622</v>
+        <v>6854626</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1810,19 +1787,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127387592</v>
+        <v>127371659</v>
       </c>
       <c r="B13" t="n">
         <v>98450</v>
@@ -1850,32 +1827,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476796</v>
+        <v>476822</v>
       </c>
       <c r="R13" t="n">
-        <v>6854627</v>
+        <v>6854617</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,14 +1867,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,26 +1888,25 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127388966</v>
+        <v>127387597</v>
       </c>
       <c r="B14" t="n">
         <v>98450</v>
@@ -1967,22 +1936,30 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476792</v>
+        <v>476831</v>
       </c>
       <c r="R14" t="n">
-        <v>6854646</v>
+        <v>6854622</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2027,60 +2004,72 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127386809</v>
+        <v>127387592</v>
       </c>
       <c r="B15" t="n">
-        <v>79052</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476898</v>
+        <v>476796</v>
       </c>
       <c r="R15" t="n">
-        <v>6854784</v>
+        <v>6854627</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,72 +2101,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127386850</v>
+        <v>127388966</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476896</v>
+        <v>476792</v>
       </c>
       <c r="R16" t="n">
-        <v>6854789</v>
+        <v>6854646</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,63 +2214,68 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127388145</v>
+        <v>127388963</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476840</v>
+        <v>476856</v>
       </c>
       <c r="R17" t="n">
-        <v>6854642</v>
+        <v>6854653</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2312,25 +2316,26 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127388963</v>
+        <v>127386305</v>
       </c>
       <c r="B18" t="n">
         <v>98450</v>
@@ -2360,19 +2365,23 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476856</v>
+        <v>476855</v>
       </c>
       <c r="R18" t="n">
-        <v>6854653</v>
+        <v>6854627</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2420,19 +2429,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127386305</v>
+        <v>127386099</v>
       </c>
       <c r="B19" t="n">
         <v>98450</v>
@@ -2462,26 +2471,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476855</v>
+        <v>476865</v>
       </c>
       <c r="R19" t="n">
-        <v>6854627</v>
+        <v>6854478</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,64 +2531,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127386099</v>
+        <v>127388145</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476865</v>
+        <v>476840</v>
       </c>
       <c r="R20" t="n">
-        <v>6854478</v>
+        <v>6854642</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2621,19 +2622,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -6437,48 +6437,60 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127386849</v>
+        <v>127387593</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>476891</v>
+        <v>476780</v>
       </c>
       <c r="R58" t="n">
-        <v>6854776</v>
+        <v>6854617</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6510,31 +6522,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127387593</v>
+        <v>127387589</v>
       </c>
       <c r="B59" t="n">
         <v>98450</v>
@@ -6564,7 +6582,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6581,10 +6599,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476780</v>
+        <v>476812</v>
       </c>
       <c r="R59" t="n">
-        <v>6854617</v>
+        <v>6854623</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6649,7 +6667,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127387589</v>
+        <v>127386313</v>
       </c>
       <c r="B60" t="n">
         <v>98450</v>
@@ -6679,14 +6697,10 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -6696,13 +6710,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476812</v>
+        <v>476881</v>
       </c>
       <c r="R60" t="n">
-        <v>6854623</v>
+        <v>6854650</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6732,11 +6746,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6752,19 +6761,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127386313</v>
+        <v>127371630</v>
       </c>
       <c r="B61" t="n">
         <v>98450</v>
@@ -6794,26 +6803,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476881</v>
+        <v>476874</v>
       </c>
       <c r="R61" t="n">
-        <v>6854650</v>
+        <v>6854475</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6840,37 +6850,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127371630</v>
+        <v>127387590</v>
       </c>
       <c r="B62" t="n">
         <v>98450</v>
@@ -6900,27 +6919,30 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476874</v>
+        <v>476860</v>
       </c>
       <c r="R62" t="n">
-        <v>6854475</v>
+        <v>6854552</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6947,19 +6969,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>16:38</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>4 blommande stänglar</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6968,78 +6985,67 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127387590</v>
+        <v>127386849</v>
       </c>
       <c r="B63" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>476860</v>
+        <v>476891</v>
       </c>
       <c r="R63" t="n">
-        <v>6854552</v>
+        <v>6854776</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7071,30 +7077,24 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>4 blommande stänglar</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8645,48 +8645,56 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127369891</v>
+        <v>127386315</v>
       </c>
       <c r="B79" t="n">
-        <v>80158</v>
+        <v>98450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476866</v>
+        <v>476883</v>
       </c>
       <c r="R79" t="n">
-        <v>6854642</v>
+        <v>6854657</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8713,87 +8721,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127386820</v>
+        <v>127386103</v>
       </c>
       <c r="B80" t="n">
-        <v>92614</v>
+        <v>98450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476882</v>
+        <v>476832</v>
       </c>
       <c r="R80" t="n">
-        <v>6854669</v>
+        <v>6854485</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8831,63 +8834,72 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127369660</v>
+        <v>127386300</v>
       </c>
       <c r="B81" t="n">
-        <v>96702</v>
+        <v>98450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476880</v>
+        <v>476830</v>
       </c>
       <c r="R81" t="n">
-        <v>6854794</v>
+        <v>6854480</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -8917,46 +8929,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386315</v>
+        <v>127386843</v>
       </c>
       <c r="B82" t="n">
         <v>98450</v>
@@ -8984,28 +8987,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476883</v>
+        <v>476842</v>
       </c>
       <c r="R82" t="n">
-        <v>6854657</v>
+        <v>6854652</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9043,68 +9038,63 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386103</v>
+        <v>127386082</v>
       </c>
       <c r="B83" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476832</v>
+        <v>476804</v>
       </c>
       <c r="R83" t="n">
-        <v>6854485</v>
+        <v>6854643</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9145,7 +9135,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9164,42 +9153,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386300</v>
+        <v>127386834</v>
       </c>
       <c r="B84" t="n">
-        <v>98450</v>
+        <v>80083</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9207,13 +9191,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476830</v>
+        <v>476869</v>
       </c>
       <c r="R84" t="n">
-        <v>6854480</v>
+        <v>6854645</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9258,60 +9242,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127386843</v>
+        <v>127369660</v>
       </c>
       <c r="B85" t="n">
-        <v>98450</v>
+        <v>96702</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476842</v>
+        <v>476880</v>
       </c>
       <c r="R85" t="n">
-        <v>6854652</v>
+        <v>6854794</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9338,9 +9322,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9355,22 +9349,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386834</v>
+        <v>127369891</v>
       </c>
       <c r="B86" t="n">
-        <v>80083</v>
+        <v>80158</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9378,40 +9372,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476869</v>
+        <v>476866</v>
       </c>
       <c r="R86" t="n">
-        <v>6854645</v>
+        <v>6854642</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9438,40 +9429,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127386082</v>
+        <v>127386820</v>
       </c>
       <c r="B87" t="n">
-        <v>78779</v>
+        <v>92614</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9479,21 +9479,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9503,13 +9503,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476804</v>
+        <v>476882</v>
       </c>
       <c r="R87" t="n">
-        <v>6854643</v>
+        <v>6854669</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9553,12 +9553,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127386081</v>
+        <v>127369923</v>
       </c>
       <c r="B3" t="n">
-        <v>78779</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>476867</v>
       </c>
       <c r="R3" t="n">
-        <v>6854478</v>
+        <v>6854642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +850,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -986,48 +996,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127369923</v>
+        <v>127386314</v>
       </c>
       <c r="B5" t="n">
-        <v>80152</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>476867</v>
       </c>
       <c r="R5" t="n">
-        <v>6854642</v>
+        <v>6854648</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,46 +1072,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127386314</v>
+        <v>127386098</v>
       </c>
       <c r="B6" t="n">
         <v>98450</v>
@@ -1123,26 +1132,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476867</v>
+        <v>476851</v>
       </c>
       <c r="R6" t="n">
-        <v>6854648</v>
+        <v>6854670</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,12 +1192,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1296,49 +1301,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127386098</v>
+        <v>127386081</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476851</v>
+        <v>476867</v>
       </c>
       <c r="R8" t="n">
-        <v>6854670</v>
+        <v>6854478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,7 +1380,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127386850</v>
+        <v>127386809</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476896</v>
+        <v>476898</v>
       </c>
       <c r="R9" t="n">
-        <v>6854789</v>
+        <v>6854784</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127386809</v>
+        <v>127386850</v>
       </c>
       <c r="B10" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,21 +1506,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476898</v>
+        <v>476896</v>
       </c>
       <c r="R10" t="n">
-        <v>6854784</v>
+        <v>6854789</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127388973</v>
+        <v>127371659</v>
       </c>
       <c r="B12" t="n">
         <v>98450</v>
@@ -1725,21 +1725,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476828</v>
+        <v>476822</v>
       </c>
       <c r="R12" t="n">
-        <v>6854626</v>
+        <v>6854617</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1769,37 +1765,46 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127371659</v>
+        <v>127387592</v>
       </c>
       <c r="B13" t="n">
         <v>98450</v>
@@ -1827,20 +1832,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476822</v>
+        <v>476796</v>
       </c>
       <c r="R13" t="n">
-        <v>6854617</v>
+        <v>6854627</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1867,19 +1884,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:39</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,25 +1900,26 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127387597</v>
+        <v>127388966</v>
       </c>
       <c r="B14" t="n">
         <v>98450</v>
@@ -1936,30 +1949,22 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476831</v>
+        <v>476792</v>
       </c>
       <c r="R14" t="n">
-        <v>6854622</v>
+        <v>6854646</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2004,19 +2009,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127387592</v>
+        <v>127388973</v>
       </c>
       <c r="B15" t="n">
         <v>98450</v>
@@ -2046,30 +2051,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476796</v>
+        <v>476828</v>
       </c>
       <c r="R15" t="n">
-        <v>6854627</v>
+        <v>6854626</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2099,11 +2096,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,19 +2111,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127388966</v>
+        <v>127387597</v>
       </c>
       <c r="B16" t="n">
         <v>98450</v>
@@ -2161,22 +2153,30 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476792</v>
+        <v>476831</v>
       </c>
       <c r="R16" t="n">
-        <v>6854646</v>
+        <v>6854622</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2221,61 +2221,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127388963</v>
+        <v>127388145</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476856</v>
+        <v>476840</v>
       </c>
       <c r="R17" t="n">
-        <v>6854653</v>
+        <v>6854642</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2316,26 +2312,25 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127386305</v>
+        <v>127388963</v>
       </c>
       <c r="B18" t="n">
         <v>98450</v>
@@ -2365,23 +2360,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476855</v>
+        <v>476856</v>
       </c>
       <c r="R18" t="n">
-        <v>6854627</v>
+        <v>6854653</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2429,19 +2420,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127386099</v>
+        <v>127386305</v>
       </c>
       <c r="B19" t="n">
         <v>98450</v>
@@ -2471,22 +2462,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476865</v>
+        <v>476855</v>
       </c>
       <c r="R19" t="n">
-        <v>6854478</v>
+        <v>6854627</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2531,60 +2526,64 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127388145</v>
+        <v>127386099</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476840</v>
+        <v>476865</v>
       </c>
       <c r="R20" t="n">
-        <v>6854642</v>
+        <v>6854478</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2622,18 +2621,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin, Erik Christiansson</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2835,48 +2835,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127386319</v>
+        <v>127369424</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>80152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476821</v>
+        <v>476879</v>
       </c>
       <c r="R23" t="n">
-        <v>6854475</v>
+        <v>6854650</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2903,9 +2903,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2920,68 +2930,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127386302</v>
+        <v>127387585</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476828</v>
+        <v>476865</v>
       </c>
       <c r="R24" t="n">
-        <v>6854531</v>
+        <v>6854638</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3019,72 +3021,63 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127388976</v>
+        <v>127386319</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476880</v>
+        <v>476821</v>
       </c>
       <c r="R25" t="n">
-        <v>6854486</v>
+        <v>6854475</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3125,71 +3118,66 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127386102</v>
+        <v>127387581</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476821</v>
+        <v>476827</v>
       </c>
       <c r="R26" t="n">
-        <v>6854465</v>
+        <v>6854629</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3227,67 +3215,74 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127387585</v>
+        <v>127386302</v>
       </c>
       <c r="B27" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476865</v>
+        <v>476828</v>
       </c>
       <c r="R27" t="n">
-        <v>6854638</v>
+        <v>6854531</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3325,63 +3320,68 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127369424</v>
+        <v>127386102</v>
       </c>
       <c r="B28" t="n">
-        <v>80152</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476879</v>
+        <v>476821</v>
       </c>
       <c r="R28" t="n">
-        <v>6854650</v>
+        <v>6854465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3411,87 +3411,86 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127387581</v>
+        <v>127388976</v>
       </c>
       <c r="B29" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476827</v>
+        <v>476880</v>
       </c>
       <c r="R29" t="n">
-        <v>6854629</v>
+        <v>6854486</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3529,28 +3528,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127386295</v>
+        <v>127371357</v>
       </c>
       <c r="B30" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,41 +3558,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476888</v>
+        <v>476901</v>
       </c>
       <c r="R30" t="n">
-        <v>6854664</v>
+        <v>6854667</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3622,30 +3615,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3759,10 +3761,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127371357</v>
+        <v>127386295</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3770,34 +3772,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476901</v>
+        <v>476888</v>
       </c>
       <c r="R32" t="n">
-        <v>6854667</v>
+        <v>6854664</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -3827,39 +3836,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4374,48 +4374,60 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127386117</v>
+        <v>127387587</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476835</v>
+        <v>476850</v>
       </c>
       <c r="R38" t="n">
-        <v>6854539</v>
+        <v>6854640</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4453,25 +4465,26 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127386108</v>
+        <v>127386311</v>
       </c>
       <c r="B39" t="n">
         <v>98450</v>
@@ -4499,20 +4512,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476830</v>
+        <v>476828</v>
       </c>
       <c r="R39" t="n">
-        <v>6854468</v>
+        <v>6854592</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4544,31 +4565,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127387587</v>
+        <v>127387586</v>
       </c>
       <c r="B40" t="n">
         <v>98450</v>
@@ -4596,29 +4623,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476850</v>
+        <v>476859</v>
       </c>
       <c r="R40" t="n">
-        <v>6854640</v>
+        <v>6854667</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4659,7 +4674,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4678,7 +4692,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127386311</v>
+        <v>127369992</v>
       </c>
       <c r="B41" t="n">
         <v>98450</v>
@@ -4706,28 +4720,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476828</v>
+        <v>476859</v>
       </c>
       <c r="R41" t="n">
-        <v>6854592</v>
+        <v>6854645</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4754,14 +4765,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>1 blommande</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4770,26 +4786,25 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127387586</v>
+        <v>127388975</v>
       </c>
       <c r="B42" t="n">
         <v>98450</v>
@@ -4817,20 +4832,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476859</v>
+        <v>476864</v>
       </c>
       <c r="R42" t="n">
-        <v>6854667</v>
+        <v>6854487</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4868,25 +4887,26 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127369992</v>
+        <v>127386108</v>
       </c>
       <c r="B43" t="n">
         <v>98450</v>
@@ -4915,21 +4935,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476859</v>
+        <v>476830</v>
       </c>
       <c r="R43" t="n">
-        <v>6854645</v>
+        <v>6854468</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,19 +4974,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4986,64 +4991,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127388975</v>
+        <v>127386117</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476864</v>
+        <v>476835</v>
       </c>
       <c r="R44" t="n">
-        <v>6854487</v>
+        <v>6854539</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5081,51 +5082,50 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127386808</v>
+        <v>127386078</v>
       </c>
       <c r="B45" t="n">
-        <v>79052</v>
+        <v>98471</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476882</v>
+        <v>476854</v>
       </c>
       <c r="R45" t="n">
-        <v>6854781</v>
+        <v>6854673</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5185,44 +5185,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127386078</v>
+        <v>127386808</v>
       </c>
       <c r="B46" t="n">
-        <v>98471</v>
+        <v>79052</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5232,13 +5232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476854</v>
+        <v>476882</v>
       </c>
       <c r="R46" t="n">
-        <v>6854673</v>
+        <v>6854781</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5282,12 +5282,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127371200</v>
+        <v>127386087</v>
       </c>
       <c r="B48" t="n">
-        <v>92614</v>
+        <v>78778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5412,37 +5412,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476901</v>
+        <v>476780</v>
       </c>
       <c r="R48" t="n">
-        <v>6854667</v>
+        <v>6854482</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5469,19 +5469,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5496,12 +5486,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5605,7 +5595,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127386087</v>
+        <v>127371346</v>
       </c>
       <c r="B50" t="n">
         <v>78778</v>
@@ -5636,17 +5626,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476780</v>
+        <v>476826</v>
       </c>
       <c r="R50" t="n">
-        <v>6854482</v>
+        <v>6854459</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5673,9 +5663,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5690,22 +5690,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127371346</v>
+        <v>127371200</v>
       </c>
       <c r="B51" t="n">
-        <v>78778</v>
+        <v>92614</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476826</v>
+        <v>476901</v>
       </c>
       <c r="R51" t="n">
-        <v>6854459</v>
+        <v>6854667</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5797,12 +5797,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127387598</v>
+        <v>127386838</v>
       </c>
       <c r="B53" t="n">
         <v>98450</v>
@@ -5934,32 +5934,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476767</v>
+        <v>476819</v>
       </c>
       <c r="R53" t="n">
-        <v>6854589</v>
+        <v>6854632</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5997,26 +5985,25 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127386838</v>
+        <v>127387598</v>
       </c>
       <c r="B54" t="n">
         <v>98450</v>
@@ -6044,20 +6031,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476819</v>
+        <v>476767</v>
       </c>
       <c r="R54" t="n">
-        <v>6854632</v>
+        <v>6854589</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6095,70 +6094,64 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127388147</v>
+        <v>127370418</v>
       </c>
       <c r="B55" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476787</v>
+        <v>476867</v>
       </c>
       <c r="R55" t="n">
-        <v>6854642</v>
+        <v>6854691</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6188,30 +6181,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6330,45 +6332,52 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127370418</v>
+        <v>127388147</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476867</v>
+        <v>476787</v>
       </c>
       <c r="R57" t="n">
-        <v>6854691</v>
+        <v>6854642</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6398,39 +6407,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6552,7 +6552,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127387589</v>
+        <v>127386313</v>
       </c>
       <c r="B59" t="n">
         <v>98450</v>
@@ -6582,14 +6582,10 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -6599,13 +6595,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476812</v>
+        <v>476881</v>
       </c>
       <c r="R59" t="n">
-        <v>6854623</v>
+        <v>6854650</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6635,11 +6631,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6655,19 +6646,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127386313</v>
+        <v>127387589</v>
       </c>
       <c r="B60" t="n">
         <v>98450</v>
@@ -6697,10 +6688,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -6710,13 +6705,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476881</v>
+        <v>476812</v>
       </c>
       <c r="R60" t="n">
-        <v>6854650</v>
+        <v>6854623</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6746,6 +6741,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6761,12 +6761,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7191,55 +7191,63 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin, Erik Christiansson</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127371302</v>
+        <v>127386308</v>
       </c>
       <c r="B65" t="n">
-        <v>78779</v>
+        <v>98450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476826</v>
+        <v>476825</v>
       </c>
       <c r="R65" t="n">
-        <v>6854459</v>
+        <v>6854551</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7266,46 +7274,37 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386308</v>
+        <v>127386842</v>
       </c>
       <c r="B66" t="n">
         <v>98450</v>
@@ -7333,28 +7332,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476825</v>
+        <v>476869</v>
       </c>
       <c r="R66" t="n">
-        <v>6854551</v>
+        <v>6854655</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7392,26 +7383,25 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386110</v>
+        <v>127386096</v>
       </c>
       <c r="B67" t="n">
         <v>98450</v>
@@ -7439,17 +7429,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476818</v>
+        <v>476806</v>
       </c>
       <c r="R67" t="n">
-        <v>6854660</v>
+        <v>6854483</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7490,6 +7484,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7508,48 +7503,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386842</v>
+        <v>127371302</v>
       </c>
       <c r="B68" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476869</v>
+        <v>476826</v>
       </c>
       <c r="R68" t="n">
-        <v>6854655</v>
+        <v>6854459</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7576,9 +7571,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7593,19 +7598,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127386096</v>
+        <v>127386110</v>
       </c>
       <c r="B69" t="n">
         <v>98450</v>
@@ -7633,21 +7638,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476806</v>
+        <v>476818</v>
       </c>
       <c r="R69" t="n">
-        <v>6854483</v>
+        <v>6854660</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7688,7 +7689,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127386841</v>
+        <v>127388972</v>
       </c>
       <c r="B75" t="n">
         <v>98450</v>
@@ -8262,20 +8262,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476865</v>
+        <v>476809</v>
       </c>
       <c r="R75" t="n">
-        <v>6854629</v>
+        <v>6854638</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8313,25 +8317,26 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127388972</v>
+        <v>127386097</v>
       </c>
       <c r="B76" t="n">
         <v>98450</v>
@@ -8361,7 +8366,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8370,13 +8375,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476809</v>
+        <v>476794</v>
       </c>
       <c r="R76" t="n">
-        <v>6854638</v>
+        <v>6854562</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8421,19 +8426,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127387595</v>
+        <v>127386841</v>
       </c>
       <c r="B77" t="n">
         <v>98450</v>
@@ -8461,32 +8466,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476804</v>
+        <v>476865</v>
       </c>
       <c r="R77" t="n">
-        <v>6854628</v>
+        <v>6854629</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8524,26 +8517,25 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127386097</v>
+        <v>127387595</v>
       </c>
       <c r="B78" t="n">
         <v>98450</v>
@@ -8573,22 +8565,30 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476794</v>
+        <v>476804</v>
       </c>
       <c r="R78" t="n">
-        <v>6854562</v>
+        <v>6854628</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8633,65 +8633,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127386315</v>
+        <v>127369660</v>
       </c>
       <c r="B79" t="n">
-        <v>98450</v>
+        <v>96702</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476883</v>
+        <v>476880</v>
       </c>
       <c r="R79" t="n">
-        <v>6854657</v>
+        <v>6854794</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8721,79 +8713,84 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127386103</v>
+        <v>127369891</v>
       </c>
       <c r="B80" t="n">
-        <v>98450</v>
+        <v>80158</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476832</v>
+        <v>476866</v>
       </c>
       <c r="R80" t="n">
-        <v>6854485</v>
+        <v>6854642</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8823,86 +8820,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127386300</v>
+        <v>127386820</v>
       </c>
       <c r="B81" t="n">
-        <v>98450</v>
+        <v>92614</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476830</v>
+        <v>476882</v>
       </c>
       <c r="R81" t="n">
-        <v>6854480</v>
+        <v>6854669</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8940,51 +8938,50 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386843</v>
+        <v>127386082</v>
       </c>
       <c r="B82" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8994,13 +8991,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476842</v>
+        <v>476804</v>
       </c>
       <c r="R82" t="n">
-        <v>6854652</v>
+        <v>6854643</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9044,60 +9041,63 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386082</v>
+        <v>127386834</v>
       </c>
       <c r="B83" t="n">
-        <v>78779</v>
+        <v>80083</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476804</v>
+        <v>476869</v>
       </c>
       <c r="R83" t="n">
-        <v>6854643</v>
+        <v>6854645</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9135,55 +9135,61 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386834</v>
+        <v>127386315</v>
       </c>
       <c r="B84" t="n">
-        <v>80083</v>
+        <v>98450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9191,13 +9197,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476869</v>
+        <v>476883</v>
       </c>
       <c r="R84" t="n">
-        <v>6854645</v>
+        <v>6854657</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9242,60 +9248,64 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127369660</v>
+        <v>127386103</v>
       </c>
       <c r="B85" t="n">
-        <v>96702</v>
+        <v>98450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476880</v>
+        <v>476832</v>
       </c>
       <c r="R85" t="n">
-        <v>6854794</v>
+        <v>6854485</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9322,87 +9332,86 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127369891</v>
+        <v>127386300</v>
       </c>
       <c r="B86" t="n">
-        <v>80158</v>
+        <v>98450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476866</v>
+        <v>476830</v>
       </c>
       <c r="R86" t="n">
-        <v>6854642</v>
+        <v>6854480</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9429,71 +9438,62 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127386820</v>
+        <v>127386843</v>
       </c>
       <c r="B87" t="n">
-        <v>92614</v>
+        <v>98450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9503,10 +9503,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476882</v>
+        <v>476842</v>
       </c>
       <c r="R87" t="n">
-        <v>6854669</v>
+        <v>6854652</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9565,48 +9565,52 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127386828</v>
+        <v>127388974</v>
       </c>
       <c r="B88" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476869</v>
+        <v>476859</v>
       </c>
       <c r="R88" t="n">
-        <v>6854645</v>
+        <v>6854547</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9644,66 +9648,79 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386080</v>
+        <v>127386840</v>
       </c>
       <c r="B89" t="n">
-        <v>92634</v>
+        <v>98450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476799</v>
+        <v>476852</v>
       </c>
       <c r="R89" t="n">
-        <v>6854562</v>
+        <v>6854630</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9741,50 +9758,51 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127386129</v>
+        <v>127386828</v>
       </c>
       <c r="B90" t="n">
-        <v>92622</v>
+        <v>80123</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9794,13 +9812,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476790</v>
+        <v>476869</v>
       </c>
       <c r="R90" t="n">
-        <v>6854633</v>
+        <v>6854645</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9844,64 +9862,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127388974</v>
+        <v>127386080</v>
       </c>
       <c r="B91" t="n">
-        <v>98450</v>
+        <v>92634</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476859</v>
+        <v>476799</v>
       </c>
       <c r="R91" t="n">
-        <v>6854547</v>
+        <v>6854562</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9939,79 +9953,66 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127386840</v>
+        <v>127386129</v>
       </c>
       <c r="B92" t="n">
-        <v>98450</v>
+        <v>92622</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476852</v>
+        <v>476790</v>
       </c>
       <c r="R92" t="n">
-        <v>6854630</v>
+        <v>6854633</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10049,19 +10050,18 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10170,32 +10170,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127386837</v>
+        <v>127386320</v>
       </c>
       <c r="B94" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10205,13 +10205,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>476808</v>
+        <v>476832</v>
       </c>
       <c r="R94" t="n">
-        <v>6854629</v>
+        <v>6854631</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10255,44 +10255,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127386320</v>
+        <v>127386837</v>
       </c>
       <c r="B95" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10302,13 +10302,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>476832</v>
+        <v>476808</v>
       </c>
       <c r="R95" t="n">
-        <v>6854631</v>
+        <v>6854629</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10352,12 +10352,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Nadja Karlsson, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10780,32 +10780,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127386854</v>
+        <v>127386088</v>
       </c>
       <c r="B100" t="n">
-        <v>92622</v>
+        <v>78778</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10815,13 +10815,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>476899</v>
+        <v>476826</v>
       </c>
       <c r="R100" t="n">
-        <v>6854779</v>
+        <v>6854482</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10865,44 +10865,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127386088</v>
+        <v>127386854</v>
       </c>
       <c r="B101" t="n">
-        <v>78778</v>
+        <v>92622</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10912,13 +10912,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476826</v>
+        <v>476899</v>
       </c>
       <c r="R101" t="n">
-        <v>6854482</v>
+        <v>6854779</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10962,19 +10962,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127386310</v>
+        <v>127388967</v>
       </c>
       <c r="B102" t="n">
         <v>98450</v>
@@ -11004,23 +11004,19 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>476822</v>
+        <v>476843</v>
       </c>
       <c r="R102" t="n">
-        <v>6854557</v>
+        <v>6854525</v>
       </c>
       <c r="S102" t="n">
         <v>4</v>
@@ -11068,19 +11064,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127388967</v>
+        <v>127386310</v>
       </c>
       <c r="B103" t="n">
         <v>98450</v>
@@ -11110,19 +11106,23 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>476843</v>
+        <v>476822</v>
       </c>
       <c r="R103" t="n">
-        <v>6854525</v>
+        <v>6854557</v>
       </c>
       <c r="S103" t="n">
         <v>4</v>
@@ -11170,12 +11170,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127369215</v>
+        <v>127371169</v>
       </c>
       <c r="B2" t="n">
-        <v>78687</v>
+        <v>91358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476907</v>
+        <v>476901</v>
       </c>
       <c r="R2" t="n">
-        <v>6854785</v>
+        <v>6854667</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127371169</v>
+        <v>127386081</v>
       </c>
       <c r="B4" t="n">
-        <v>91352</v>
+        <v>78779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476901</v>
+        <v>476867</v>
       </c>
       <c r="R4" t="n">
-        <v>6854667</v>
+        <v>6854478</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,19 +957,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,65 +974,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127386314</v>
+        <v>127369215</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>78687</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476867</v>
+        <v>476907</v>
       </c>
       <c r="R5" t="n">
-        <v>6854648</v>
+        <v>6854785</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1072,30 +1054,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1105,7 +1096,7 @@
         <v>127386098</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127386839</v>
+        <v>127386314</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,20 +1223,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476824</v>
+        <v>476867</v>
       </c>
       <c r="R7" t="n">
-        <v>6854630</v>
+        <v>6854648</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,50 +1282,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127386081</v>
+        <v>127386839</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476867</v>
+        <v>476824</v>
       </c>
       <c r="R8" t="n">
-        <v>6854478</v>
+        <v>6854630</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,22 +1386,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127386809</v>
+        <v>127388142</v>
       </c>
       <c r="B9" t="n">
-        <v>79052</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1409,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476898</v>
+        <v>476840</v>
       </c>
       <c r="R9" t="n">
-        <v>6854784</v>
+        <v>6854642</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1483,12 +1491,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1592,10 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127388142</v>
+        <v>127386809</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>79052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,45 +1611,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476840</v>
+        <v>476898</v>
       </c>
       <c r="R11" t="n">
-        <v>6854642</v>
+        <v>6854784</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1685,22 +1685,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127371659</v>
+        <v>127388966</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1725,17 +1725,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476822</v>
+        <v>476792</v>
       </c>
       <c r="R12" t="n">
-        <v>6854617</v>
+        <v>6854646</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1765,49 +1769,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127387592</v>
+        <v>127388973</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,30 +1829,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476796</v>
+        <v>476828</v>
       </c>
       <c r="R13" t="n">
-        <v>6854627</v>
+        <v>6854626</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,11 +1874,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,22 +1889,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127388966</v>
+        <v>127387592</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,22 +1931,30 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476792</v>
+        <v>476796</v>
       </c>
       <c r="R14" t="n">
-        <v>6854646</v>
+        <v>6854627</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1994,6 +1984,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127388973</v>
+        <v>127387597</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,22 +2046,30 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476828</v>
+        <v>476831</v>
       </c>
       <c r="R15" t="n">
-        <v>6854626</v>
+        <v>6854622</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2111,22 +2114,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127387597</v>
+        <v>127371659</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,32 +2154,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476831</v>
+        <v>476822</v>
       </c>
       <c r="R16" t="n">
-        <v>6854622</v>
+        <v>6854617</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2203,30 +2194,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
         <v>127388963</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127386305</v>
+        <v>127386099</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,26 +2462,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476855</v>
+        <v>476865</v>
       </c>
       <c r="R19" t="n">
-        <v>6854627</v>
+        <v>6854478</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,22 +2522,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127386099</v>
+        <v>127386305</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,22 +2564,26 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476865</v>
+        <v>476855</v>
       </c>
       <c r="R20" t="n">
-        <v>6854478</v>
+        <v>6854627</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2740,7 +2740,7 @@
         <v>127386848</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,48 +2835,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127369424</v>
+        <v>127386319</v>
       </c>
       <c r="B23" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476879</v>
+        <v>476821</v>
       </c>
       <c r="R23" t="n">
-        <v>6854650</v>
+        <v>6854475</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2903,19 +2903,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2930,60 +2920,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127387585</v>
+        <v>127369424</v>
       </c>
       <c r="B24" t="n">
-        <v>80123</v>
+        <v>80152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476865</v>
+        <v>476879</v>
       </c>
       <c r="R24" t="n">
-        <v>6854638</v>
+        <v>6854650</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3010,9 +3000,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3027,22 +3027,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127386319</v>
+        <v>127387585</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,21 +3050,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476821</v>
+        <v>476865</v>
       </c>
       <c r="R25" t="n">
-        <v>6854475</v>
+        <v>6854638</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3124,12 +3124,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3139,7 +3139,7 @@
         <v>127387581</v>
       </c>
       <c r="B26" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127386302</v>
+        <v>127386102</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3263,26 +3263,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476828</v>
+        <v>476821</v>
       </c>
       <c r="R27" t="n">
-        <v>6854531</v>
+        <v>6854465</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3327,22 +3323,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127386102</v>
+        <v>127388976</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,24 +3363,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476821</v>
+        <v>476880</v>
       </c>
       <c r="R28" t="n">
-        <v>6854465</v>
+        <v>6854486</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3429,22 +3429,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127388976</v>
+        <v>127386302</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3469,13 +3469,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476880</v>
+        <v>476828</v>
       </c>
       <c r="R29" t="n">
-        <v>6854486</v>
+        <v>6854531</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3535,39 +3535,39 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127371357</v>
+        <v>127370759</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>80158</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476901</v>
+        <v>476877</v>
       </c>
       <c r="R30" t="n">
-        <v>6854667</v>
+        <v>6854663</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3654,45 +3654,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127370759</v>
+        <v>127386295</v>
       </c>
       <c r="B31" t="n">
-        <v>80158</v>
+        <v>91358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476877</v>
+        <v>476888</v>
       </c>
       <c r="R31" t="n">
-        <v>6854663</v>
+        <v>6854664</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -3722,49 +3729,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127386295</v>
+        <v>127371357</v>
       </c>
       <c r="B32" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3772,41 +3770,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476888</v>
+        <v>476901</v>
       </c>
       <c r="R32" t="n">
-        <v>6854664</v>
+        <v>6854667</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -3836,40 +3827,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127386111</v>
+        <v>127386112</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476831</v>
+        <v>476873</v>
       </c>
       <c r="R33" t="n">
-        <v>6854682</v>
+        <v>6854658</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127386100</v>
+        <v>127386303</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3993,22 +3993,26 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476829</v>
+        <v>476836</v>
       </c>
       <c r="R34" t="n">
-        <v>6854465</v>
+        <v>6854627</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4053,12 +4057,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4068,7 +4072,7 @@
         <v>127386299</v>
       </c>
       <c r="B35" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4171,10 +4175,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127386303</v>
+        <v>127386100</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4201,26 +4205,22 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476836</v>
+        <v>476829</v>
       </c>
       <c r="R36" t="n">
-        <v>6854627</v>
+        <v>6854465</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4265,22 +4265,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127386112</v>
+        <v>127386111</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476873</v>
+        <v>476831</v>
       </c>
       <c r="R37" t="n">
-        <v>6854658</v>
+        <v>6854682</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4374,60 +4374,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127387587</v>
+        <v>127386117</v>
       </c>
       <c r="B38" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476850</v>
+        <v>476835</v>
       </c>
       <c r="R38" t="n">
-        <v>6854640</v>
+        <v>6854539</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4465,29 +4453,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127386311</v>
+        <v>127387586</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4512,28 +4499,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476828</v>
+        <v>476859</v>
       </c>
       <c r="R39" t="n">
-        <v>6854592</v>
+        <v>6854667</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4565,40 +4544,34 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>1 blommande</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127387586</v>
+        <v>127387587</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4623,17 +4596,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476859</v>
+        <v>476850</v>
       </c>
       <c r="R40" t="n">
-        <v>6854667</v>
+        <v>6854640</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4674,6 +4659,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4695,7 +4681,7 @@
         <v>127369992</v>
       </c>
       <c r="B41" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4804,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127388975</v>
+        <v>127386311</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4834,19 +4820,23 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476864</v>
+        <v>476828</v>
       </c>
       <c r="R42" t="n">
-        <v>6854487</v>
+        <v>6854592</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -4881,6 +4871,11 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4894,22 +4889,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127386108</v>
+        <v>127388975</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4934,20 +4929,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476830</v>
+        <v>476864</v>
       </c>
       <c r="R43" t="n">
-        <v>6854468</v>
+        <v>6854487</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4985,50 +4984,51 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127386117</v>
+        <v>127386108</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476835</v>
+        <v>476830</v>
       </c>
       <c r="R44" t="n">
-        <v>6854539</v>
+        <v>6854468</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127386078</v>
+        <v>127386808</v>
       </c>
       <c r="B45" t="n">
-        <v>98471</v>
+        <v>79052</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476854</v>
+        <v>476882</v>
       </c>
       <c r="R45" t="n">
-        <v>6854673</v>
+        <v>6854781</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5185,44 +5185,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127386808</v>
+        <v>127386078</v>
       </c>
       <c r="B46" t="n">
-        <v>79052</v>
+        <v>98477</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5232,13 +5232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476882</v>
+        <v>476854</v>
       </c>
       <c r="R46" t="n">
-        <v>6854781</v>
+        <v>6854673</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5282,22 +5282,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127370572</v>
+        <v>127371200</v>
       </c>
       <c r="B47" t="n">
-        <v>96702</v>
+        <v>92620</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476857</v>
+        <v>476901</v>
       </c>
       <c r="R47" t="n">
-        <v>6854654</v>
+        <v>6854667</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5401,10 +5401,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127386087</v>
+        <v>127370572</v>
       </c>
       <c r="B48" t="n">
-        <v>78778</v>
+        <v>96708</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5412,37 +5412,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476780</v>
+        <v>476857</v>
       </c>
       <c r="R48" t="n">
-        <v>6854482</v>
+        <v>6854654</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5469,9 +5469,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5486,19 +5496,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127386089</v>
+        <v>127386087</v>
       </c>
       <c r="B49" t="n">
         <v>78778</v>
@@ -5533,10 +5543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476838</v>
+        <v>476780</v>
       </c>
       <c r="R49" t="n">
-        <v>6854681</v>
+        <v>6854482</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,7 +5605,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127371346</v>
+        <v>127386089</v>
       </c>
       <c r="B50" t="n">
         <v>78778</v>
@@ -5626,17 +5636,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476826</v>
+        <v>476838</v>
       </c>
       <c r="R50" t="n">
-        <v>6854459</v>
+        <v>6854681</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5663,19 +5673,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5690,22 +5690,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127371200</v>
+        <v>127371346</v>
       </c>
       <c r="B51" t="n">
-        <v>92614</v>
+        <v>78778</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476901</v>
+        <v>476826</v>
       </c>
       <c r="R51" t="n">
-        <v>6854667</v>
+        <v>6854459</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5797,22 +5797,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386312</v>
+        <v>127386838</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5844,13 +5844,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476860</v>
+        <v>476819</v>
       </c>
       <c r="R52" t="n">
-        <v>6854625</v>
+        <v>6854632</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5894,22 +5894,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127386838</v>
+        <v>127387598</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5934,20 +5934,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476819</v>
+        <v>476767</v>
       </c>
       <c r="R53" t="n">
-        <v>6854632</v>
+        <v>6854589</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5985,28 +5997,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127387598</v>
+        <v>127386312</v>
       </c>
       <c r="B54" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6031,32 +6044,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476767</v>
+        <v>476860</v>
       </c>
       <c r="R54" t="n">
-        <v>6854589</v>
+        <v>6854625</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6094,64 +6095,68 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127370418</v>
+        <v>127372315</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476867</v>
+        <v>476894</v>
       </c>
       <c r="R55" t="n">
-        <v>6854691</v>
+        <v>6854772</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6183,7 +6188,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6193,7 +6198,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6220,50 +6225,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127372315</v>
+        <v>127370418</v>
       </c>
       <c r="B56" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476894</v>
+        <v>476867</v>
       </c>
       <c r="R56" t="n">
-        <v>6854772</v>
+        <v>6854691</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6335,7 +6335,7 @@
         <v>127388147</v>
       </c>
       <c r="B57" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6437,10 +6437,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127387593</v>
+        <v>127386313</v>
       </c>
       <c r="B58" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6467,14 +6467,10 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -6484,13 +6480,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>476780</v>
+        <v>476881</v>
       </c>
       <c r="R58" t="n">
-        <v>6854617</v>
+        <v>6854650</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6520,11 +6516,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6540,22 +6531,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127386313</v>
+        <v>127371630</v>
       </c>
       <c r="B59" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6582,26 +6573,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476881</v>
+        <v>476874</v>
       </c>
       <c r="R59" t="n">
-        <v>6854650</v>
+        <v>6854475</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6628,40 +6620,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127387589</v>
+        <v>127387593</v>
       </c>
       <c r="B60" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6688,7 +6689,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6705,10 +6706,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476812</v>
+        <v>476780</v>
       </c>
       <c r="R60" t="n">
-        <v>6854623</v>
+        <v>6854617</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6773,10 +6774,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127371630</v>
+        <v>127387590</v>
       </c>
       <c r="B61" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6803,27 +6804,30 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476874</v>
+        <v>476860</v>
       </c>
       <c r="R61" t="n">
-        <v>6854475</v>
+        <v>6854552</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6850,19 +6854,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>16:38</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>4 blommande stänglar</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6871,28 +6870,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127387590</v>
+        <v>127387589</v>
       </c>
       <c r="B62" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6936,10 +6936,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476860</v>
+        <v>476812</v>
       </c>
       <c r="R62" t="n">
-        <v>6854552</v>
+        <v>6854623</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>4 blommande stänglar</t>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7198,56 +7198,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127386308</v>
+        <v>127371302</v>
       </c>
       <c r="B65" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476825</v>
+        <v>476826</v>
       </c>
       <c r="R65" t="n">
-        <v>6854551</v>
+        <v>6854459</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7274,40 +7266,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386842</v>
+        <v>127386096</v>
       </c>
       <c r="B66" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,20 +7333,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476869</v>
+        <v>476806</v>
       </c>
       <c r="R66" t="n">
-        <v>6854655</v>
+        <v>6854483</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7383,28 +7388,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386096</v>
+        <v>127386308</v>
       </c>
       <c r="B67" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7431,22 +7437,26 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476806</v>
+        <v>476825</v>
       </c>
       <c r="R67" t="n">
-        <v>6854483</v>
+        <v>6854551</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7491,60 +7501,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127371302</v>
+        <v>127386842</v>
       </c>
       <c r="B68" t="n">
-        <v>78779</v>
+        <v>98456</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476826</v>
+        <v>476869</v>
       </c>
       <c r="R68" t="n">
-        <v>6854459</v>
+        <v>6854655</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7571,19 +7581,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7598,12 +7598,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7613,7 +7613,7 @@
         <v>127386110</v>
       </c>
       <c r="B69" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127388970</v>
+        <v>127371242</v>
       </c>
       <c r="B70" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7737,22 +7737,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>476836</v>
+        <v>476826</v>
       </c>
       <c r="R70" t="n">
-        <v>6854641</v>
+        <v>6854459</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7779,40 +7779,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127387596</v>
+        <v>127386109</v>
       </c>
       <c r="B71" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7837,32 +7846,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>476827</v>
+        <v>476831</v>
       </c>
       <c r="R71" t="n">
-        <v>6854628</v>
+        <v>6854531</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7900,29 +7897,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127371242</v>
+        <v>127387596</v>
       </c>
       <c r="B72" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7949,22 +7945,30 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>476826</v>
+        <v>476827</v>
       </c>
       <c r="R72" t="n">
-        <v>6854459</v>
+        <v>6854628</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7991,49 +7995,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127386109</v>
+        <v>127388970</v>
       </c>
       <c r="B73" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8058,20 +8053,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>476831</v>
+        <v>476836</v>
       </c>
       <c r="R73" t="n">
-        <v>6854531</v>
+        <v>6854641</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8109,18 +8108,19 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8234,10 +8234,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127388972</v>
+        <v>127386841</v>
       </c>
       <c r="B75" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8262,24 +8262,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476809</v>
+        <v>476865</v>
       </c>
       <c r="R75" t="n">
-        <v>6854638</v>
+        <v>6854629</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8317,19 +8313,18 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8339,7 +8334,7 @@
         <v>127386097</v>
       </c>
       <c r="B76" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8438,10 +8433,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127386841</v>
+        <v>127388972</v>
       </c>
       <c r="B77" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8466,20 +8461,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476865</v>
+        <v>476809</v>
       </c>
       <c r="R77" t="n">
-        <v>6854629</v>
+        <v>6854638</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8517,18 +8516,19 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
         <v>127387595</v>
       </c>
       <c r="B78" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8645,10 +8645,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127369660</v>
+        <v>127386082</v>
       </c>
       <c r="B79" t="n">
-        <v>96702</v>
+        <v>78779</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8656,37 +8656,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476880</v>
+        <v>476804</v>
       </c>
       <c r="R79" t="n">
-        <v>6854794</v>
+        <v>6854643</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8713,19 +8713,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8740,22 +8730,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127369891</v>
+        <v>127386834</v>
       </c>
       <c r="B80" t="n">
-        <v>80158</v>
+        <v>80083</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8763,37 +8753,40 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476866</v>
+        <v>476869</v>
       </c>
       <c r="R80" t="n">
-        <v>6854642</v>
+        <v>6854645</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8820,39 +8813,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8862,7 +8846,7 @@
         <v>127386820</v>
       </c>
       <c r="B81" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8956,10 +8940,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127386082</v>
+        <v>127369660</v>
       </c>
       <c r="B82" t="n">
-        <v>78779</v>
+        <v>96708</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8967,37 +8951,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476804</v>
+        <v>476880</v>
       </c>
       <c r="R82" t="n">
-        <v>6854643</v>
+        <v>6854794</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9024,9 +9008,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9041,22 +9035,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127386834</v>
+        <v>127369891</v>
       </c>
       <c r="B83" t="n">
-        <v>80083</v>
+        <v>80158</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9064,40 +9058,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476869</v>
+        <v>476866</v>
       </c>
       <c r="R83" t="n">
-        <v>6854645</v>
+        <v>6854642</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9124,40 +9115,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386315</v>
+        <v>127386300</v>
       </c>
       <c r="B84" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
@@ -9197,10 +9197,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476883</v>
+        <v>476830</v>
       </c>
       <c r="R84" t="n">
-        <v>6854657</v>
+        <v>6854480</v>
       </c>
       <c r="S84" t="n">
         <v>4</v>
@@ -9260,10 +9260,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127386103</v>
+        <v>127386843</v>
       </c>
       <c r="B85" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9288,24 +9288,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476832</v>
+        <v>476842</v>
       </c>
       <c r="R85" t="n">
-        <v>6854485</v>
+        <v>6854652</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9343,29 +9339,28 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386300</v>
+        <v>127386315</v>
       </c>
       <c r="B86" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,7 +9387,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
@@ -9405,10 +9400,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476830</v>
+        <v>476883</v>
       </c>
       <c r="R86" t="n">
-        <v>6854480</v>
+        <v>6854657</v>
       </c>
       <c r="S86" t="n">
         <v>4</v>
@@ -9468,10 +9463,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127386843</v>
+        <v>127386103</v>
       </c>
       <c r="B87" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9496,20 +9491,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476842</v>
+        <v>476832</v>
       </c>
       <c r="R87" t="n">
-        <v>6854652</v>
+        <v>6854485</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9547,70 +9546,67 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127388974</v>
+        <v>127386828</v>
       </c>
       <c r="B88" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476859</v>
+        <v>476869</v>
       </c>
       <c r="R88" t="n">
-        <v>6854547</v>
+        <v>6854645</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9648,79 +9644,66 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386840</v>
+        <v>127386080</v>
       </c>
       <c r="B89" t="n">
-        <v>98450</v>
+        <v>92640</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476852</v>
+        <v>476799</v>
       </c>
       <c r="R89" t="n">
-        <v>6854630</v>
+        <v>6854562</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9758,51 +9741,50 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127386828</v>
+        <v>127386129</v>
       </c>
       <c r="B90" t="n">
-        <v>80123</v>
+        <v>92628</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9812,13 +9794,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476869</v>
+        <v>476790</v>
       </c>
       <c r="R90" t="n">
-        <v>6854645</v>
+        <v>6854633</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9862,60 +9844,72 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127386080</v>
+        <v>127386840</v>
       </c>
       <c r="B91" t="n">
-        <v>92634</v>
+        <v>98456</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476799</v>
+        <v>476852</v>
       </c>
       <c r="R91" t="n">
-        <v>6854562</v>
+        <v>6854630</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9953,66 +9947,71 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127386129</v>
+        <v>127388974</v>
       </c>
       <c r="B92" t="n">
-        <v>92622</v>
+        <v>98456</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476790</v>
+        <v>476859</v>
       </c>
       <c r="R92" t="n">
-        <v>6854633</v>
+        <v>6854547</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10050,70 +10049,67 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127386101</v>
+        <v>127386320</v>
       </c>
       <c r="B93" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>476785</v>
+        <v>476832</v>
       </c>
       <c r="R93" t="n">
-        <v>6854487</v>
+        <v>6854631</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10151,67 +10147,70 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127386320</v>
+        <v>127386101</v>
       </c>
       <c r="B94" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>476832</v>
+        <v>476785</v>
       </c>
       <c r="R94" t="n">
-        <v>6854631</v>
+        <v>6854487</v>
       </c>
       <c r="S94" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10249,18 +10248,19 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10270,7 +10270,7 @@
         <v>127386837</v>
       </c>
       <c r="B95" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10364,10 +10364,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127370318</v>
+        <v>127388141</v>
       </c>
       <c r="B96" t="n">
-        <v>80123</v>
+        <v>57660</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10375,37 +10375,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476810</v>
+        <v>476834</v>
       </c>
       <c r="R96" t="n">
-        <v>6854587</v>
+        <v>6854535</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10432,19 +10440,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10459,68 +10457,64 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127388141</v>
+        <v>127386107</v>
       </c>
       <c r="B97" t="n">
-        <v>57660</v>
+        <v>98456</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476834</v>
+        <v>476800</v>
       </c>
       <c r="R97" t="n">
-        <v>6854535</v>
+        <v>6854551</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10558,67 +10552,64 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127386104</v>
+        <v>127370318</v>
       </c>
       <c r="B98" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>476865</v>
+        <v>476810</v>
       </c>
       <c r="R98" t="n">
-        <v>6854661</v>
+        <v>6854587</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10648,40 +10639,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127386107</v>
+        <v>127386104</v>
       </c>
       <c r="B99" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476800</v>
+        <v>476865</v>
       </c>
       <c r="R99" t="n">
-        <v>6854551</v>
+        <v>6854661</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10780,32 +10780,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127386088</v>
+        <v>127386854</v>
       </c>
       <c r="B100" t="n">
-        <v>78778</v>
+        <v>92628</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10815,13 +10815,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>476826</v>
+        <v>476899</v>
       </c>
       <c r="R100" t="n">
-        <v>6854482</v>
+        <v>6854779</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10865,44 +10865,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127386854</v>
+        <v>127386088</v>
       </c>
       <c r="B101" t="n">
-        <v>92622</v>
+        <v>78778</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10912,13 +10912,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476899</v>
+        <v>476826</v>
       </c>
       <c r="R101" t="n">
-        <v>6854779</v>
+        <v>6854482</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10962,12 +10962,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10977,7 +10977,7 @@
         <v>127388967</v>
       </c>
       <c r="B102" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>127386310</v>
       </c>
       <c r="B103" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>127387594</v>
       </c>
       <c r="B104" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127371169</v>
+        <v>127369215</v>
       </c>
       <c r="B2" t="n">
-        <v>91358</v>
+        <v>78690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476901</v>
+        <v>476907</v>
       </c>
       <c r="R2" t="n">
-        <v>6854667</v>
+        <v>6854785</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127369923</v>
+        <v>127371169</v>
       </c>
       <c r="B3" t="n">
-        <v>80152</v>
+        <v>91361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476867</v>
+        <v>476901</v>
       </c>
       <c r="R3" t="n">
-        <v>6854642</v>
+        <v>6854667</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,57 +877,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127386081</v>
+        <v>127369923</v>
       </c>
       <c r="B4" t="n">
-        <v>78779</v>
+        <v>80155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>476867</v>
       </c>
       <c r="R4" t="n">
-        <v>6854478</v>
+        <v>6854642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,9 +957,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,57 +984,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127369215</v>
+        <v>127386314</v>
       </c>
       <c r="B5" t="n">
-        <v>78687</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476907</v>
+        <v>476867</v>
       </c>
       <c r="R5" t="n">
-        <v>6854785</v>
+        <v>6854648</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1054,49 +1072,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127386098</v>
+        <v>127386839</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,24 +1130,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476851</v>
+        <v>476824</v>
       </c>
       <c r="R6" t="n">
-        <v>6854670</v>
+        <v>6854630</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,29 +1181,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127386314</v>
+        <v>127386098</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,26 +1229,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476867</v>
+        <v>476851</v>
       </c>
       <c r="R7" t="n">
-        <v>6854648</v>
+        <v>6854670</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,44 +1289,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127386839</v>
+        <v>127386081</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>78782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476824</v>
+        <v>476867</v>
       </c>
       <c r="R8" t="n">
-        <v>6854630</v>
+        <v>6854478</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,22 +1386,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127388142</v>
+        <v>127386809</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>79055</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,45 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476840</v>
+        <v>476898</v>
       </c>
       <c r="R9" t="n">
-        <v>6854642</v>
+        <v>6854784</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,22 +1483,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127386850</v>
+        <v>127388142</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1514,37 +1506,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476896</v>
+        <v>476840</v>
       </c>
       <c r="R10" t="n">
-        <v>6854789</v>
+        <v>6854642</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,22 +1588,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127386809</v>
+        <v>127386850</v>
       </c>
       <c r="B11" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476898</v>
+        <v>476896</v>
       </c>
       <c r="R11" t="n">
-        <v>6854784</v>
+        <v>6854789</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127388966</v>
+        <v>127388973</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476792</v>
+        <v>476828</v>
       </c>
       <c r="R12" t="n">
-        <v>6854646</v>
+        <v>6854626</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127388973</v>
+        <v>127371659</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,21 +1827,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476828</v>
+        <v>476822</v>
       </c>
       <c r="R13" t="n">
-        <v>6854626</v>
+        <v>6854617</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1871,40 +1867,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127387592</v>
+        <v>127387597</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,7 +1936,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1948,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476796</v>
+        <v>476831</v>
       </c>
       <c r="R14" t="n">
-        <v>6854627</v>
+        <v>6854622</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1984,11 +1989,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127387597</v>
+        <v>127387592</v>
       </c>
       <c r="B15" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476831</v>
+        <v>476796</v>
       </c>
       <c r="R15" t="n">
-        <v>6854622</v>
+        <v>6854627</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2099,6 +2099,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2126,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127371659</v>
+        <v>127388966</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,17 +2159,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476822</v>
+        <v>476792</v>
       </c>
       <c r="R16" t="n">
-        <v>6854617</v>
+        <v>6854646</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2194,39 +2203,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2236,7 +2236,7 @@
         <v>127388145</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>127388963</v>
       </c>
       <c r="B18" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127386099</v>
+        <v>127386305</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,22 +2462,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476865</v>
+        <v>476855</v>
       </c>
       <c r="R19" t="n">
-        <v>6854478</v>
+        <v>6854627</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2522,22 +2526,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127386305</v>
+        <v>127386099</v>
       </c>
       <c r="B20" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2564,26 +2568,22 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476855</v>
+        <v>476865</v>
       </c>
       <c r="R20" t="n">
-        <v>6854627</v>
+        <v>6854478</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,44 +2628,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127386067</v>
+        <v>127386848</v>
       </c>
       <c r="B21" t="n">
-        <v>79052</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476821</v>
+        <v>476840</v>
       </c>
       <c r="R21" t="n">
-        <v>6854543</v>
+        <v>6854622</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,50 +2719,51 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127386848</v>
+        <v>127386067</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>79055</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2772,13 +2773,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476840</v>
+        <v>476821</v>
       </c>
       <c r="R22" t="n">
-        <v>6854622</v>
+        <v>6854543</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2816,51 +2817,50 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127386319</v>
+        <v>127387581</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>97336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476821</v>
+        <v>476827</v>
       </c>
       <c r="R23" t="n">
-        <v>6854475</v>
+        <v>6854629</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2920,60 +2920,68 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127369424</v>
+        <v>127386302</v>
       </c>
       <c r="B24" t="n">
-        <v>80152</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476879</v>
+        <v>476828</v>
       </c>
       <c r="R24" t="n">
-        <v>6854650</v>
+        <v>6854531</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3000,87 +3008,86 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127387585</v>
+        <v>127388976</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>98459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476865</v>
+        <v>476880</v>
       </c>
       <c r="R25" t="n">
-        <v>6854638</v>
+        <v>6854486</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3118,66 +3125,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127387581</v>
+        <v>127386102</v>
       </c>
       <c r="B26" t="n">
-        <v>97333</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476827</v>
+        <v>476821</v>
       </c>
       <c r="R26" t="n">
-        <v>6854629</v>
+        <v>6854465</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3215,67 +3227,64 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127386102</v>
+        <v>127369424</v>
       </c>
       <c r="B27" t="n">
-        <v>98456</v>
+        <v>80155</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476821</v>
+        <v>476879</v>
       </c>
       <c r="R27" t="n">
-        <v>6854465</v>
+        <v>6854650</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3305,86 +3314,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127388976</v>
+        <v>127387585</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>80126</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476880</v>
+        <v>476865</v>
       </c>
       <c r="R28" t="n">
-        <v>6854486</v>
+        <v>6854638</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3422,72 +3432,63 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127386302</v>
+        <v>127386319</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476828</v>
+        <v>476821</v>
       </c>
       <c r="R29" t="n">
-        <v>6854531</v>
+        <v>6854475</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3528,7 +3529,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3547,48 +3547,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127370759</v>
+        <v>127386111</v>
       </c>
       <c r="B30" t="n">
-        <v>80158</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476877</v>
+        <v>476831</v>
       </c>
       <c r="R30" t="n">
-        <v>6854663</v>
+        <v>6854682</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3615,19 +3615,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3642,67 +3632,64 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127386295</v>
+        <v>127386100</v>
       </c>
       <c r="B31" t="n">
-        <v>91358</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476888</v>
+        <v>476829</v>
       </c>
       <c r="R31" t="n">
-        <v>6854664</v>
+        <v>6854465</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3747,60 +3734,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127371357</v>
+        <v>127386112</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476901</v>
+        <v>476873</v>
       </c>
       <c r="R32" t="n">
-        <v>6854667</v>
+        <v>6854658</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3827,19 +3814,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3854,60 +3831,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127386112</v>
+        <v>127370759</v>
       </c>
       <c r="B33" t="n">
-        <v>98456</v>
+        <v>80161</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476873</v>
+        <v>476877</v>
       </c>
       <c r="R33" t="n">
-        <v>6854658</v>
+        <v>6854663</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3934,9 +3911,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3951,54 +3938,53 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127386303</v>
+        <v>127386295</v>
       </c>
       <c r="B34" t="n">
-        <v>98456</v>
+        <v>91361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4006,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476836</v>
+        <v>476888</v>
       </c>
       <c r="R34" t="n">
-        <v>6854627</v>
+        <v>6854664</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4069,53 +4055,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127386299</v>
+        <v>127371357</v>
       </c>
       <c r="B35" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476817</v>
+        <v>476901</v>
       </c>
       <c r="R35" t="n">
-        <v>6854465</v>
+        <v>6854667</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4145,40 +4123,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127386100</v>
+        <v>127386299</v>
       </c>
       <c r="B36" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4205,22 +4192,26 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476829</v>
+        <v>476817</v>
       </c>
       <c r="R36" t="n">
         <v>6854465</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4265,22 +4256,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127386111</v>
+        <v>127386303</v>
       </c>
       <c r="B37" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4305,20 +4296,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476831</v>
+        <v>476836</v>
       </c>
       <c r="R37" t="n">
-        <v>6854682</v>
+        <v>6854627</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4356,18 +4355,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4377,7 +4377,7 @@
         <v>127386117</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4464,17 +4464,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127387586</v>
+        <v>127386108</v>
       </c>
       <c r="B39" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4506,13 +4506,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476859</v>
+        <v>476830</v>
       </c>
       <c r="R39" t="n">
-        <v>6854667</v>
+        <v>6854468</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4556,12 +4556,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
         <v>127387587</v>
       </c>
       <c r="B40" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127369992</v>
+        <v>127386311</v>
       </c>
       <c r="B41" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4706,25 +4706,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476859</v>
+        <v>476828</v>
       </c>
       <c r="R41" t="n">
-        <v>6854645</v>
+        <v>6854592</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4751,19 +4754,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:41</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4772,28 +4770,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127386311</v>
+        <v>127387586</v>
       </c>
       <c r="B42" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4818,28 +4817,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476828</v>
+        <v>476859</v>
       </c>
       <c r="R42" t="n">
-        <v>6854592</v>
+        <v>6854667</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4871,40 +4862,34 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 blommande</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127388975</v>
+        <v>127369992</v>
       </c>
       <c r="B43" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4929,24 +4914,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476864</v>
+        <v>476859</v>
       </c>
       <c r="R43" t="n">
-        <v>6854487</v>
+        <v>6854645</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4973,40 +4959,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127386108</v>
+        <v>127388975</v>
       </c>
       <c r="B44" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5031,20 +5026,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476830</v>
+        <v>476864</v>
       </c>
       <c r="R44" t="n">
-        <v>6854468</v>
+        <v>6854487</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5082,18 +5081,19 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5103,7 +5103,7 @@
         <v>127386808</v>
       </c>
       <c r="B45" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>127386078</v>
       </c>
       <c r="B46" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5294,10 +5294,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127371200</v>
+        <v>127370572</v>
       </c>
       <c r="B47" t="n">
-        <v>92620</v>
+        <v>96711</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476901</v>
+        <v>476857</v>
       </c>
       <c r="R47" t="n">
-        <v>6854667</v>
+        <v>6854654</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5401,45 +5401,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127370572</v>
+        <v>127386312</v>
       </c>
       <c r="B48" t="n">
-        <v>96708</v>
+        <v>98459</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476857</v>
+        <v>476860</v>
       </c>
       <c r="R48" t="n">
-        <v>6854654</v>
+        <v>6854625</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5469,19 +5469,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5496,60 +5486,72 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127386087</v>
+        <v>127387598</v>
       </c>
       <c r="B49" t="n">
-        <v>78778</v>
+        <v>98459</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476780</v>
+        <v>476767</v>
       </c>
       <c r="R49" t="n">
-        <v>6854482</v>
+        <v>6854589</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5587,50 +5589,51 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127386089</v>
+        <v>127386838</v>
       </c>
       <c r="B50" t="n">
-        <v>78778</v>
+        <v>98459</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5640,13 +5643,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476838</v>
+        <v>476819</v>
       </c>
       <c r="R50" t="n">
-        <v>6854681</v>
+        <v>6854632</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5690,22 +5693,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127371346</v>
+        <v>127386087</v>
       </c>
       <c r="B51" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5733,17 +5736,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476826</v>
+        <v>476780</v>
       </c>
       <c r="R51" t="n">
-        <v>6854459</v>
+        <v>6854482</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5770,19 +5773,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5797,44 +5790,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386838</v>
+        <v>127386089</v>
       </c>
       <c r="B52" t="n">
-        <v>98456</v>
+        <v>78781</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5844,13 +5837,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476819</v>
+        <v>476838</v>
       </c>
       <c r="R52" t="n">
-        <v>6854632</v>
+        <v>6854681</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5894,72 +5887,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127387598</v>
+        <v>127371200</v>
       </c>
       <c r="B53" t="n">
-        <v>98456</v>
+        <v>92623</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476767</v>
+        <v>476901</v>
       </c>
       <c r="R53" t="n">
-        <v>6854589</v>
+        <v>6854667</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5986,78 +5967,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127386312</v>
+        <v>127371346</v>
       </c>
       <c r="B54" t="n">
-        <v>98456</v>
+        <v>78781</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476860</v>
+        <v>476826</v>
       </c>
       <c r="R54" t="n">
-        <v>6854625</v>
+        <v>6854459</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6084,9 +6074,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6101,62 +6101,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127372315</v>
+        <v>127370418</v>
       </c>
       <c r="B55" t="n">
-        <v>56855</v>
+        <v>79023</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476894</v>
+        <v>476867</v>
       </c>
       <c r="R55" t="n">
-        <v>6854772</v>
+        <v>6854691</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6188,7 +6183,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6198,7 +6193,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6225,45 +6220,52 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127370418</v>
+        <v>127388147</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476867</v>
+        <v>476787</v>
       </c>
       <c r="R56" t="n">
-        <v>6854691</v>
+        <v>6854642</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6293,49 +6295,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127388147</v>
+        <v>127372315</v>
       </c>
       <c r="B57" t="n">
-        <v>92628</v>
+        <v>56858</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6343,41 +6336,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476787</v>
+        <v>476894</v>
       </c>
       <c r="R57" t="n">
-        <v>6854642</v>
+        <v>6854772</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6407,86 +6398,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127386313</v>
+        <v>127386849</v>
       </c>
       <c r="B58" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>476881</v>
+        <v>476891</v>
       </c>
       <c r="R58" t="n">
-        <v>6854650</v>
+        <v>6854776</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6524,29 +6516,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127371630</v>
+        <v>127387593</v>
       </c>
       <c r="B59" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6573,27 +6564,30 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476874</v>
+        <v>476780</v>
       </c>
       <c r="R59" t="n">
-        <v>6854475</v>
+        <v>6854617</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6620,19 +6614,14 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>16:38</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>1 blommande stängel</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6641,28 +6630,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127387593</v>
+        <v>127387589</v>
       </c>
       <c r="B60" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6689,7 +6679,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6706,10 +6696,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476780</v>
+        <v>476812</v>
       </c>
       <c r="R60" t="n">
-        <v>6854617</v>
+        <v>6854623</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6774,10 +6764,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127387590</v>
+        <v>127386313</v>
       </c>
       <c r="B61" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6804,14 +6794,10 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -6821,13 +6807,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476860</v>
+        <v>476881</v>
       </c>
       <c r="R61" t="n">
-        <v>6854552</v>
+        <v>6854650</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6857,11 +6843,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>4 blommande stänglar</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6877,22 +6858,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127387589</v>
+        <v>127371630</v>
       </c>
       <c r="B62" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6919,30 +6900,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476812</v>
+        <v>476874</v>
       </c>
       <c r="R62" t="n">
-        <v>6854623</v>
+        <v>6854475</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6969,14 +6947,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>1 blommande stängel</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6985,67 +6968,78 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Filippa Paperin, Tilde Carlinger, Elis Lewin, Erik Christiansson, Malte Lindberg, Elias Blad, Emilia Blixt, Karin Berg Andersson, Nadja Karlsson, Karla Alfaro Gripe, Alexander Ahl, Alice Helander, Sofia Damne, Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127386849</v>
+        <v>127387590</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>476891</v>
+        <v>476860</v>
       </c>
       <c r="R63" t="n">
-        <v>6854776</v>
+        <v>6854552</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7077,24 +7071,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>4 blommande stänglar</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7104,7 +7104,7 @@
         <v>127386068</v>
       </c>
       <c r="B64" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7198,48 +7198,56 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127371302</v>
+        <v>127386308</v>
       </c>
       <c r="B65" t="n">
-        <v>78779</v>
+        <v>98459</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476826</v>
+        <v>476825</v>
       </c>
       <c r="R65" t="n">
-        <v>6854459</v>
+        <v>6854551</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7266,49 +7274,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127386096</v>
+        <v>127386842</v>
       </c>
       <c r="B66" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7333,24 +7332,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476806</v>
+        <v>476869</v>
       </c>
       <c r="R66" t="n">
-        <v>6854483</v>
+        <v>6854655</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7388,29 +7383,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386308</v>
+        <v>127386110</v>
       </c>
       <c r="B67" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7435,28 +7429,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476825</v>
+        <v>476818</v>
       </c>
       <c r="R67" t="n">
-        <v>6854551</v>
+        <v>6854660</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7494,29 +7480,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386842</v>
+        <v>127386096</v>
       </c>
       <c r="B68" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7541,20 +7526,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476869</v>
+        <v>476806</v>
       </c>
       <c r="R68" t="n">
-        <v>6854655</v>
+        <v>6854483</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7592,66 +7581,67 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127386110</v>
+        <v>127371302</v>
       </c>
       <c r="B69" t="n">
-        <v>98456</v>
+        <v>78782</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476818</v>
+        <v>476826</v>
       </c>
       <c r="R69" t="n">
-        <v>6854660</v>
+        <v>6854459</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7678,9 +7668,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7695,22 +7695,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127371242</v>
+        <v>127388970</v>
       </c>
       <c r="B70" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7737,22 +7737,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>476826</v>
+        <v>476836</v>
       </c>
       <c r="R70" t="n">
-        <v>6854459</v>
+        <v>6854641</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7779,49 +7779,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127386109</v>
+        <v>127387596</v>
       </c>
       <c r="B71" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7846,20 +7837,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>476831</v>
+        <v>476827</v>
       </c>
       <c r="R71" t="n">
-        <v>6854531</v>
+        <v>6854628</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7897,28 +7900,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127387596</v>
+        <v>127371242</v>
       </c>
       <c r="B72" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7945,30 +7949,22 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>476827</v>
+        <v>476826</v>
       </c>
       <c r="R72" t="n">
-        <v>6854628</v>
+        <v>6854459</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7995,40 +7991,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127388970</v>
+        <v>127386109</v>
       </c>
       <c r="B73" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8053,24 +8058,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>476836</v>
+        <v>476831</v>
       </c>
       <c r="R73" t="n">
-        <v>6854641</v>
+        <v>6854531</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8108,19 +8109,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8130,7 +8130,7 @@
         <v>127369233</v>
       </c>
       <c r="B74" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8234,10 +8234,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127386841</v>
+        <v>127388972</v>
       </c>
       <c r="B75" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8262,20 +8262,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476865</v>
+        <v>476809</v>
       </c>
       <c r="R75" t="n">
-        <v>6854629</v>
+        <v>6854638</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8313,28 +8317,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127386097</v>
+        <v>127387595</v>
       </c>
       <c r="B76" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8361,22 +8366,30 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476794</v>
+        <v>476804</v>
       </c>
       <c r="R76" t="n">
-        <v>6854562</v>
+        <v>6854628</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8421,22 +8434,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127388972</v>
+        <v>127386097</v>
       </c>
       <c r="B77" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8463,7 +8476,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8472,13 +8485,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476809</v>
+        <v>476794</v>
       </c>
       <c r="R77" t="n">
-        <v>6854638</v>
+        <v>6854562</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8523,22 +8536,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127387595</v>
+        <v>127386841</v>
       </c>
       <c r="B78" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8563,32 +8576,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476804</v>
+        <v>476865</v>
       </c>
       <c r="R78" t="n">
-        <v>6854628</v>
+        <v>6854629</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8626,29 +8627,28 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127386082</v>
+        <v>127386820</v>
       </c>
       <c r="B79" t="n">
-        <v>78779</v>
+        <v>92623</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8656,21 +8656,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8680,13 +8680,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476804</v>
+        <v>476882</v>
       </c>
       <c r="R79" t="n">
-        <v>6854643</v>
+        <v>6854669</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8730,49 +8730,54 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127386834</v>
+        <v>127386315</v>
       </c>
       <c r="B80" t="n">
-        <v>80083</v>
+        <v>98459</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8780,13 +8785,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476869</v>
+        <v>476883</v>
       </c>
       <c r="R80" t="n">
-        <v>6854645</v>
+        <v>6854657</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8831,60 +8836,64 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127386820</v>
+        <v>127386103</v>
       </c>
       <c r="B81" t="n">
-        <v>92620</v>
+        <v>98459</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476882</v>
+        <v>476832</v>
       </c>
       <c r="R81" t="n">
-        <v>6854669</v>
+        <v>6854485</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8922,63 +8931,72 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127369660</v>
+        <v>127386300</v>
       </c>
       <c r="B82" t="n">
-        <v>96708</v>
+        <v>98459</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476880</v>
+        <v>476830</v>
       </c>
       <c r="R82" t="n">
-        <v>6854794</v>
+        <v>6854480</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -9008,87 +9026,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127369891</v>
+        <v>127386843</v>
       </c>
       <c r="B83" t="n">
-        <v>80158</v>
+        <v>98459</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476866</v>
+        <v>476842</v>
       </c>
       <c r="R83" t="n">
-        <v>6854642</v>
+        <v>6854652</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9115,19 +9124,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9142,68 +9141,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127386300</v>
+        <v>127386082</v>
       </c>
       <c r="B84" t="n">
-        <v>98456</v>
+        <v>78782</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476830</v>
+        <v>476804</v>
       </c>
       <c r="R84" t="n">
-        <v>6854480</v>
+        <v>6854643</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9241,64 +9232,66 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127386843</v>
+        <v>127386834</v>
       </c>
       <c r="B85" t="n">
-        <v>98456</v>
+        <v>80086</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476842</v>
+        <v>476869</v>
       </c>
       <c r="R85" t="n">
-        <v>6854652</v>
+        <v>6854645</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9339,6 +9332,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9350,63 +9344,55 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elias Blad, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127386315</v>
+        <v>127369891</v>
       </c>
       <c r="B86" t="n">
-        <v>98456</v>
+        <v>80161</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476883</v>
+        <v>476866</v>
       </c>
       <c r="R86" t="n">
-        <v>6854657</v>
+        <v>6854642</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9433,82 +9419,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127386103</v>
+        <v>127369660</v>
       </c>
       <c r="B87" t="n">
-        <v>98456</v>
+        <v>96711</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476832</v>
+        <v>476880</v>
       </c>
       <c r="R87" t="n">
-        <v>6854485</v>
+        <v>6854794</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9535,30 +9526,39 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9568,7 +9568,7 @@
         <v>127386828</v>
       </c>
       <c r="B88" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>127386080</v>
       </c>
       <c r="B89" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>127386129</v>
       </c>
       <c r="B90" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127386840</v>
+        <v>127388974</v>
       </c>
       <c r="B91" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9886,30 +9886,22 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476852</v>
+        <v>476859</v>
       </c>
       <c r="R91" t="n">
-        <v>6854630</v>
+        <v>6854547</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9954,22 +9946,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127388974</v>
+        <v>127386840</v>
       </c>
       <c r="B92" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9996,22 +9988,30 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476859</v>
+        <v>476852</v>
       </c>
       <c r="R92" t="n">
-        <v>6854547</v>
+        <v>6854630</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10056,12 +10056,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10071,7 +10071,7 @@
         <v>127386320</v>
       </c>
       <c r="B93" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>127386101</v>
       </c>
       <c r="B94" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10270,7 +10270,7 @@
         <v>127386837</v>
       </c>
       <c r="B95" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10364,10 +10364,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127388141</v>
+        <v>127370318</v>
       </c>
       <c r="B96" t="n">
-        <v>57660</v>
+        <v>80126</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10375,45 +10375,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476834</v>
+        <v>476810</v>
       </c>
       <c r="R96" t="n">
-        <v>6854535</v>
+        <v>6854587</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10440,9 +10432,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10457,12 +10459,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Filippa Paperin, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10472,7 +10474,7 @@
         <v>127386107</v>
       </c>
       <c r="B97" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10564,52 +10566,56 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127370318</v>
+        <v>127386104</v>
       </c>
       <c r="B98" t="n">
-        <v>80123</v>
+        <v>98459</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>476810</v>
+        <v>476865</v>
       </c>
       <c r="R98" t="n">
-        <v>6854587</v>
+        <v>6854661</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10639,91 +10645,86 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127386104</v>
+        <v>127388141</v>
       </c>
       <c r="B99" t="n">
-        <v>98456</v>
+        <v>57663</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476865</v>
+        <v>476834</v>
       </c>
       <c r="R99" t="n">
-        <v>6854661</v>
+        <v>6854535</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10761,67 +10762,70 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127386854</v>
+        <v>127388967</v>
       </c>
       <c r="B100" t="n">
-        <v>92628</v>
+        <v>98459</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>476899</v>
+        <v>476843</v>
       </c>
       <c r="R100" t="n">
-        <v>6854779</v>
+        <v>6854525</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10859,28 +10863,29 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127386088</v>
+        <v>127386811</v>
       </c>
       <c r="B101" t="n">
-        <v>78778</v>
+        <v>79612</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10888,21 +10893,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10912,13 +10917,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476826</v>
+        <v>476887</v>
       </c>
       <c r="R101" t="n">
-        <v>6854482</v>
+        <v>6854810</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10962,22 +10967,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127388967</v>
+        <v>127386310</v>
       </c>
       <c r="B102" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11004,19 +11009,23 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>476843</v>
+        <v>476822</v>
       </c>
       <c r="R102" t="n">
-        <v>6854525</v>
+        <v>6854557</v>
       </c>
       <c r="S102" t="n">
         <v>4</v>
@@ -11064,22 +11073,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127386310</v>
+        <v>127387594</v>
       </c>
       <c r="B103" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11106,10 +11115,14 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
@@ -11119,13 +11132,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>476822</v>
+        <v>476850</v>
       </c>
       <c r="R103" t="n">
-        <v>6854557</v>
+        <v>6854546</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11170,72 +11183,60 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127387594</v>
+        <v>127386088</v>
       </c>
       <c r="B104" t="n">
-        <v>98456</v>
+        <v>78781</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>476850</v>
+        <v>476826</v>
       </c>
       <c r="R104" t="n">
-        <v>6854546</v>
+        <v>6854482</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11273,51 +11274,50 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127386811</v>
+        <v>127386854</v>
       </c>
       <c r="B105" t="n">
-        <v>79609</v>
+        <v>92631</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11327,10 +11327,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>476887</v>
+        <v>476899</v>
       </c>
       <c r="R105" t="n">
-        <v>6854810</v>
+        <v>6854779</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 60836-2020 artfynd.xlsx
+++ b/artfynd/A 60836-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127369215</v>
+        <v>127386081</v>
       </c>
       <c r="B2" t="n">
-        <v>78690</v>
+        <v>78788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476907</v>
+        <v>476867</v>
       </c>
       <c r="R2" t="n">
-        <v>6854785</v>
+        <v>6854478</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +775,7 @@
         <v>127371169</v>
       </c>
       <c r="B3" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127369923</v>
+        <v>127369215</v>
       </c>
       <c r="B4" t="n">
-        <v>80155</v>
+        <v>78696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +914,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476867</v>
+        <v>476907</v>
       </c>
       <c r="R4" t="n">
-        <v>6854642</v>
+        <v>6854785</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,68 +974,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127386314</v>
+        <v>127369923</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>80161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>476867</v>
       </c>
       <c r="R5" t="n">
-        <v>6854648</v>
+        <v>6854642</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,40 +1054,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127386839</v>
+        <v>127386314</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,20 +1121,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476824</v>
+        <v>476867</v>
       </c>
       <c r="R6" t="n">
-        <v>6854630</v>
+        <v>6854648</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,28 +1180,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127386098</v>
+        <v>127386839</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,24 +1227,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476851</v>
+        <v>476824</v>
       </c>
       <c r="R7" t="n">
-        <v>6854670</v>
+        <v>6854630</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,64 +1278,67 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127386081</v>
+        <v>127386098</v>
       </c>
       <c r="B8" t="n">
-        <v>78782</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476867</v>
+        <v>476851</v>
       </c>
       <c r="R8" t="n">
-        <v>6854478</v>
+        <v>6854670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,6 +1379,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1401,7 +1401,7 @@
         <v>127386809</v>
       </c>
       <c r="B9" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127388142</v>
+        <v>127386850</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,45 +1506,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476840</v>
+        <v>476896</v>
       </c>
       <c r="R10" t="n">
-        <v>6854642</v>
+        <v>6854789</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,22 +1580,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127386850</v>
+        <v>127388142</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1611,37 +1603,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476896</v>
+        <v>476840</v>
       </c>
       <c r="R11" t="n">
-        <v>6854789</v>
+        <v>6854642</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1685,12 +1685,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Nadja Karlsson, Tilde Carlinger, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Ivar Anderberg, Filippa Paperin, Erik Christiansson, Emilia Blixt, Elias Blad, Elis Lewin, Alexander Ahl, Alice Helander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1700,7 +1700,7 @@
         <v>127388973</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127371659</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>127387597</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>127387592</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>127388966</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>127388145</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Nadja Karlsson, Tilde Carlinger, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Ivar Anderberg, Filippa Paperin, Erik Christiansson, Emilia Blixt, Elias Blad, Elis Lewin, Alexander Ahl, Alice Helander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
         <v>127388963</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>127386305</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127386099</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,39 +2633,39 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127386848</v>
+        <v>127386067</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>79061</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476840</v>
+        <v>476821</v>
       </c>
       <c r="R21" t="n">
-        <v>6854622</v>
+        <v>6854543</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,51 +2719,50 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127386067</v>
+        <v>127386848</v>
       </c>
       <c r="B22" t="n">
-        <v>79055</v>
+        <v>98467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,13 +2772,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476821</v>
+        <v>476840</v>
       </c>
       <c r="R22" t="n">
-        <v>6854543</v>
+        <v>6854622</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2817,50 +2816,51 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127387581</v>
+        <v>127386319</v>
       </c>
       <c r="B23" t="n">
-        <v>97336</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476827</v>
+        <v>476821</v>
       </c>
       <c r="R23" t="n">
-        <v>6854629</v>
+        <v>6854475</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2920,68 +2920,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127386302</v>
+        <v>127369424</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>80161</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476828</v>
+        <v>476879</v>
       </c>
       <c r="R24" t="n">
-        <v>6854531</v>
+        <v>6854650</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3008,86 +3000,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127388976</v>
+        <v>127387585</v>
       </c>
       <c r="B25" t="n">
-        <v>98459</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476880</v>
+        <v>476865</v>
       </c>
       <c r="R25" t="n">
-        <v>6854486</v>
+        <v>6854638</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3125,29 +3118,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127386102</v>
+        <v>127386302</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,22 +3166,26 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476821</v>
+        <v>476828</v>
       </c>
       <c r="R26" t="n">
-        <v>6854465</v>
+        <v>6854531</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3234,60 +3230,68 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127369424</v>
+        <v>127388976</v>
       </c>
       <c r="B27" t="n">
-        <v>80155</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476879</v>
+        <v>476880</v>
       </c>
       <c r="R27" t="n">
-        <v>6854650</v>
+        <v>6854486</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3314,87 +3318,82 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127387585</v>
+        <v>127386102</v>
       </c>
       <c r="B28" t="n">
-        <v>80126</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476865</v>
+        <v>476821</v>
       </c>
       <c r="R28" t="n">
-        <v>6854638</v>
+        <v>6854465</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3432,50 +3431,51 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127386319</v>
+        <v>127387581</v>
       </c>
       <c r="B29" t="n">
-        <v>79023</v>
+        <v>97344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,13 +3485,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476821</v>
+        <v>476827</v>
       </c>
       <c r="R29" t="n">
-        <v>6854475</v>
+        <v>6854629</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3535,60 +3535,67 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127386111</v>
+        <v>127386295</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>91369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476831</v>
+        <v>476888</v>
       </c>
       <c r="R30" t="n">
-        <v>6854682</v>
+        <v>6854664</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3626,70 +3633,67 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127386100</v>
+        <v>127370759</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>80167</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476829</v>
+        <v>476877</v>
       </c>
       <c r="R31" t="n">
-        <v>6854465</v>
+        <v>6854663</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3716,78 +3720,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127386112</v>
+        <v>127371357</v>
       </c>
       <c r="B32" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476873</v>
+        <v>476901</v>
       </c>
       <c r="R32" t="n">
-        <v>6854658</v>
+        <v>6854667</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3814,9 +3827,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3831,60 +3854,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127370759</v>
+        <v>127386111</v>
       </c>
       <c r="B33" t="n">
-        <v>80161</v>
+        <v>98467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476877</v>
+        <v>476831</v>
       </c>
       <c r="R33" t="n">
-        <v>6854663</v>
+        <v>6854682</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3911,19 +3934,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3938,67 +3951,64 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127386295</v>
+        <v>127386100</v>
       </c>
       <c r="B34" t="n">
-        <v>91361</v>
+        <v>98467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476888</v>
+        <v>476829</v>
       </c>
       <c r="R34" t="n">
-        <v>6854664</v>
+        <v>6854465</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4043,57 +4053,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127371357</v>
+        <v>127386299</v>
       </c>
       <c r="B35" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476901</v>
+        <v>476817</v>
       </c>
       <c r="R35" t="n">
-        <v>6854667</v>
+        <v>6854465</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4123,49 +4141,40 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127386299</v>
+        <v>127386303</v>
       </c>
       <c r="B36" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4192,7 +4201,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -4205,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476817</v>
+        <v>476836</v>
       </c>
       <c r="R36" t="n">
-        <v>6854465</v>
+        <v>6854627</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4268,10 +4277,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127386303</v>
+        <v>127386112</v>
       </c>
       <c r="B37" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4296,28 +4305,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476836</v>
+        <v>476873</v>
       </c>
       <c r="R37" t="n">
-        <v>6854627</v>
+        <v>6854658</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4355,19 +4356,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4377,7 +4377,7 @@
         <v>127386117</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
         <v>127386108</v>
       </c>
       <c r="B39" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>127387587</v>
       </c>
       <c r="B40" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>127386311</v>
       </c>
       <c r="B41" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>127387586</v>
       </c>
       <c r="B42" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>127369992</v>
       </c>
       <c r="B43" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>127388975</v>
       </c>
       <c r="B44" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>127386808</v>
       </c>
       <c r="B45" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>127386078</v>
       </c>
       <c r="B46" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>127370572</v>
       </c>
       <c r="B47" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5401,32 +5401,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127386312</v>
+        <v>127386087</v>
       </c>
       <c r="B48" t="n">
-        <v>98459</v>
+        <v>78787</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5436,13 +5436,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476860</v>
+        <v>476780</v>
       </c>
       <c r="R48" t="n">
-        <v>6854625</v>
+        <v>6854482</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5486,72 +5486,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127387598</v>
+        <v>127371346</v>
       </c>
       <c r="B49" t="n">
-        <v>98459</v>
+        <v>78787</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476767</v>
+        <v>476826</v>
       </c>
       <c r="R49" t="n">
-        <v>6854589</v>
+        <v>6854459</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5578,78 +5566,87 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127386838</v>
+        <v>127371200</v>
       </c>
       <c r="B50" t="n">
-        <v>98459</v>
+        <v>92631</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476819</v>
+        <v>476901</v>
       </c>
       <c r="R50" t="n">
-        <v>6854632</v>
+        <v>6854667</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5676,9 +5673,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5693,22 +5700,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127386087</v>
+        <v>127386089</v>
       </c>
       <c r="B51" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5740,10 +5747,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476780</v>
+        <v>476838</v>
       </c>
       <c r="R51" t="n">
-        <v>6854482</v>
+        <v>6854681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5802,32 +5809,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127386089</v>
+        <v>127386312</v>
       </c>
       <c r="B52" t="n">
-        <v>78781</v>
+        <v>98467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5837,13 +5844,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476838</v>
+        <v>476860</v>
       </c>
       <c r="R52" t="n">
-        <v>6854681</v>
+        <v>6854625</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5887,60 +5894,72 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127371200</v>
+        <v>127387598</v>
       </c>
       <c r="B53" t="n">
-        <v>92623</v>
+        <v>98467</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476901</v>
+        <v>476767</v>
       </c>
       <c r="R53" t="n">
-        <v>6854667</v>
+        <v>6854589</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5967,87 +5986,78 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127371346</v>
+        <v>127386838</v>
       </c>
       <c r="B54" t="n">
-        <v>78781</v>
+        <v>98467</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476826</v>
+        <v>476819</v>
       </c>
       <c r="R54" t="n">
-        <v>6854459</v>
+        <v>6854632</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6074,19 +6084,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6101,12 +6101,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elis Lewin, Alexander Ahl, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Sofia Damne, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6116,7 +6116,7 @@
         <v>127370418</v>
       </c>
       <c r="B55" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6220,10 +6220,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127388147</v>
+        <v>127372315</v>
       </c>
       <c r="B56" t="n">
-        <v>92631</v>
+        <v>56864</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6231,41 +6231,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476787</v>
+        <v>476894</v>
       </c>
       <c r="R56" t="n">
-        <v>6854642</v>
+        <v>6854772</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6295,40 +6293,49 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127372315</v>
+        <v>127388147</v>
       </c>
       <c r="B57" t="n">
-        <v>56858</v>
+        <v>92639</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6336,39 +6343,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476894</v>
+        <v>476787</v>
       </c>
       <c r="R57" t="n">
-        <v>6854772</v>
+        <v>6854642</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6398,39 +6407,30 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>17:12</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>17:12</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nadja Karlsson, Tilde Carlinger, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Ivar Anderberg, Filippa Paperin, Erik Christiansson, Emilia Blixt, Elias Blad, Elis Lewin, Alexander Ahl, Alice Helander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6440,7 +6440,7 @@
         <v>127386849</v>
       </c>
       <c r="B58" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>127387593</v>
       </c>
       <c r="B59" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>127387589</v>
       </c>
       <c r="B60" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>127386313</v>
       </c>
       <c r="B61" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>127371630</v>
       </c>
       <c r="B62" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>127387590</v>
       </c>
       <c r="B63" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7101,48 +7101,56 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127386068</v>
+        <v>127386308</v>
       </c>
       <c r="B64" t="n">
-        <v>79055</v>
+        <v>98467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>476822</v>
+        <v>476825</v>
       </c>
       <c r="R64" t="n">
         <v>6854551</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7180,28 +7188,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127386308</v>
+        <v>127386110</v>
       </c>
       <c r="B65" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7226,28 +7235,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476825</v>
+        <v>476818</v>
       </c>
       <c r="R65" t="n">
-        <v>6854551</v>
+        <v>6854660</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7285,19 +7286,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karla Alfaro Gripe</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7307,7 +7307,7 @@
         <v>127386842</v>
       </c>
       <c r="B66" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7401,10 +7401,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127386110</v>
+        <v>127386096</v>
       </c>
       <c r="B67" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7429,17 +7429,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476818</v>
+        <v>476806</v>
       </c>
       <c r="R67" t="n">
-        <v>6854660</v>
+        <v>6854483</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7480,6 +7484,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7498,49 +7503,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127386096</v>
+        <v>127386068</v>
       </c>
       <c r="B68" t="n">
-        <v>98459</v>
+        <v>79061</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476806</v>
+        <v>476822</v>
       </c>
       <c r="R68" t="n">
-        <v>6854483</v>
+        <v>6854551</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7581,7 +7582,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>127371302</v>
       </c>
       <c r="B69" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>127388970</v>
       </c>
       <c r="B70" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>127387596</v>
       </c>
       <c r="B71" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>127371242</v>
       </c>
       <c r="B72" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>127386109</v>
       </c>
       <c r="B73" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>127369233</v>
       </c>
       <c r="B74" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8234,10 +8234,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127388972</v>
+        <v>127386841</v>
       </c>
       <c r="B75" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8262,24 +8262,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476809</v>
+        <v>476865</v>
       </c>
       <c r="R75" t="n">
-        <v>6854638</v>
+        <v>6854629</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8317,29 +8313,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127387595</v>
+        <v>127388972</v>
       </c>
       <c r="B76" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8366,30 +8361,22 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476804</v>
+        <v>476809</v>
       </c>
       <c r="R76" t="n">
-        <v>6854628</v>
+        <v>6854638</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8434,22 +8421,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127386097</v>
+        <v>127387595</v>
       </c>
       <c r="B77" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8476,22 +8463,30 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476794</v>
+        <v>476804</v>
       </c>
       <c r="R77" t="n">
-        <v>6854562</v>
+        <v>6854628</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8536,22 +8531,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127386841</v>
+        <v>127386097</v>
       </c>
       <c r="B78" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8576,20 +8571,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476865</v>
+        <v>476794</v>
       </c>
       <c r="R78" t="n">
-        <v>6854629</v>
+        <v>6854562</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8627,66 +8626,67 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127386820</v>
+        <v>127369891</v>
       </c>
       <c r="B79" t="n">
-        <v>92623</v>
+        <v>80167</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>Mörtviken, Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476882</v>
+        <v>476866</v>
       </c>
       <c r="R79" t="n">
-        <v>6854669</v>
+        <v>6854642</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8713,9 +8713,19 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8730,12 +8740,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8745,7 +8755,7 @@
         <v>127386315</v>
       </c>
       <c r="B80" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8851,7 +8861,7 @@
         <v>127386103</v>
       </c>
       <c r="B81" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8953,7 +8963,7 @@
         <v>127386300</v>
       </c>
       <c r="B82" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9059,7 +9069,7 @@
         <v>127386843</v>
       </c>
       <c r="B83" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9156,7 +9166,7 @@
         <v>127386082</v>
       </c>
       <c r="B84" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,7 +9263,7 @@
         <v>127386834</v>
       </c>
       <c r="B85" t="n">
-        <v>80086</v>
+        <v>80092</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9351,32 +9361,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127369891</v>
+        <v>127369660</v>
       </c>
       <c r="B86" t="n">
-        <v>80161</v>
+        <v>96719</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9386,13 +9396,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476866</v>
+        <v>476880</v>
       </c>
       <c r="R86" t="n">
-        <v>6854642</v>
+        <v>6854794</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9421,7 +9431,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9431,7 +9441,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9446,22 +9456,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127369660</v>
+        <v>127386820</v>
       </c>
       <c r="B87" t="n">
-        <v>96711</v>
+        <v>92631</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9469,37 +9479,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>4361</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mörtviken, Mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476880</v>
+        <v>476882</v>
       </c>
       <c r="R87" t="n">
-        <v>6854794</v>
+        <v>6854669</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9526,19 +9536,9 @@
           <t>2025-08-10</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9553,12 +9553,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9568,7 +9568,7 @@
         <v>127386828</v>
       </c>
       <c r="B88" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9662,48 +9662,52 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127386080</v>
+        <v>127388974</v>
       </c>
       <c r="B89" t="n">
-        <v>92643</v>
+        <v>98467</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476799</v>
+        <v>476859</v>
       </c>
       <c r="R89" t="n">
-        <v>6854562</v>
+        <v>6854547</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9741,28 +9745,29 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127386129</v>
+        <v>127386080</v>
       </c>
       <c r="B90" t="n">
-        <v>92631</v>
+        <v>92651</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9770,21 +9775,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9794,10 +9799,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476790</v>
+        <v>476799</v>
       </c>
       <c r="R90" t="n">
-        <v>6854633</v>
+        <v>6854562</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9856,52 +9861,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127388974</v>
+        <v>127386129</v>
       </c>
       <c r="B91" t="n">
-        <v>98459</v>
+        <v>92639</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476859</v>
+        <v>476790</v>
       </c>
       <c r="R91" t="n">
-        <v>6854547</v>
+        <v>6854633</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9939,19 +9940,18 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9961,7 +9961,7 @@
         <v>127386840</v>
       </c>
       <c r="B92" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>127386320</v>
       </c>
       <c r="B93" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>127386101</v>
       </c>
       <c r="B94" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>127386837</v>
       </c>
       <c r="B95" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>127370318</v>
       </c>
       <c r="B96" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10471,52 +10471,56 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127386107</v>
+        <v>127388141</v>
       </c>
       <c r="B97" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Mörtviken, Hjd</t>
+          <t>mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476800</v>
+        <v>476834</v>
       </c>
       <c r="R97" t="n">
-        <v>6854551</v>
+        <v>6854535</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10554,19 +10558,18 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Nadja Karlsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
+          <t>Nadja Karlsson, Tilde Carlinger, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Ivar Anderberg, Filippa Paperin, Erik Christiansson, Emilia Blixt, Elias Blad, Elis Lewin, Alexander Ahl, Alice Helander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10576,7 +10579,7 @@
         <v>127386104</v>
       </c>
       <c r="B98" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10675,56 +10678,52 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127388141</v>
+        <v>127386107</v>
       </c>
       <c r="B99" t="n">
-        <v>57663</v>
+        <v>98467</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>mörtviken, Hjd</t>
+          <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476834</v>
+        <v>476800</v>
       </c>
       <c r="R99" t="n">
-        <v>6854535</v>
+        <v>6854551</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10762,70 +10761,67 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Nadja Karlsson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Nadja Karlsson, Alice Helander, Alexander Ahl, Elis Lewin, Elias Blad, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger</t>
+          <t>Erik Christiansson, Elis Lewin, Ivar Anderberg, Alexander Ahl, Nadja Karlsson, Tilde Carlinger, Emilia Blixt, Alice Helander, Sofia Damne, Malte Lindberg, Karla Alfaro Gripe, Karin Berg Andersson, Filippa Paperin, Elias Blad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127388967</v>
+        <v>127386088</v>
       </c>
       <c r="B100" t="n">
-        <v>98459</v>
+        <v>78787</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>476843</v>
+        <v>476826</v>
       </c>
       <c r="R100" t="n">
-        <v>6854525</v>
+        <v>6854482</v>
       </c>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10863,51 +10859,50 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Tilde Carlinger</t>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127386811</v>
+        <v>127386854</v>
       </c>
       <c r="B101" t="n">
-        <v>79612</v>
+        <v>92639</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10917,10 +10912,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476887</v>
+        <v>476899</v>
       </c>
       <c r="R101" t="n">
-        <v>6854810</v>
+        <v>6854779</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10972,7 +10967,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Elias Blad, Karin Berg Andersson, Elis Lewin, Erik Christiansson, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Tilde Carlinger, Nadja Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10982,7 +10977,7 @@
         <v>127386310</v>
       </c>
       <c r="B102" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11085,10 +11080,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127387594</v>
+        <v>127388967</v>
       </c>
       <c r="B103" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11115,30 +11110,22 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Mörtviken, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>476850</v>
+        <v>476843</v>
       </c>
       <c r="R103" t="n">
-        <v>6854546</v>
+        <v>6854525</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11183,60 +11170,72 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson, Erik Christiansson, Elis Lewin, Tilde Carlinger, Emilia Blixt, Malte Lindberg, Elias Blad, Alice Helander, Nadja Karlsson, Filippa Paperin</t>
+          <t>Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127386088</v>
+        <v>127387594</v>
       </c>
       <c r="B104" t="n">
-        <v>78781</v>
+        <v>98467</v>
       </c>
       <c r="D104" t=